--- a/salidas/empresas/GILD.xlsx
+++ b/salidas/empresas/GILD.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Mensual" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="EPS" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Acciones" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Info" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="Mensual" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="EPS" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Acciones" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="Info" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -23,13 +23,16 @@
     <numFmt numFmtId="164" formatCode="yyyy-mm-dd"/>
     <numFmt numFmtId="165" formatCode="YYYY-MM-DD"/>
   </numFmts>
-  <fonts count="1">
+  <fonts count="2">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -40,7 +43,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -48,12 +51,21 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
@@ -435,58 +447,58 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>fecha</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>precio_ajustado</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>precio_cierre</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>volumen</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>eps_ttm</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>pe</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>acciones_circulacion</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>market_cap</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>rotacion</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="1" t="n">
+      <c r="A2" s="2" t="n">
         <v>38748</v>
       </c>
       <c r="B2" t="n">
-        <v>10.38554573059082</v>
+        <v>10.38554382324219</v>
       </c>
       <c r="C2" t="n">
         <v>15.21749973297119</v>
@@ -501,11 +513,11 @@
       <c r="I2" t="inlineStr"/>
     </row>
     <row r="3">
-      <c r="A3" s="1" t="n">
+      <c r="A3" s="2" t="n">
         <v>38776</v>
       </c>
       <c r="B3" t="n">
-        <v>10.62440872192383</v>
+        <v>10.62440967559814</v>
       </c>
       <c r="C3" t="n">
         <v>15.56750011444092</v>
@@ -520,11 +532,11 @@
       <c r="I3" t="inlineStr"/>
     </row>
     <row r="4">
-      <c r="A4" s="1" t="n">
+      <c r="A4" s="2" t="n">
         <v>38807</v>
       </c>
       <c r="B4" t="n">
-        <v>10.61587905883789</v>
+        <v>10.61587810516357</v>
       </c>
       <c r="C4" t="n">
         <v>15.55500030517578</v>
@@ -539,11 +551,11 @@
       <c r="I4" t="inlineStr"/>
     </row>
     <row r="5">
-      <c r="A5" s="1" t="n">
+      <c r="A5" s="2" t="n">
         <v>38837</v>
       </c>
       <c r="B5" t="n">
-        <v>9.81055736541748</v>
+        <v>9.810559272766113</v>
       </c>
       <c r="C5" t="n">
         <v>14.375</v>
@@ -558,11 +570,11 @@
       <c r="I5" t="inlineStr"/>
     </row>
     <row r="6">
-      <c r="A6" s="1" t="n">
+      <c r="A6" s="2" t="n">
         <v>38868</v>
       </c>
       <c r="B6" t="n">
-        <v>9.78155517578125</v>
+        <v>9.781558036804199</v>
       </c>
       <c r="C6" t="n">
         <v>14.33250045776367</v>
@@ -577,11 +589,11 @@
       <c r="I6" t="inlineStr"/>
     </row>
     <row r="7">
-      <c r="A7" s="1" t="n">
+      <c r="A7" s="2" t="n">
         <v>38898</v>
       </c>
       <c r="B7" t="n">
-        <v>10.09378433227539</v>
+        <v>10.09378910064697</v>
       </c>
       <c r="C7" t="n">
         <v>14.78999996185303</v>
@@ -596,11 +608,11 @@
       <c r="I7" t="inlineStr"/>
     </row>
     <row r="8">
-      <c r="A8" s="1" t="n">
+      <c r="A8" s="2" t="n">
         <v>38929</v>
       </c>
       <c r="B8" t="n">
-        <v>10.49644470214844</v>
+        <v>10.49644565582275</v>
       </c>
       <c r="C8" t="n">
         <v>15.38000011444092</v>
@@ -615,7 +627,7 @@
       <c r="I8" t="inlineStr"/>
     </row>
     <row r="9">
-      <c r="A9" s="1" t="n">
+      <c r="A9" s="2" t="n">
         <v>38960</v>
       </c>
       <c r="B9" t="n">
@@ -634,11 +646,11 @@
       <c r="I9" t="inlineStr"/>
     </row>
     <row r="10">
-      <c r="A10" s="1" t="n">
+      <c r="A10" s="2" t="n">
         <v>38990</v>
       </c>
       <c r="B10" t="n">
-        <v>11.73342895507812</v>
+        <v>11.73343086242676</v>
       </c>
       <c r="C10" t="n">
         <v>17.1924991607666</v>
@@ -653,11 +665,11 @@
       <c r="I10" t="inlineStr"/>
     </row>
     <row r="11">
-      <c r="A11" s="1" t="n">
+      <c r="A11" s="2" t="n">
         <v>39021</v>
       </c>
       <c r="B11" t="n">
-        <v>11.75560760498047</v>
+        <v>11.7556095123291</v>
       </c>
       <c r="C11" t="n">
         <v>17.22500038146973</v>
@@ -672,7 +684,7 @@
       <c r="I11" t="inlineStr"/>
     </row>
     <row r="12">
-      <c r="A12" s="1" t="n">
+      <c r="A12" s="2" t="n">
         <v>39051</v>
       </c>
       <c r="B12" t="n">
@@ -691,11 +703,11 @@
       <c r="I12" t="inlineStr"/>
     </row>
     <row r="13">
-      <c r="A13" s="1" t="n">
+      <c r="A13" s="2" t="n">
         <v>39082</v>
       </c>
       <c r="B13" t="n">
-        <v>11.07825183868408</v>
+        <v>11.07825374603271</v>
       </c>
       <c r="C13" t="n">
         <v>16.23250007629395</v>
@@ -710,11 +722,11 @@
       <c r="I13" t="inlineStr"/>
     </row>
     <row r="14">
-      <c r="A14" s="1" t="n">
+      <c r="A14" s="2" t="n">
         <v>39113</v>
       </c>
       <c r="B14" t="n">
-        <v>10.97417640686035</v>
+        <v>10.9741792678833</v>
       </c>
       <c r="C14" t="n">
         <v>16.07999992370605</v>
@@ -729,11 +741,11 @@
       <c r="I14" t="inlineStr"/>
     </row>
     <row r="15">
-      <c r="A15" s="1" t="n">
+      <c r="A15" s="2" t="n">
         <v>39141</v>
       </c>
       <c r="B15" t="n">
-        <v>12.20945739746094</v>
+        <v>12.2094554901123</v>
       </c>
       <c r="C15" t="n">
         <v>17.88999938964844</v>
@@ -748,11 +760,11 @@
       <c r="I15" t="inlineStr"/>
     </row>
     <row r="16">
-      <c r="A16" s="1" t="n">
+      <c r="A16" s="2" t="n">
         <v>39172</v>
       </c>
       <c r="B16" t="n">
-        <v>13.05231285095215</v>
+        <v>13.05231094360352</v>
       </c>
       <c r="C16" t="n">
         <v>19.125</v>
@@ -767,11 +779,11 @@
       <c r="I16" t="inlineStr"/>
     </row>
     <row r="17">
-      <c r="A17" s="1" t="n">
+      <c r="A17" s="2" t="n">
         <v>39202</v>
       </c>
       <c r="B17" t="n">
-        <v>13.94293308258057</v>
+        <v>13.94293689727783</v>
       </c>
       <c r="C17" t="n">
         <v>20.43000030517578</v>
@@ -786,11 +798,11 @@
       <c r="I17" t="inlineStr"/>
     </row>
     <row r="18">
-      <c r="A18" s="1" t="n">
+      <c r="A18" s="2" t="n">
         <v>39233</v>
       </c>
       <c r="B18" t="n">
-        <v>14.12208461761475</v>
+        <v>14.1220874786377</v>
       </c>
       <c r="C18" t="n">
         <v>20.6924991607666</v>
@@ -805,11 +817,11 @@
       <c r="I18" t="inlineStr"/>
     </row>
     <row r="19">
-      <c r="A19" s="1" t="n">
+      <c r="A19" s="2" t="n">
         <v>39263</v>
       </c>
       <c r="B19" t="n">
-        <v>13.23998832702637</v>
+        <v>13.23998928070068</v>
       </c>
       <c r="C19" t="n">
         <v>19.39999961853027</v>
@@ -824,11 +836,11 @@
       <c r="I19" t="inlineStr"/>
     </row>
     <row r="20">
-      <c r="A20" s="1" t="n">
+      <c r="A20" s="2" t="n">
         <v>39294</v>
       </c>
       <c r="B20" t="n">
-        <v>12.70424938201904</v>
+        <v>12.70424842834473</v>
       </c>
       <c r="C20" t="n">
         <v>18.61499977111816</v>
@@ -843,11 +855,11 @@
       <c r="I20" t="inlineStr"/>
     </row>
     <row r="21">
-      <c r="A21" s="1" t="n">
+      <c r="A21" s="2" t="n">
         <v>39325</v>
       </c>
       <c r="B21" t="n">
-        <v>12.41078186035156</v>
+        <v>12.41078567504883</v>
       </c>
       <c r="C21" t="n">
         <v>18.18499946594238</v>
@@ -862,7 +874,7 @@
       <c r="I21" t="inlineStr"/>
     </row>
     <row r="22">
-      <c r="A22" s="1" t="n">
+      <c r="A22" s="2" t="n">
         <v>39355</v>
       </c>
       <c r="B22" t="n">
@@ -881,11 +893,11 @@
       <c r="I22" t="inlineStr"/>
     </row>
     <row r="23">
-      <c r="A23" s="1" t="n">
+      <c r="A23" s="2" t="n">
         <v>39386</v>
       </c>
       <c r="B23" t="n">
-        <v>15.76172637939453</v>
+        <v>15.76173114776611</v>
       </c>
       <c r="C23" t="n">
         <v>23.09499931335449</v>
@@ -900,11 +912,11 @@
       <c r="I23" t="inlineStr"/>
     </row>
     <row r="24">
-      <c r="A24" s="1" t="n">
+      <c r="A24" s="2" t="n">
         <v>39416</v>
       </c>
       <c r="B24" t="n">
-        <v>15.8811616897583</v>
+        <v>15.88116645812988</v>
       </c>
       <c r="C24" t="n">
         <v>23.27000045776367</v>
@@ -919,11 +931,11 @@
       <c r="I24" t="inlineStr"/>
     </row>
     <row r="25">
-      <c r="A25" s="1" t="n">
+      <c r="A25" s="2" t="n">
         <v>39447</v>
       </c>
       <c r="B25" t="n">
-        <v>15.70031070709229</v>
+        <v>15.70030975341797</v>
       </c>
       <c r="C25" t="n">
         <v>23.0049991607666</v>
@@ -938,11 +950,11 @@
       <c r="I25" t="inlineStr"/>
     </row>
     <row r="26">
-      <c r="A26" s="1" t="n">
+      <c r="A26" s="2" t="n">
         <v>39478</v>
       </c>
       <c r="B26" t="n">
-        <v>15.59110832214355</v>
+        <v>15.59111595153809</v>
       </c>
       <c r="C26" t="n">
         <v>22.84499931335449</v>
@@ -957,11 +969,11 @@
       <c r="I26" t="inlineStr"/>
     </row>
     <row r="27">
-      <c r="A27" s="1" t="n">
+      <c r="A27" s="2" t="n">
         <v>39507</v>
       </c>
       <c r="B27" t="n">
-        <v>16.14732360839844</v>
+        <v>16.1473331451416</v>
       </c>
       <c r="C27" t="n">
         <v>23.65999984741211</v>
@@ -976,11 +988,11 @@
       <c r="I27" t="inlineStr"/>
     </row>
     <row r="28">
-      <c r="A28" s="1" t="n">
+      <c r="A28" s="2" t="n">
         <v>39538</v>
       </c>
       <c r="B28" t="n">
-        <v>17.58393669128418</v>
+        <v>17.58392715454102</v>
       </c>
       <c r="C28" t="n">
         <v>25.76499938964844</v>
@@ -995,7 +1007,7 @@
       <c r="I28" t="inlineStr"/>
     </row>
     <row r="29">
-      <c r="A29" s="1" t="n">
+      <c r="A29" s="2" t="n">
         <v>39568</v>
       </c>
       <c r="B29" t="n">
@@ -1014,11 +1026,11 @@
       <c r="I29" t="inlineStr"/>
     </row>
     <row r="30">
-      <c r="A30" s="1" t="n">
+      <c r="A30" s="2" t="n">
         <v>39599</v>
       </c>
       <c r="B30" t="n">
-        <v>18.87722206115723</v>
+        <v>18.87722015380859</v>
       </c>
       <c r="C30" t="n">
         <v>27.65999984741211</v>
@@ -1033,11 +1045,11 @@
       <c r="I30" t="inlineStr"/>
     </row>
     <row r="31">
-      <c r="A31" s="1" t="n">
+      <c r="A31" s="2" t="n">
         <v>39629</v>
       </c>
       <c r="B31" t="n">
-        <v>18.06849479675293</v>
+        <v>18.06848907470703</v>
       </c>
       <c r="C31" t="n">
         <v>26.47500038146973</v>
@@ -1052,11 +1064,11 @@
       <c r="I31" t="inlineStr"/>
     </row>
     <row r="32">
-      <c r="A32" s="1" t="n">
+      <c r="A32" s="2" t="n">
         <v>39660</v>
       </c>
       <c r="B32" t="n">
-        <v>18.41996383666992</v>
+        <v>18.41996574401855</v>
       </c>
       <c r="C32" t="n">
         <v>26.98999977111816</v>
@@ -1071,11 +1083,11 @@
       <c r="I32" t="inlineStr"/>
     </row>
     <row r="33">
-      <c r="A33" s="1" t="n">
+      <c r="A33" s="2" t="n">
         <v>39691</v>
       </c>
       <c r="B33" t="n">
-        <v>17.97635841369629</v>
+        <v>17.97636222839355</v>
       </c>
       <c r="C33" t="n">
         <v>26.34000015258789</v>
@@ -1090,11 +1102,11 @@
       <c r="I33" t="inlineStr"/>
     </row>
     <row r="34">
-      <c r="A34" s="1" t="n">
+      <c r="A34" s="2" t="n">
         <v>39721</v>
       </c>
       <c r="B34" t="n">
-        <v>15.57063865661621</v>
+        <v>15.57063293457031</v>
       </c>
       <c r="C34" t="n">
         <v>22.81500053405762</v>
@@ -1109,11 +1121,11 @@
       <c r="I34" t="inlineStr"/>
     </row>
     <row r="35">
-      <c r="A35" s="1" t="n">
+      <c r="A35" s="2" t="n">
         <v>39752</v>
       </c>
       <c r="B35" t="n">
-        <v>15.64571094512939</v>
+        <v>15.64570426940918</v>
       </c>
       <c r="C35" t="n">
         <v>22.92499923706055</v>
@@ -1128,11 +1140,11 @@
       <c r="I35" t="inlineStr"/>
     </row>
     <row r="36">
-      <c r="A36" s="1" t="n">
+      <c r="A36" s="2" t="n">
         <v>39782</v>
       </c>
       <c r="B36" t="n">
-        <v>15.2840051651001</v>
+        <v>15.28400325775146</v>
       </c>
       <c r="C36" t="n">
         <v>22.39500045776367</v>
@@ -1147,11 +1159,11 @@
       <c r="I36" t="inlineStr"/>
     </row>
     <row r="37">
-      <c r="A37" s="1" t="n">
+      <c r="A37" s="2" t="n">
         <v>39813</v>
       </c>
       <c r="B37" t="n">
-        <v>17.45085334777832</v>
+        <v>17.45085144042969</v>
       </c>
       <c r="C37" t="n">
         <v>25.56999969482422</v>
@@ -1166,7 +1178,7 @@
       <c r="I37" t="inlineStr"/>
     </row>
     <row r="38">
-      <c r="A38" s="1" t="n">
+      <c r="A38" s="2" t="n">
         <v>39844</v>
       </c>
       <c r="B38" t="n">
@@ -1185,11 +1197,11 @@
       <c r="I38" t="inlineStr"/>
     </row>
     <row r="39">
-      <c r="A39" s="1" t="n">
+      <c r="A39" s="2" t="n">
         <v>39872</v>
       </c>
       <c r="B39" t="n">
-        <v>15.28741455078125</v>
+        <v>15.28740787506104</v>
       </c>
       <c r="C39" t="n">
         <v>22.39999961853027</v>
@@ -1204,11 +1216,11 @@
       <c r="I39" t="inlineStr"/>
     </row>
     <row r="40">
-      <c r="A40" s="1" t="n">
+      <c r="A40" s="2" t="n">
         <v>39903</v>
       </c>
       <c r="B40" t="n">
-        <v>15.80608654022217</v>
+        <v>15.80608749389648</v>
       </c>
       <c r="C40" t="n">
         <v>23.15999984741211</v>
@@ -1223,11 +1235,11 @@
       <c r="I40" t="inlineStr"/>
     </row>
     <row r="41">
-      <c r="A41" s="1" t="n">
+      <c r="A41" s="2" t="n">
         <v>39933</v>
       </c>
       <c r="B41" t="n">
-        <v>15.6286506652832</v>
+        <v>15.62864971160889</v>
       </c>
       <c r="C41" t="n">
         <v>22.89999961853027</v>
@@ -1242,11 +1254,11 @@
       <c r="I41" t="inlineStr"/>
     </row>
     <row r="42">
-      <c r="A42" s="1" t="n">
+      <c r="A42" s="2" t="n">
         <v>39964</v>
       </c>
       <c r="B42" t="n">
-        <v>14.70730209350586</v>
+        <v>14.70730590820312</v>
       </c>
       <c r="C42" t="n">
         <v>21.54999923706055</v>
@@ -1261,11 +1273,11 @@
       <c r="I42" t="inlineStr"/>
     </row>
     <row r="43">
-      <c r="A43" s="1" t="n">
+      <c r="A43" s="2" t="n">
         <v>39994</v>
       </c>
       <c r="B43" t="n">
-        <v>15.98353576660156</v>
+        <v>15.98353290557861</v>
       </c>
       <c r="C43" t="n">
         <v>23.42000007629395</v>
@@ -1280,11 +1292,11 @@
       <c r="I43" t="inlineStr"/>
     </row>
     <row r="44">
-      <c r="A44" s="1" t="n">
+      <c r="A44" s="2" t="n">
         <v>40025</v>
       </c>
       <c r="B44" t="n">
-        <v>16.69671821594238</v>
+        <v>16.69672584533691</v>
       </c>
       <c r="C44" t="n">
         <v>24.46500015258789</v>
@@ -1299,7 +1311,7 @@
       <c r="I44" t="inlineStr"/>
     </row>
     <row r="45">
-      <c r="A45" s="1" t="n">
+      <c r="A45" s="2" t="n">
         <v>40056</v>
       </c>
       <c r="B45" t="n">
@@ -1324,11 +1336,11 @@
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="1" t="n">
+      <c r="A46" s="2" t="n">
         <v>40086</v>
       </c>
       <c r="B46" t="n">
-        <v>15.86751174926758</v>
+        <v>15.86751461029053</v>
       </c>
       <c r="C46" t="n">
         <v>23.25</v>
@@ -1349,11 +1361,11 @@
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="1" t="n">
+      <c r="A47" s="2" t="n">
         <v>40117</v>
       </c>
       <c r="B47" t="n">
-        <v>14.51963329315186</v>
+        <v>14.51962375640869</v>
       </c>
       <c r="C47" t="n">
         <v>21.27499961853027</v>
@@ -1374,11 +1386,11 @@
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="1" t="n">
+      <c r="A48" s="2" t="n">
         <v>40147</v>
       </c>
       <c r="B48" t="n">
-        <v>15.73443126678467</v>
+        <v>15.73443222045898</v>
       </c>
       <c r="C48" t="n">
         <v>23.05500030517578</v>
@@ -1399,11 +1411,11 @@
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="1" t="n">
+      <c r="A49" s="2" t="n">
         <v>40178</v>
       </c>
       <c r="B49" t="n">
-        <v>14.76531791687012</v>
+        <v>14.76531219482422</v>
       </c>
       <c r="C49" t="n">
         <v>21.63500022888184</v>
@@ -1424,11 +1436,11 @@
       </c>
     </row>
     <row r="50">
-      <c r="A50" s="1" t="n">
+      <c r="A50" s="2" t="n">
         <v>40209</v>
       </c>
       <c r="B50" t="n">
-        <v>16.47150611877441</v>
+        <v>16.47150421142578</v>
       </c>
       <c r="C50" t="n">
         <v>24.13500022888184</v>
@@ -1449,11 +1461,11 @@
       </c>
     </row>
     <row r="51">
-      <c r="A51" s="1" t="n">
+      <c r="A51" s="2" t="n">
         <v>40237</v>
       </c>
       <c r="B51" t="n">
-        <v>16.24628829956055</v>
+        <v>16.24629020690918</v>
       </c>
       <c r="C51" t="n">
         <v>23.80500030517578</v>
@@ -1474,11 +1486,11 @@
       </c>
     </row>
     <row r="52">
-      <c r="A52" s="1" t="n">
+      <c r="A52" s="2" t="n">
         <v>40268</v>
       </c>
       <c r="B52" t="n">
-        <v>15.51603889465332</v>
+        <v>15.51604080200195</v>
       </c>
       <c r="C52" t="n">
         <v>22.73500061035156</v>
@@ -1499,11 +1511,11 @@
       </c>
     </row>
     <row r="53">
-      <c r="A53" s="1" t="n">
+      <c r="A53" s="2" t="n">
         <v>40298</v>
       </c>
       <c r="B53" t="n">
-        <v>13.55051422119141</v>
+        <v>13.55051326751709</v>
       </c>
       <c r="C53" t="n">
         <v>19.85499954223633</v>
@@ -1524,11 +1536,11 @@
       </c>
     </row>
     <row r="54">
-      <c r="A54" s="1" t="n">
+      <c r="A54" s="2" t="n">
         <v>40329</v>
       </c>
       <c r="B54" t="n">
-        <v>12.25722789764404</v>
+        <v>12.25722599029541</v>
       </c>
       <c r="C54" t="n">
         <v>17.95999908447266</v>
@@ -1549,11 +1561,11 @@
       </c>
     </row>
     <row r="55">
-      <c r="A55" s="1" t="n">
+      <c r="A55" s="2" t="n">
         <v>40359</v>
       </c>
       <c r="B55" t="n">
-        <v>11.69759464263916</v>
+        <v>11.69759941101074</v>
       </c>
       <c r="C55" t="n">
         <v>17.13999938964844</v>
@@ -1574,11 +1586,11 @@
       </c>
     </row>
     <row r="56">
-      <c r="A56" s="1" t="n">
+      <c r="A56" s="2" t="n">
         <v>40390</v>
       </c>
       <c r="B56" t="n">
-        <v>11.37001419067383</v>
+        <v>11.37001037597656</v>
       </c>
       <c r="C56" t="n">
         <v>16.65999984741211</v>
@@ -1599,11 +1611,11 @@
       </c>
     </row>
     <row r="57">
-      <c r="A57" s="1" t="n">
+      <c r="A57" s="2" t="n">
         <v>40421</v>
       </c>
       <c r="B57" t="n">
-        <v>10.86157035827637</v>
+        <v>10.86156845092773</v>
       </c>
       <c r="C57" t="n">
         <v>15.91499996185303</v>
@@ -1624,11 +1636,11 @@
       </c>
     </row>
     <row r="58">
-      <c r="A58" s="1" t="n">
+      <c r="A58" s="2" t="n">
         <v>40451</v>
       </c>
       <c r="B58" t="n">
-        <v>12.15144729614258</v>
+        <v>12.151442527771</v>
       </c>
       <c r="C58" t="n">
         <v>17.80500030517578</v>
@@ -1649,11 +1661,11 @@
       </c>
     </row>
     <row r="59">
-      <c r="A59" s="1" t="n">
+      <c r="A59" s="2" t="n">
         <v>40482</v>
       </c>
       <c r="B59" t="n">
-        <v>13.53686714172363</v>
+        <v>13.53686428070068</v>
       </c>
       <c r="C59" t="n">
         <v>19.83499908447266</v>
@@ -1674,11 +1686,11 @@
       </c>
     </row>
     <row r="60">
-      <c r="A60" s="1" t="n">
+      <c r="A60" s="2" t="n">
         <v>40512</v>
       </c>
       <c r="B60" t="n">
-        <v>12.45514488220215</v>
+        <v>12.45514392852783</v>
       </c>
       <c r="C60" t="n">
         <v>18.25</v>
@@ -1699,11 +1711,11 @@
       </c>
     </row>
     <row r="61">
-      <c r="A61" s="1" t="n">
+      <c r="A61" s="2" t="n">
         <v>40543</v>
       </c>
       <c r="B61" t="n">
-        <v>12.36642456054688</v>
+        <v>12.36642265319824</v>
       </c>
       <c r="C61" t="n">
         <v>18.1200008392334</v>
@@ -1724,11 +1736,11 @@
       </c>
     </row>
     <row r="62">
-      <c r="A62" s="1" t="n">
+      <c r="A62" s="2" t="n">
         <v>40574</v>
       </c>
       <c r="B62" t="n">
-        <v>13.09667491912842</v>
+        <v>13.09667301177979</v>
       </c>
       <c r="C62" t="n">
         <v>19.19000053405762</v>
@@ -1749,11 +1761,11 @@
       </c>
     </row>
     <row r="63">
-      <c r="A63" s="1" t="n">
+      <c r="A63" s="2" t="n">
         <v>40602</v>
       </c>
       <c r="B63" t="n">
-        <v>13.30141067504883</v>
+        <v>13.30141448974609</v>
       </c>
       <c r="C63" t="n">
         <v>19.48999977111816</v>
@@ -1778,11 +1790,11 @@
       </c>
     </row>
     <row r="64">
-      <c r="A64" s="1" t="n">
+      <c r="A64" s="2" t="n">
         <v>40633</v>
       </c>
       <c r="B64" t="n">
-        <v>14.49232959747314</v>
+        <v>14.49233055114746</v>
       </c>
       <c r="C64" t="n">
         <v>21.23500061035156</v>
@@ -1807,11 +1819,11 @@
       </c>
     </row>
     <row r="65">
-      <c r="A65" s="1" t="n">
+      <c r="A65" s="2" t="n">
         <v>40663</v>
       </c>
       <c r="B65" t="n">
-        <v>13.25364112854004</v>
+        <v>13.25363636016846</v>
       </c>
       <c r="C65" t="n">
         <v>19.42000007629395</v>
@@ -1836,11 +1848,11 @@
       </c>
     </row>
     <row r="66">
-      <c r="A66" s="1" t="n">
+      <c r="A66" s="2" t="n">
         <v>40694</v>
       </c>
       <c r="B66" t="n">
-        <v>14.24322414398193</v>
+        <v>14.24322700500488</v>
       </c>
       <c r="C66" t="n">
         <v>20.8700008392334</v>
@@ -1865,11 +1877,11 @@
       </c>
     </row>
     <row r="67">
-      <c r="A67" s="1" t="n">
+      <c r="A67" s="2" t="n">
         <v>40724</v>
       </c>
       <c r="B67" t="n">
-        <v>14.13061904907227</v>
+        <v>14.13061618804932</v>
       </c>
       <c r="C67" t="n">
         <v>20.70499992370605</v>
@@ -1894,7 +1906,7 @@
       </c>
     </row>
     <row r="68">
-      <c r="A68" s="1" t="n">
+      <c r="A68" s="2" t="n">
         <v>40755</v>
       </c>
       <c r="B68" t="n">
@@ -1923,11 +1935,11 @@
       </c>
     </row>
     <row r="69">
-      <c r="A69" s="1" t="n">
+      <c r="A69" s="2" t="n">
         <v>40786</v>
       </c>
       <c r="B69" t="n">
-        <v>13.60852718353271</v>
+        <v>13.6085262298584</v>
       </c>
       <c r="C69" t="n">
         <v>19.94000053405762</v>
@@ -1952,11 +1964,11 @@
       </c>
     </row>
     <row r="70">
-      <c r="A70" s="1" t="n">
+      <c r="A70" s="2" t="n">
         <v>40816</v>
       </c>
       <c r="B70" t="n">
-        <v>13.23998832702637</v>
+        <v>13.23998928070068</v>
       </c>
       <c r="C70" t="n">
         <v>19.39999961853027</v>
@@ -1981,11 +1993,11 @@
       </c>
     </row>
     <row r="71">
-      <c r="A71" s="1" t="n">
+      <c r="A71" s="2" t="n">
         <v>40847</v>
       </c>
       <c r="B71" t="n">
-        <v>14.21592712402344</v>
+        <v>14.21592617034912</v>
       </c>
       <c r="C71" t="n">
         <v>20.82999992370605</v>
@@ -2010,11 +2022,11 @@
       </c>
     </row>
     <row r="72">
-      <c r="A72" s="1" t="n">
+      <c r="A72" s="2" t="n">
         <v>40877</v>
       </c>
       <c r="B72" t="n">
-        <v>13.59828758239746</v>
+        <v>13.59828948974609</v>
       </c>
       <c r="C72" t="n">
         <v>19.92499923706055</v>
@@ -2039,11 +2051,11 @@
       </c>
     </row>
     <row r="73">
-      <c r="A73" s="1" t="n">
+      <c r="A73" s="2" t="n">
         <v>40908</v>
       </c>
       <c r="B73" t="n">
-        <v>13.96682453155518</v>
+        <v>13.96682834625244</v>
       </c>
       <c r="C73" t="n">
         <v>20.46500015258789</v>
@@ -2068,11 +2080,11 @@
       </c>
     </row>
     <row r="74">
-      <c r="A74" s="1" t="n">
+      <c r="A74" s="2" t="n">
         <v>40939</v>
       </c>
       <c r="B74" t="n">
-        <v>16.67283630371094</v>
+        <v>16.67283248901367</v>
       </c>
       <c r="C74" t="n">
         <v>24.43000030517578</v>
@@ -2097,11 +2109,11 @@
       </c>
     </row>
     <row r="75">
-      <c r="A75" s="1" t="n">
+      <c r="A75" s="2" t="n">
         <v>40968</v>
       </c>
       <c r="B75" t="n">
-        <v>15.53992938995361</v>
+        <v>15.53992652893066</v>
       </c>
       <c r="C75" t="n">
         <v>22.77000045776367</v>
@@ -2126,11 +2138,11 @@
       </c>
     </row>
     <row r="76">
-      <c r="A76" s="1" t="n">
+      <c r="A76" s="2" t="n">
         <v>40999</v>
       </c>
       <c r="B76" t="n">
-        <v>16.67283630371094</v>
+        <v>16.67283248901367</v>
       </c>
       <c r="C76" t="n">
         <v>24.43000030517578</v>
@@ -2155,11 +2167,11 @@
       </c>
     </row>
     <row r="77">
-      <c r="A77" s="1" t="n">
+      <c r="A77" s="2" t="n">
         <v>41029</v>
       </c>
       <c r="B77" t="n">
-        <v>17.75114059448242</v>
+        <v>17.75113868713379</v>
       </c>
       <c r="C77" t="n">
         <v>26.01000022888184</v>
@@ -2184,11 +2196,11 @@
       </c>
     </row>
     <row r="78">
-      <c r="A78" s="1" t="n">
+      <c r="A78" s="2" t="n">
         <v>41060</v>
       </c>
       <c r="B78" t="n">
-        <v>17.04478073120117</v>
+        <v>17.04478645324707</v>
       </c>
       <c r="C78" t="n">
         <v>24.97500038146973</v>
@@ -2213,11 +2225,11 @@
       </c>
     </row>
     <row r="79">
-      <c r="A79" s="1" t="n">
+      <c r="A79" s="2" t="n">
         <v>41090</v>
       </c>
       <c r="B79" t="n">
-        <v>17.49862861633301</v>
+        <v>17.49862670898438</v>
       </c>
       <c r="C79" t="n">
         <v>25.63999938964844</v>
@@ -2242,11 +2254,11 @@
       </c>
     </row>
     <row r="80">
-      <c r="A80" s="1" t="n">
+      <c r="A80" s="2" t="n">
         <v>41121</v>
       </c>
       <c r="B80" t="n">
-        <v>18.53939437866211</v>
+        <v>18.53939819335938</v>
       </c>
       <c r="C80" t="n">
         <v>27.16500091552734</v>
@@ -2271,11 +2283,11 @@
       </c>
     </row>
     <row r="81">
-      <c r="A81" s="1" t="n">
+      <c r="A81" s="2" t="n">
         <v>41152</v>
       </c>
       <c r="B81" t="n">
-        <v>19.68594932556152</v>
+        <v>19.68595314025879</v>
       </c>
       <c r="C81" t="n">
         <v>28.84499931335449</v>
@@ -2300,11 +2312,11 @@
       </c>
     </row>
     <row r="82">
-      <c r="A82" s="1" t="n">
+      <c r="A82" s="2" t="n">
         <v>41182</v>
       </c>
       <c r="B82" t="n">
-        <v>22.63424491882324</v>
+        <v>22.63423728942871</v>
       </c>
       <c r="C82" t="n">
         <v>33.16500091552734</v>
@@ -2329,11 +2341,11 @@
       </c>
     </row>
     <row r="83">
-      <c r="A83" s="1" t="n">
+      <c r="A83" s="2" t="n">
         <v>41213</v>
       </c>
       <c r="B83" t="n">
-        <v>22.92429351806641</v>
+        <v>22.92429733276367</v>
       </c>
       <c r="C83" t="n">
         <v>33.59000015258789</v>
@@ -2358,11 +2370,11 @@
       </c>
     </row>
     <row r="84">
-      <c r="A84" s="1" t="n">
+      <c r="A84" s="2" t="n">
         <v>41243</v>
       </c>
       <c r="B84" t="n">
-        <v>25.59276390075684</v>
+        <v>25.5927619934082</v>
       </c>
       <c r="C84" t="n">
         <v>37.5</v>
@@ -2387,11 +2399,11 @@
       </c>
     </row>
     <row r="85">
-      <c r="A85" s="1" t="n">
+      <c r="A85" s="2" t="n">
         <v>41274</v>
       </c>
       <c r="B85" t="n">
-        <v>25.06384468078613</v>
+        <v>25.06384658813477</v>
       </c>
       <c r="C85" t="n">
         <v>36.72499847412109</v>
@@ -2416,7 +2428,7 @@
       </c>
     </row>
     <row r="86">
-      <c r="A86" s="1" t="n">
+      <c r="A86" s="2" t="n">
         <v>41305</v>
       </c>
       <c r="B86" t="n">
@@ -2445,11 +2457,11 @@
       </c>
     </row>
     <row r="87">
-      <c r="A87" s="1" t="n">
+      <c r="A87" s="2" t="n">
         <v>41333</v>
       </c>
       <c r="B87" t="n">
-        <v>29.15527153015137</v>
+        <v>29.1552791595459</v>
       </c>
       <c r="C87" t="n">
         <v>42.72000122070312</v>
@@ -2474,11 +2486,11 @@
       </c>
     </row>
     <row r="88">
-      <c r="A88" s="1" t="n">
+      <c r="A88" s="2" t="n">
         <v>41364</v>
       </c>
       <c r="B88" t="n">
-        <v>33.40027236938477</v>
+        <v>33.40026092529297</v>
       </c>
       <c r="C88" t="n">
         <v>48.93999862670898</v>
@@ -2503,7 +2515,7 @@
       </c>
     </row>
     <row r="89">
-      <c r="A89" s="1" t="n">
+      <c r="A89" s="2" t="n">
         <v>41394</v>
       </c>
       <c r="B89" t="n">
@@ -2532,7 +2544,7 @@
       </c>
     </row>
     <row r="90">
-      <c r="A90" s="1" t="n">
+      <c r="A90" s="2" t="n">
         <v>41425</v>
       </c>
       <c r="B90" t="n">
@@ -2561,11 +2573,11 @@
       </c>
     </row>
     <row r="91">
-      <c r="A91" s="1" t="n">
+      <c r="A91" s="2" t="n">
         <v>41455</v>
       </c>
       <c r="B91" t="n">
-        <v>34.99042892456055</v>
+        <v>34.99043655395508</v>
       </c>
       <c r="C91" t="n">
         <v>51.27000045776367</v>
@@ -2590,11 +2602,11 @@
       </c>
     </row>
     <row r="92">
-      <c r="A92" s="1" t="n">
+      <c r="A92" s="2" t="n">
         <v>41486</v>
       </c>
       <c r="B92" t="n">
-        <v>41.90388870239258</v>
+        <v>41.90387725830078</v>
       </c>
       <c r="C92" t="n">
         <v>61.40000152587891</v>
@@ -2619,11 +2631,11 @@
       </c>
     </row>
     <row r="93">
-      <c r="A93" s="1" t="n">
+      <c r="A93" s="2" t="n">
         <v>41517</v>
       </c>
       <c r="B93" t="n">
-        <v>41.13269805908203</v>
+        <v>41.13268661499023</v>
       </c>
       <c r="C93" t="n">
         <v>60.27000045776367</v>
@@ -2648,11 +2660,11 @@
       </c>
     </row>
     <row r="94">
-      <c r="A94" s="1" t="n">
+      <c r="A94" s="2" t="n">
         <v>41547</v>
       </c>
       <c r="B94" t="n">
-        <v>42.90711975097656</v>
+        <v>42.90712356567383</v>
       </c>
       <c r="C94" t="n">
         <v>62.86999893188477</v>
@@ -2677,11 +2689,11 @@
       </c>
     </row>
     <row r="95">
-      <c r="A95" s="1" t="n">
+      <c r="A95" s="2" t="n">
         <v>41578</v>
       </c>
       <c r="B95" t="n">
-        <v>48.5784797668457</v>
+        <v>48.57848739624023</v>
       </c>
       <c r="C95" t="n">
         <v>71.18000030517578</v>
@@ -2706,11 +2718,11 @@
       </c>
     </row>
     <row r="96">
-      <c r="A96" s="1" t="n">
+      <c r="A96" s="2" t="n">
         <v>41608</v>
       </c>
       <c r="B96" t="n">
-        <v>51.05585479736328</v>
+        <v>51.05585098266602</v>
       </c>
       <c r="C96" t="n">
         <v>74.80999755859375</v>
@@ -2735,11 +2747,11 @@
       </c>
     </row>
     <row r="97">
-      <c r="A97" s="1" t="n">
+      <c r="A97" s="2" t="n">
         <v>41639</v>
       </c>
       <c r="B97" t="n">
-        <v>51.25378799438477</v>
+        <v>51.2537727355957</v>
       </c>
       <c r="C97" t="n">
         <v>75.09999847412109</v>
@@ -2764,11 +2776,11 @@
       </c>
     </row>
     <row r="98">
-      <c r="A98" s="1" t="n">
+      <c r="A98" s="2" t="n">
         <v>41670</v>
       </c>
       <c r="B98" t="n">
-        <v>55.04149627685547</v>
+        <v>55.04150009155273</v>
       </c>
       <c r="C98" t="n">
         <v>80.65000152587891</v>
@@ -2793,11 +2805,11 @@
       </c>
     </row>
     <row r="99">
-      <c r="A99" s="1" t="n">
+      <c r="A99" s="2" t="n">
         <v>41698</v>
       </c>
       <c r="B99" t="n">
-        <v>56.50200271606445</v>
+        <v>56.50199890136719</v>
       </c>
       <c r="C99" t="n">
         <v>82.79000091552734</v>
@@ -2822,11 +2834,11 @@
       </c>
     </row>
     <row r="100">
-      <c r="A100" s="1" t="n">
+      <c r="A100" s="2" t="n">
         <v>41729</v>
       </c>
       <c r="B100" t="n">
-        <v>48.3600959777832</v>
+        <v>48.36009216308594</v>
       </c>
       <c r="C100" t="n">
         <v>70.86000061035156</v>
@@ -2851,11 +2863,11 @@
       </c>
     </row>
     <row r="101">
-      <c r="A101" s="1" t="n">
+      <c r="A101" s="2" t="n">
         <v>41759</v>
       </c>
       <c r="B101" t="n">
-        <v>53.56736755371094</v>
+        <v>53.56735610961914</v>
       </c>
       <c r="C101" t="n">
         <v>78.48999786376953</v>
@@ -2880,11 +2892,11 @@
       </c>
     </row>
     <row r="102">
-      <c r="A102" s="1" t="n">
+      <c r="A102" s="2" t="n">
         <v>41790</v>
       </c>
       <c r="B102" t="n">
-        <v>55.42367935180664</v>
+        <v>55.4237174987793</v>
       </c>
       <c r="C102" t="n">
         <v>81.20999908447266</v>
@@ -2909,11 +2921,11 @@
       </c>
     </row>
     <row r="103">
-      <c r="A103" s="1" t="n">
+      <c r="A103" s="2" t="n">
         <v>41820</v>
       </c>
       <c r="B103" t="n">
-        <v>56.58388519287109</v>
+        <v>56.58390045166016</v>
       </c>
       <c r="C103" t="n">
         <v>82.91000366210938</v>
@@ -2938,11 +2950,11 @@
       </c>
     </row>
     <row r="104">
-      <c r="A104" s="1" t="n">
+      <c r="A104" s="2" t="n">
         <v>41851</v>
       </c>
       <c r="B104" t="n">
-        <v>62.48047256469727</v>
+        <v>62.48048400878906</v>
       </c>
       <c r="C104" t="n">
         <v>91.55000305175781</v>
@@ -2967,11 +2979,11 @@
       </c>
     </row>
     <row r="105">
-      <c r="A105" s="1" t="n">
+      <c r="A105" s="2" t="n">
         <v>41882</v>
       </c>
       <c r="B105" t="n">
-        <v>73.40689086914062</v>
+        <v>73.4068603515625</v>
       </c>
       <c r="C105" t="n">
         <v>107.5599975585938</v>
@@ -2996,11 +3008,11 @@
       </c>
     </row>
     <row r="106">
-      <c r="A106" s="1" t="n">
+      <c r="A106" s="2" t="n">
         <v>41912</v>
       </c>
       <c r="B106" t="n">
-        <v>72.64932250976562</v>
+        <v>72.64933013916016</v>
       </c>
       <c r="C106" t="n">
         <v>106.4499969482422</v>
@@ -3025,7 +3037,7 @@
       </c>
     </row>
     <row r="107">
-      <c r="A107" s="1" t="n">
+      <c r="A107" s="2" t="n">
         <v>41943</v>
       </c>
       <c r="B107" t="n">
@@ -3054,7 +3066,7 @@
       </c>
     </row>
     <row r="108">
-      <c r="A108" s="1" t="n">
+      <c r="A108" s="2" t="n">
         <v>41973</v>
       </c>
       <c r="B108" t="n">
@@ -3083,11 +3095,11 @@
       </c>
     </row>
     <row r="109">
-      <c r="A109" s="1" t="n">
+      <c r="A109" s="2" t="n">
         <v>42004</v>
       </c>
       <c r="B109" t="n">
-        <v>64.32997894287109</v>
+        <v>64.33000183105469</v>
       </c>
       <c r="C109" t="n">
         <v>94.26000213623047</v>
@@ -3112,11 +3124,11 @@
       </c>
     </row>
     <row r="110">
-      <c r="A110" s="1" t="n">
+      <c r="A110" s="2" t="n">
         <v>42035</v>
       </c>
       <c r="B110" t="n">
-        <v>71.543701171875</v>
+        <v>71.54372406005859</v>
       </c>
       <c r="C110" t="n">
         <v>104.8300018310547</v>
@@ -3141,11 +3153,11 @@
       </c>
     </row>
     <row r="111">
-      <c r="A111" s="1" t="n">
+      <c r="A111" s="2" t="n">
         <v>42063</v>
       </c>
       <c r="B111" t="n">
-        <v>70.656494140625</v>
+        <v>70.65651702880859</v>
       </c>
       <c r="C111" t="n">
         <v>103.5299987792969</v>
@@ -3170,11 +3182,11 @@
       </c>
     </row>
     <row r="112">
-      <c r="A112" s="1" t="n">
+      <c r="A112" s="2" t="n">
         <v>42094</v>
       </c>
       <c r="B112" t="n">
-        <v>66.97111511230469</v>
+        <v>66.97114562988281</v>
       </c>
       <c r="C112" t="n">
         <v>98.12999725341797</v>
@@ -3199,11 +3211,11 @@
       </c>
     </row>
     <row r="113">
-      <c r="A113" s="1" t="n">
+      <c r="A113" s="2" t="n">
         <v>42124</v>
       </c>
       <c r="B113" t="n">
-        <v>68.59543609619141</v>
+        <v>68.59544372558594</v>
       </c>
       <c r="C113" t="n">
         <v>100.5100021362305</v>
@@ -3228,11 +3240,11 @@
       </c>
     </row>
     <row r="114">
-      <c r="A114" s="1" t="n">
+      <c r="A114" s="2" t="n">
         <v>42155</v>
       </c>
       <c r="B114" t="n">
-        <v>76.62133026123047</v>
+        <v>76.62132263183594</v>
       </c>
       <c r="C114" t="n">
         <v>112.2699966430664</v>
@@ -3257,7 +3269,7 @@
       </c>
     </row>
     <row r="115">
-      <c r="A115" s="1" t="n">
+      <c r="A115" s="2" t="n">
         <v>42185</v>
       </c>
       <c r="B115" t="n">
@@ -3286,11 +3298,11 @@
       </c>
     </row>
     <row r="116">
-      <c r="A116" s="1" t="n">
+      <c r="A116" s="2" t="n">
         <v>42216</v>
       </c>
       <c r="B116" t="n">
-        <v>80.72774505615234</v>
+        <v>80.72775268554688</v>
       </c>
       <c r="C116" t="n">
         <v>117.8600006103516</v>
@@ -3315,11 +3327,11 @@
       </c>
     </row>
     <row r="117">
-      <c r="A117" s="1" t="n">
+      <c r="A117" s="2" t="n">
         <v>42247</v>
       </c>
       <c r="B117" t="n">
-        <v>71.96726226806641</v>
+        <v>71.96730804443359</v>
       </c>
       <c r="C117" t="n">
         <v>105.0699996948242</v>
@@ -3344,11 +3356,11 @@
       </c>
     </row>
     <row r="118">
-      <c r="A118" s="1" t="n">
+      <c r="A118" s="2" t="n">
         <v>42277</v>
       </c>
       <c r="B118" t="n">
-        <v>67.51971435546875</v>
+        <v>67.51969146728516</v>
       </c>
       <c r="C118" t="n">
         <v>98.19000244140625</v>
@@ -3373,7 +3385,7 @@
       </c>
     </row>
     <row r="119">
-      <c r="A119" s="1" t="n">
+      <c r="A119" s="2" t="n">
         <v>42308</v>
       </c>
       <c r="B119" t="n">
@@ -3402,11 +3414,11 @@
       </c>
     </row>
     <row r="120">
-      <c r="A120" s="1" t="n">
+      <c r="A120" s="2" t="n">
         <v>42338</v>
       </c>
       <c r="B120" t="n">
-        <v>72.86269378662109</v>
+        <v>72.86264038085938</v>
       </c>
       <c r="C120" t="n">
         <v>105.9599990844727</v>
@@ -3431,11 +3443,11 @@
       </c>
     </row>
     <row r="121">
-      <c r="A121" s="1" t="n">
+      <c r="A121" s="2" t="n">
         <v>42369</v>
       </c>
       <c r="B121" t="n">
-        <v>69.88300323486328</v>
+        <v>69.88301849365234</v>
       </c>
       <c r="C121" t="n">
         <v>101.1900024414062</v>
@@ -3460,11 +3472,11 @@
       </c>
     </row>
     <row r="122">
-      <c r="A122" s="1" t="n">
+      <c r="A122" s="2" t="n">
         <v>42400</v>
       </c>
       <c r="B122" t="n">
-        <v>57.32077789306641</v>
+        <v>57.32080078125</v>
       </c>
       <c r="C122" t="n">
         <v>83</v>
@@ -3489,11 +3501,11 @@
       </c>
     </row>
     <row r="123">
-      <c r="A123" s="1" t="n">
+      <c r="A123" s="2" t="n">
         <v>42429</v>
       </c>
       <c r="B123" t="n">
-        <v>60.25589752197266</v>
+        <v>60.25587844848633</v>
       </c>
       <c r="C123" t="n">
         <v>87.25</v>
@@ -3518,11 +3530,11 @@
       </c>
     </row>
     <row r="124">
-      <c r="A124" s="1" t="n">
+      <c r="A124" s="2" t="n">
         <v>42460</v>
       </c>
       <c r="B124" t="n">
-        <v>63.74534225463867</v>
+        <v>63.74536514282227</v>
       </c>
       <c r="C124" t="n">
         <v>91.86000061035156</v>
@@ -3547,11 +3559,11 @@
       </c>
     </row>
     <row r="125">
-      <c r="A125" s="1" t="n">
+      <c r="A125" s="2" t="n">
         <v>42490</v>
       </c>
       <c r="B125" t="n">
-        <v>61.21247100830078</v>
+        <v>61.21249008178711</v>
       </c>
       <c r="C125" t="n">
         <v>88.20999908447266</v>
@@ -3576,11 +3588,11 @@
       </c>
     </row>
     <row r="126">
-      <c r="A126" s="1" t="n">
+      <c r="A126" s="2" t="n">
         <v>42521</v>
       </c>
       <c r="B126" t="n">
-        <v>60.41444396972656</v>
+        <v>60.41443634033203</v>
       </c>
       <c r="C126" t="n">
         <v>87.05999755859375</v>
@@ -3605,11 +3617,11 @@
       </c>
     </row>
     <row r="127">
-      <c r="A127" s="1" t="n">
+      <c r="A127" s="2" t="n">
         <v>42551</v>
       </c>
       <c r="B127" t="n">
-        <v>58.21431732177734</v>
+        <v>58.21429443359375</v>
       </c>
       <c r="C127" t="n">
         <v>83.41999816894531</v>
@@ -3634,11 +3646,11 @@
       </c>
     </row>
     <row r="128">
-      <c r="A128" s="1" t="n">
+      <c r="A128" s="2" t="n">
         <v>42582</v>
       </c>
       <c r="B128" t="n">
-        <v>55.45780181884766</v>
+        <v>55.45781326293945</v>
       </c>
       <c r="C128" t="n">
         <v>79.47000122070312</v>
@@ -3663,11 +3675,11 @@
       </c>
     </row>
     <row r="129">
-      <c r="A129" s="1" t="n">
+      <c r="A129" s="2" t="n">
         <v>42613</v>
       </c>
       <c r="B129" t="n">
-        <v>54.69715881347656</v>
+        <v>54.6971549987793</v>
       </c>
       <c r="C129" t="n">
         <v>78.37999725341797</v>
@@ -3692,11 +3704,11 @@
       </c>
     </row>
     <row r="130">
-      <c r="A130" s="1" t="n">
+      <c r="A130" s="2" t="n">
         <v>42643</v>
       </c>
       <c r="B130" t="n">
-        <v>55.54800796508789</v>
+        <v>55.54803848266602</v>
       </c>
       <c r="C130" t="n">
         <v>79.12000274658203</v>
@@ -3721,11 +3733,11 @@
       </c>
     </row>
     <row r="131">
-      <c r="A131" s="1" t="n">
+      <c r="A131" s="2" t="n">
         <v>42674</v>
       </c>
       <c r="B131" t="n">
-        <v>51.69364166259766</v>
+        <v>51.69363784790039</v>
       </c>
       <c r="C131" t="n">
         <v>73.62999725341797</v>
@@ -3750,7 +3762,7 @@
       </c>
     </row>
     <row r="132">
-      <c r="A132" s="1" t="n">
+      <c r="A132" s="2" t="n">
         <v>42704</v>
       </c>
       <c r="B132" t="n">
@@ -3779,11 +3791,11 @@
       </c>
     </row>
     <row r="133">
-      <c r="A133" s="1" t="n">
+      <c r="A133" s="2" t="n">
         <v>42735</v>
       </c>
       <c r="B133" t="n">
-        <v>50.59914779663086</v>
+        <v>50.59915161132812</v>
       </c>
       <c r="C133" t="n">
         <v>71.61000061035156</v>
@@ -3808,7 +3820,7 @@
       </c>
     </row>
     <row r="134">
-      <c r="A134" s="1" t="n">
+      <c r="A134" s="2" t="n">
         <v>42766</v>
       </c>
       <c r="B134" t="n">
@@ -3837,11 +3849,11 @@
       </c>
     </row>
     <row r="135">
-      <c r="A135" s="1" t="n">
+      <c r="A135" s="2" t="n">
         <v>42794</v>
       </c>
       <c r="B135" t="n">
-        <v>49.80069732666016</v>
+        <v>49.80068969726562</v>
       </c>
       <c r="C135" t="n">
         <v>70.48000335693359</v>
@@ -3866,11 +3878,11 @@
       </c>
     </row>
     <row r="136">
-      <c r="A136" s="1" t="n">
+      <c r="A136" s="2" t="n">
         <v>42825</v>
       </c>
       <c r="B136" t="n">
-        <v>48.36107635498047</v>
+        <v>48.361083984375</v>
       </c>
       <c r="C136" t="n">
         <v>67.91999816894531</v>
@@ -3895,7 +3907,7 @@
       </c>
     </row>
     <row r="137">
-      <c r="A137" s="1" t="n">
+      <c r="A137" s="2" t="n">
         <v>42855</v>
       </c>
       <c r="B137" t="n">
@@ -3924,11 +3936,11 @@
       </c>
     </row>
     <row r="138">
-      <c r="A138" s="1" t="n">
+      <c r="A138" s="2" t="n">
         <v>42886</v>
       </c>
       <c r="B138" t="n">
-        <v>46.20365142822266</v>
+        <v>46.20363235473633</v>
       </c>
       <c r="C138" t="n">
         <v>64.88999938964844</v>
@@ -3953,7 +3965,7 @@
       </c>
     </row>
     <row r="139">
-      <c r="A139" s="1" t="n">
+      <c r="A139" s="2" t="n">
         <v>42916</v>
       </c>
       <c r="B139" t="n">
@@ -3982,11 +3994,11 @@
       </c>
     </row>
     <row r="140">
-      <c r="A140" s="1" t="n">
+      <c r="A140" s="2" t="n">
         <v>42947</v>
       </c>
       <c r="B140" t="n">
-        <v>54.61428833007812</v>
+        <v>54.61430358886719</v>
       </c>
       <c r="C140" t="n">
         <v>76.08999633789062</v>
@@ -4011,11 +4023,11 @@
       </c>
     </row>
     <row r="141">
-      <c r="A141" s="1" t="n">
+      <c r="A141" s="2" t="n">
         <v>42978</v>
       </c>
       <c r="B141" t="n">
-        <v>60.08360290527344</v>
+        <v>60.08361053466797</v>
       </c>
       <c r="C141" t="n">
         <v>83.70999908447266</v>
@@ -4040,11 +4052,11 @@
       </c>
     </row>
     <row r="142">
-      <c r="A142" s="1" t="n">
+      <c r="A142" s="2" t="n">
         <v>43008</v>
       </c>
       <c r="B142" t="n">
-        <v>58.5164680480957</v>
+        <v>58.5164794921875</v>
       </c>
       <c r="C142" t="n">
         <v>81.01999664306641</v>
@@ -4069,7 +4081,7 @@
       </c>
     </row>
     <row r="143">
-      <c r="A143" s="1" t="n">
+      <c r="A143" s="2" t="n">
         <v>43039</v>
       </c>
       <c r="B143" t="n">
@@ -4098,11 +4110,11 @@
       </c>
     </row>
     <row r="144">
-      <c r="A144" s="1" t="n">
+      <c r="A144" s="2" t="n">
         <v>43069</v>
       </c>
       <c r="B144" t="n">
-        <v>54.00963973999023</v>
+        <v>54.0096435546875</v>
       </c>
       <c r="C144" t="n">
         <v>74.77999877929688</v>
@@ -4127,11 +4139,11 @@
       </c>
     </row>
     <row r="145">
-      <c r="A145" s="1" t="n">
+      <c r="A145" s="2" t="n">
         <v>43100</v>
       </c>
       <c r="B145" t="n">
-        <v>52.09552764892578</v>
+        <v>52.09553909301758</v>
       </c>
       <c r="C145" t="n">
         <v>71.63999938964844</v>
@@ -4156,11 +4168,11 @@
       </c>
     </row>
     <row r="146">
-      <c r="A146" s="1" t="n">
+      <c r="A146" s="2" t="n">
         <v>43131</v>
       </c>
       <c r="B146" t="n">
-        <v>60.93811798095703</v>
+        <v>60.93810653686523</v>
       </c>
       <c r="C146" t="n">
         <v>83.80000305175781</v>
@@ -4185,11 +4197,11 @@
       </c>
     </row>
     <row r="147">
-      <c r="A147" s="1" t="n">
+      <c r="A147" s="2" t="n">
         <v>43159</v>
       </c>
       <c r="B147" t="n">
-        <v>57.25127410888672</v>
+        <v>57.25125885009766</v>
       </c>
       <c r="C147" t="n">
         <v>78.73000335693359</v>
@@ -4214,7 +4226,7 @@
       </c>
     </row>
     <row r="148">
-      <c r="A148" s="1" t="n">
+      <c r="A148" s="2" t="n">
         <v>43190</v>
       </c>
       <c r="B148" t="n">
@@ -4243,11 +4255,11 @@
       </c>
     </row>
     <row r="149">
-      <c r="A149" s="1" t="n">
+      <c r="A149" s="2" t="n">
         <v>43220</v>
       </c>
       <c r="B149" t="n">
-        <v>52.89635467529297</v>
+        <v>52.89634704589844</v>
       </c>
       <c r="C149" t="n">
         <v>72.23000335693359</v>
@@ -4272,7 +4284,7 @@
       </c>
     </row>
     <row r="150">
-      <c r="A150" s="1" t="n">
+      <c r="A150" s="2" t="n">
         <v>43251</v>
       </c>
       <c r="B150" t="n">
@@ -4301,11 +4313,11 @@
       </c>
     </row>
     <row r="151">
-      <c r="A151" s="1" t="n">
+      <c r="A151" s="2" t="n">
         <v>43281</v>
       </c>
       <c r="B151" t="n">
-        <v>52.29652404785156</v>
+        <v>52.29653549194336</v>
       </c>
       <c r="C151" t="n">
         <v>70.83999633789062</v>
@@ -4330,11 +4342,11 @@
       </c>
     </row>
     <row r="152">
-      <c r="A152" s="1" t="n">
+      <c r="A152" s="2" t="n">
         <v>43312</v>
       </c>
       <c r="B152" t="n">
-        <v>57.45680236816406</v>
+        <v>57.45680999755859</v>
       </c>
       <c r="C152" t="n">
         <v>77.83000183105469</v>
@@ -4359,7 +4371,7 @@
       </c>
     </row>
     <row r="153">
-      <c r="A153" s="1" t="n">
+      <c r="A153" s="2" t="n">
         <v>43343</v>
       </c>
       <c r="B153" t="n">
@@ -4388,11 +4400,11 @@
       </c>
     </row>
     <row r="154">
-      <c r="A154" s="1" t="n">
+      <c r="A154" s="2" t="n">
         <v>43373</v>
       </c>
       <c r="B154" t="n">
-        <v>57.44173812866211</v>
+        <v>57.44172668457031</v>
       </c>
       <c r="C154" t="n">
         <v>77.20999908447266</v>
@@ -4417,7 +4429,7 @@
       </c>
     </row>
     <row r="155">
-      <c r="A155" s="1" t="n">
+      <c r="A155" s="2" t="n">
         <v>43404</v>
       </c>
       <c r="B155" t="n">
@@ -4446,11 +4458,11 @@
       </c>
     </row>
     <row r="156">
-      <c r="A156" s="1" t="n">
+      <c r="A156" s="2" t="n">
         <v>43434</v>
       </c>
       <c r="B156" t="n">
-        <v>53.52102279663086</v>
+        <v>53.52101898193359</v>
       </c>
       <c r="C156" t="n">
         <v>71.94000244140625</v>
@@ -4475,11 +4487,11 @@
       </c>
     </row>
     <row r="157">
-      <c r="A157" s="1" t="n">
+      <c r="A157" s="2" t="n">
         <v>43465</v>
       </c>
       <c r="B157" t="n">
-        <v>46.92771911621094</v>
+        <v>46.92771148681641</v>
       </c>
       <c r="C157" t="n">
         <v>62.54999923706055</v>
@@ -4504,11 +4516,11 @@
       </c>
     </row>
     <row r="158">
-      <c r="A158" s="1" t="n">
+      <c r="A158" s="2" t="n">
         <v>43496</v>
       </c>
       <c r="B158" t="n">
-        <v>52.52455139160156</v>
+        <v>52.52453994750977</v>
       </c>
       <c r="C158" t="n">
         <v>70.01000213623047</v>
@@ -4533,11 +4545,11 @@
       </c>
     </row>
     <row r="159">
-      <c r="A159" s="1" t="n">
+      <c r="A159" s="2" t="n">
         <v>43524</v>
       </c>
       <c r="B159" t="n">
-        <v>48.78083038330078</v>
+        <v>48.78081512451172</v>
       </c>
       <c r="C159" t="n">
         <v>65.01999664306641</v>
@@ -4562,11 +4574,11 @@
       </c>
     </row>
     <row r="160">
-      <c r="A160" s="1" t="n">
+      <c r="A160" s="2" t="n">
         <v>43555</v>
       </c>
       <c r="B160" t="n">
-        <v>49.24518203735352</v>
+        <v>49.24517440795898</v>
       </c>
       <c r="C160" t="n">
         <v>65.01000213623047</v>
@@ -4591,7 +4603,7 @@
       </c>
     </row>
     <row r="161">
-      <c r="A161" s="1" t="n">
+      <c r="A161" s="2" t="n">
         <v>43585</v>
       </c>
       <c r="B161" t="n">
@@ -4620,11 +4632,11 @@
       </c>
     </row>
     <row r="162">
-      <c r="A162" s="1" t="n">
+      <c r="A162" s="2" t="n">
         <v>43616</v>
       </c>
       <c r="B162" t="n">
-        <v>47.15447235107422</v>
+        <v>47.15446853637695</v>
       </c>
       <c r="C162" t="n">
         <v>62.25</v>
@@ -4649,11 +4661,11 @@
       </c>
     </row>
     <row r="163">
-      <c r="A163" s="1" t="n">
+      <c r="A163" s="2" t="n">
         <v>43646</v>
       </c>
       <c r="B163" t="n">
-        <v>51.66420364379883</v>
+        <v>51.66420745849609</v>
       </c>
       <c r="C163" t="n">
         <v>67.55999755859375</v>
@@ -4678,11 +4690,11 @@
       </c>
     </row>
     <row r="164">
-      <c r="A164" s="1" t="n">
+      <c r="A164" s="2" t="n">
         <v>43677</v>
       </c>
       <c r="B164" t="n">
-        <v>50.10418319702148</v>
+        <v>50.10417938232422</v>
       </c>
       <c r="C164" t="n">
         <v>65.51999664306641</v>
@@ -4707,11 +4719,11 @@
       </c>
     </row>
     <row r="165">
-      <c r="A165" s="1" t="n">
+      <c r="A165" s="2" t="n">
         <v>43708</v>
       </c>
       <c r="B165" t="n">
-        <v>48.59004974365234</v>
+        <v>48.59005355834961</v>
       </c>
       <c r="C165" t="n">
         <v>63.54000091552734</v>
@@ -4736,11 +4748,11 @@
       </c>
     </row>
     <row r="166">
-      <c r="A166" s="1" t="n">
+      <c r="A166" s="2" t="n">
         <v>43738</v>
       </c>
       <c r="B166" t="n">
-        <v>48.92038726806641</v>
+        <v>48.92039108276367</v>
       </c>
       <c r="C166" t="n">
         <v>63.38000106811523</v>
@@ -4765,11 +4777,11 @@
       </c>
     </row>
     <row r="167">
-      <c r="A167" s="1" t="n">
+      <c r="A167" s="2" t="n">
         <v>43769</v>
       </c>
       <c r="B167" t="n">
-        <v>49.17511749267578</v>
+        <v>49.17510223388672</v>
       </c>
       <c r="C167" t="n">
         <v>63.70999908447266</v>
@@ -4794,11 +4806,11 @@
       </c>
     </row>
     <row r="168">
-      <c r="A168" s="1" t="n">
+      <c r="A168" s="2" t="n">
         <v>43799</v>
       </c>
       <c r="B168" t="n">
-        <v>51.89976119995117</v>
+        <v>51.89977645874023</v>
       </c>
       <c r="C168" t="n">
         <v>67.23999786376953</v>
@@ -4823,11 +4835,11 @@
       </c>
     </row>
     <row r="169">
-      <c r="A169" s="1" t="n">
+      <c r="A169" s="2" t="n">
         <v>43830</v>
       </c>
       <c r="B169" t="n">
-        <v>50.62592697143555</v>
+        <v>50.62593078613281</v>
       </c>
       <c r="C169" t="n">
         <v>64.98000335693359</v>
@@ -4852,11 +4864,11 @@
       </c>
     </row>
     <row r="170">
-      <c r="A170" s="1" t="n">
+      <c r="A170" s="2" t="n">
         <v>43861</v>
       </c>
       <c r="B170" t="n">
-        <v>49.2391242980957</v>
+        <v>49.23913192749023</v>
       </c>
       <c r="C170" t="n">
         <v>63.20000076293945</v>
@@ -4881,7 +4893,7 @@
       </c>
     </row>
     <row r="171">
-      <c r="A171" s="1" t="n">
+      <c r="A171" s="2" t="n">
         <v>43890</v>
       </c>
       <c r="B171" t="n">
@@ -4910,11 +4922,11 @@
       </c>
     </row>
     <row r="172">
-      <c r="A172" s="1" t="n">
+      <c r="A172" s="2" t="n">
         <v>43921</v>
       </c>
       <c r="B172" t="n">
-        <v>58.78792572021484</v>
+        <v>58.78792953491211</v>
       </c>
       <c r="C172" t="n">
         <v>74.76000213623047</v>
@@ -4939,11 +4951,11 @@
       </c>
     </row>
     <row r="173">
-      <c r="A173" s="1" t="n">
+      <c r="A173" s="2" t="n">
         <v>43951</v>
       </c>
       <c r="B173" t="n">
-        <v>66.05384826660156</v>
+        <v>66.05385589599609</v>
       </c>
       <c r="C173" t="n">
         <v>84</v>
@@ -4968,11 +4980,11 @@
       </c>
     </row>
     <row r="174">
-      <c r="A174" s="1" t="n">
+      <c r="A174" s="2" t="n">
         <v>43982</v>
       </c>
       <c r="B174" t="n">
-        <v>61.20204544067383</v>
+        <v>61.2020378112793</v>
       </c>
       <c r="C174" t="n">
         <v>77.83000183105469</v>
@@ -4997,11 +5009,11 @@
       </c>
     </row>
     <row r="175">
-      <c r="A175" s="1" t="n">
+      <c r="A175" s="2" t="n">
         <v>44012</v>
       </c>
       <c r="B175" t="n">
-        <v>61.040771484375</v>
+        <v>61.04076385498047</v>
       </c>
       <c r="C175" t="n">
         <v>76.94000244140625</v>
@@ -5026,7 +5038,7 @@
       </c>
     </row>
     <row r="176">
-      <c r="A176" s="1" t="n">
+      <c r="A176" s="2" t="n">
         <v>44043</v>
       </c>
       <c r="B176" t="n">
@@ -5055,11 +5067,11 @@
       </c>
     </row>
     <row r="177">
-      <c r="A177" s="1" t="n">
+      <c r="A177" s="2" t="n">
         <v>44074</v>
       </c>
       <c r="B177" t="n">
-        <v>52.95647048950195</v>
+        <v>52.95645904541016</v>
       </c>
       <c r="C177" t="n">
         <v>66.75</v>
@@ -5082,11 +5094,11 @@
       </c>
     </row>
     <row r="178">
-      <c r="A178" s="1" t="n">
+      <c r="A178" s="2" t="n">
         <v>44104</v>
       </c>
       <c r="B178" t="n">
-        <v>50.65738296508789</v>
+        <v>50.65739440917969</v>
       </c>
       <c r="C178" t="n">
         <v>63.18999862670898</v>
@@ -5109,7 +5121,7 @@
       </c>
     </row>
     <row r="179">
-      <c r="A179" s="1" t="n">
+      <c r="A179" s="2" t="n">
         <v>44135</v>
       </c>
       <c r="B179" t="n">
@@ -5136,11 +5148,11 @@
       </c>
     </row>
     <row r="180">
-      <c r="A180" s="1" t="n">
+      <c r="A180" s="2" t="n">
         <v>44165</v>
       </c>
       <c r="B180" t="n">
-        <v>48.63719177246094</v>
+        <v>48.63718032836914</v>
       </c>
       <c r="C180" t="n">
         <v>60.66999816894531</v>
@@ -5165,11 +5177,11 @@
       </c>
     </row>
     <row r="181">
-      <c r="A181" s="1" t="n">
+      <c r="A181" s="2" t="n">
         <v>44196</v>
       </c>
       <c r="B181" t="n">
-        <v>47.23378372192383</v>
+        <v>47.23379135131836</v>
       </c>
       <c r="C181" t="n">
         <v>58.2599983215332</v>
@@ -5194,11 +5206,11 @@
       </c>
     </row>
     <row r="182">
-      <c r="A182" s="1" t="n">
+      <c r="A182" s="2" t="n">
         <v>44227</v>
       </c>
       <c r="B182" t="n">
-        <v>53.18463134765625</v>
+        <v>53.18463516235352</v>
       </c>
       <c r="C182" t="n">
         <v>65.59999847412109</v>
@@ -5223,11 +5235,11 @@
       </c>
     </row>
     <row r="183">
-      <c r="A183" s="1" t="n">
+      <c r="A183" s="2" t="n">
         <v>44255</v>
       </c>
       <c r="B183" t="n">
-        <v>49.77951431274414</v>
+        <v>49.77952194213867</v>
       </c>
       <c r="C183" t="n">
         <v>61.40000152587891</v>
@@ -5252,11 +5264,11 @@
       </c>
     </row>
     <row r="184">
-      <c r="A184" s="1" t="n">
+      <c r="A184" s="2" t="n">
         <v>44286</v>
       </c>
       <c r="B184" t="n">
-        <v>52.99460601806641</v>
+        <v>52.99459838867188</v>
       </c>
       <c r="C184" t="n">
         <v>64.62999725341797</v>
@@ -5281,11 +5293,11 @@
       </c>
     </row>
     <row r="185">
-      <c r="A185" s="1" t="n">
+      <c r="A185" s="2" t="n">
         <v>44316</v>
       </c>
       <c r="B185" t="n">
-        <v>52.04343795776367</v>
+        <v>52.04343414306641</v>
       </c>
       <c r="C185" t="n">
         <v>63.47000122070312</v>
@@ -5310,11 +5322,11 @@
       </c>
     </row>
     <row r="186">
-      <c r="A186" s="1" t="n">
+      <c r="A186" s="2" t="n">
         <v>44347</v>
       </c>
       <c r="B186" t="n">
-        <v>54.20816421508789</v>
+        <v>54.20816802978516</v>
       </c>
       <c r="C186" t="n">
         <v>66.11000061035156</v>
@@ -5339,11 +5351,11 @@
       </c>
     </row>
     <row r="187">
-      <c r="A187" s="1" t="n">
+      <c r="A187" s="2" t="n">
         <v>44377</v>
       </c>
       <c r="B187" t="n">
-        <v>57.05209350585938</v>
+        <v>57.05208969116211</v>
       </c>
       <c r="C187" t="n">
         <v>68.86000061035156</v>
@@ -5368,11 +5380,11 @@
       </c>
     </row>
     <row r="188">
-      <c r="A188" s="1" t="n">
+      <c r="A188" s="2" t="n">
         <v>44408</v>
       </c>
       <c r="B188" t="n">
-        <v>56.57983016967773</v>
+        <v>56.579833984375</v>
       </c>
       <c r="C188" t="n">
         <v>68.29000091552734</v>
@@ -5397,11 +5409,11 @@
       </c>
     </row>
     <row r="189">
-      <c r="A189" s="1" t="n">
+      <c r="A189" s="2" t="n">
         <v>44439</v>
       </c>
       <c r="B189" t="n">
-        <v>60.29990005493164</v>
+        <v>60.29988098144531</v>
       </c>
       <c r="C189" t="n">
         <v>72.77999877929688</v>
@@ -5426,11 +5438,11 @@
       </c>
     </row>
     <row r="190">
-      <c r="A190" s="1" t="n">
+      <c r="A190" s="2" t="n">
         <v>44469</v>
       </c>
       <c r="B190" t="n">
-        <v>58.45564270019531</v>
+        <v>58.45565032958984</v>
       </c>
       <c r="C190" t="n">
         <v>69.84999847412109</v>
@@ -5455,11 +5467,11 @@
       </c>
     </row>
     <row r="191">
-      <c r="A191" s="1" t="n">
+      <c r="A191" s="2" t="n">
         <v>44500</v>
       </c>
       <c r="B191" t="n">
-        <v>54.29638671875</v>
+        <v>54.29639053344727</v>
       </c>
       <c r="C191" t="n">
         <v>64.87999725341797</v>
@@ -5484,11 +5496,11 @@
       </c>
     </row>
     <row r="192">
-      <c r="A192" s="1" t="n">
+      <c r="A192" s="2" t="n">
         <v>44530</v>
       </c>
       <c r="B192" t="n">
-        <v>57.68572616577148</v>
+        <v>57.68571853637695</v>
       </c>
       <c r="C192" t="n">
         <v>68.93000030517578</v>
@@ -5513,11 +5525,11 @@
       </c>
     </row>
     <row r="193">
-      <c r="A193" s="1" t="n">
+      <c r="A193" s="2" t="n">
         <v>44561</v>
       </c>
       <c r="B193" t="n">
-        <v>61.38265609741211</v>
+        <v>61.38264465332031</v>
       </c>
       <c r="C193" t="n">
         <v>72.61000061035156</v>
@@ -5542,11 +5554,11 @@
       </c>
     </row>
     <row r="194">
-      <c r="A194" s="1" t="n">
+      <c r="A194" s="2" t="n">
         <v>44592</v>
       </c>
       <c r="B194" t="n">
-        <v>58.06032180786133</v>
+        <v>58.0603141784668</v>
       </c>
       <c r="C194" t="n">
         <v>68.68000030517578</v>
@@ -5571,7 +5583,7 @@
       </c>
     </row>
     <row r="195">
-      <c r="A195" s="1" t="n">
+      <c r="A195" s="2" t="n">
         <v>44620</v>
       </c>
       <c r="B195" t="n">
@@ -5600,11 +5612,11 @@
       </c>
     </row>
     <row r="196">
-      <c r="A196" s="1" t="n">
+      <c r="A196" s="2" t="n">
         <v>44651</v>
       </c>
       <c r="B196" t="n">
-        <v>50.89812850952148</v>
+        <v>50.89812469482422</v>
       </c>
       <c r="C196" t="n">
         <v>59.45000076293945</v>
@@ -5629,11 +5641,11 @@
       </c>
     </row>
     <row r="197">
-      <c r="A197" s="1" t="n">
+      <c r="A197" s="2" t="n">
         <v>44681</v>
       </c>
       <c r="B197" t="n">
-        <v>50.80395126342773</v>
+        <v>50.803955078125</v>
       </c>
       <c r="C197" t="n">
         <v>59.34000015258789</v>
@@ -5658,11 +5670,11 @@
       </c>
     </row>
     <row r="198">
-      <c r="A198" s="1" t="n">
+      <c r="A198" s="2" t="n">
         <v>44712</v>
       </c>
       <c r="B198" t="n">
-        <v>55.52133941650391</v>
+        <v>55.52133178710938</v>
       </c>
       <c r="C198" t="n">
         <v>64.84999847412109</v>
@@ -5687,11 +5699,11 @@
       </c>
     </row>
     <row r="199">
-      <c r="A199" s="1" t="n">
+      <c r="A199" s="2" t="n">
         <v>44742</v>
       </c>
       <c r="B199" t="n">
-        <v>53.57989501953125</v>
+        <v>53.57989883422852</v>
       </c>
       <c r="C199" t="n">
         <v>61.81000137329102</v>
@@ -5716,7 +5728,7 @@
       </c>
     </row>
     <row r="200">
-      <c r="A200" s="1" t="n">
+      <c r="A200" s="2" t="n">
         <v>44773</v>
       </c>
       <c r="B200" t="n">
@@ -5745,11 +5757,11 @@
       </c>
     </row>
     <row r="201">
-      <c r="A201" s="1" t="n">
+      <c r="A201" s="2" t="n">
         <v>44804</v>
       </c>
       <c r="B201" t="n">
-        <v>55.01886749267578</v>
+        <v>55.01887130737305</v>
       </c>
       <c r="C201" t="n">
         <v>63.47000122070312</v>
@@ -5774,11 +5786,11 @@
       </c>
     </row>
     <row r="202">
-      <c r="A202" s="1" t="n">
+      <c r="A202" s="2" t="n">
         <v>44834</v>
       </c>
       <c r="B202" t="n">
-        <v>54.08234024047852</v>
+        <v>54.08232879638672</v>
       </c>
       <c r="C202" t="n">
         <v>61.68999862670898</v>
@@ -5803,7 +5815,7 @@
       </c>
     </row>
     <row r="203">
-      <c r="A203" s="1" t="n">
+      <c r="A203" s="2" t="n">
         <v>44865</v>
       </c>
       <c r="B203" t="n">
@@ -5832,7 +5844,7 @@
       </c>
     </row>
     <row r="204">
-      <c r="A204" s="1" t="n">
+      <c r="A204" s="2" t="n">
         <v>44895</v>
       </c>
       <c r="B204" t="n">
@@ -5861,11 +5873,11 @@
       </c>
     </row>
     <row r="205">
-      <c r="A205" s="1" t="n">
+      <c r="A205" s="2" t="n">
         <v>44926</v>
       </c>
       <c r="B205" t="n">
-        <v>75.88711547851562</v>
+        <v>75.88709259033203</v>
       </c>
       <c r="C205" t="n">
         <v>85.84999847412109</v>
@@ -5890,7 +5902,7 @@
       </c>
     </row>
     <row r="206">
-      <c r="A206" s="1" t="n">
+      <c r="A206" s="2" t="n">
         <v>44957</v>
       </c>
       <c r="B206" t="n">
@@ -5919,11 +5931,11 @@
       </c>
     </row>
     <row r="207">
-      <c r="A207" s="1" t="n">
+      <c r="A207" s="2" t="n">
         <v>44985</v>
       </c>
       <c r="B207" t="n">
-        <v>71.18448638916016</v>
+        <v>71.18447113037109</v>
       </c>
       <c r="C207" t="n">
         <v>80.52999877929688</v>
@@ -5948,11 +5960,11 @@
       </c>
     </row>
     <row r="208">
-      <c r="A208" s="1" t="n">
+      <c r="A208" s="2" t="n">
         <v>45016</v>
       </c>
       <c r="B208" t="n">
-        <v>74.03974151611328</v>
+        <v>74.03971862792969</v>
       </c>
       <c r="C208" t="n">
         <v>82.97000122070312</v>
@@ -5977,11 +5989,11 @@
       </c>
     </row>
     <row r="209">
-      <c r="A209" s="1" t="n">
+      <c r="A209" s="2" t="n">
         <v>45046</v>
       </c>
       <c r="B209" t="n">
-        <v>73.36151123046875</v>
+        <v>73.36153411865234</v>
       </c>
       <c r="C209" t="n">
         <v>82.20999908447266</v>
@@ -6006,11 +6018,11 @@
       </c>
     </row>
     <row r="210">
-      <c r="A210" s="1" t="n">
+      <c r="A210" s="2" t="n">
         <v>45077</v>
       </c>
       <c r="B210" t="n">
-        <v>68.65874481201172</v>
+        <v>68.65875244140625</v>
       </c>
       <c r="C210" t="n">
         <v>76.94000244140625</v>
@@ -6035,11 +6047,11 @@
       </c>
     </row>
     <row r="211">
-      <c r="A211" s="1" t="n">
+      <c r="A211" s="2" t="n">
         <v>45107</v>
       </c>
       <c r="B211" t="n">
-        <v>69.4385986328125</v>
+        <v>69.43860626220703</v>
       </c>
       <c r="C211" t="n">
         <v>77.06999969482422</v>
@@ -6064,11 +6076,11 @@
       </c>
     </row>
     <row r="212">
-      <c r="A212" s="1" t="n">
+      <c r="A212" s="2" t="n">
         <v>45138</v>
       </c>
       <c r="B212" t="n">
-        <v>68.60069274902344</v>
+        <v>68.60070037841797</v>
       </c>
       <c r="C212" t="n">
         <v>76.13999938964844</v>
@@ -6093,11 +6105,11 @@
       </c>
     </row>
     <row r="213">
-      <c r="A213" s="1" t="n">
+      <c r="A213" s="2" t="n">
         <v>45169</v>
       </c>
       <c r="B213" t="n">
-        <v>68.90703582763672</v>
+        <v>68.90702819824219</v>
       </c>
       <c r="C213" t="n">
         <v>76.48000335693359</v>
@@ -6122,11 +6134,11 @@
       </c>
     </row>
     <row r="214">
-      <c r="A214" s="1" t="n">
+      <c r="A214" s="2" t="n">
         <v>45199</v>
       </c>
       <c r="B214" t="n">
-        <v>68.18096160888672</v>
+        <v>68.18095397949219</v>
       </c>
       <c r="C214" t="n">
         <v>74.94000244140625</v>
@@ -6151,7 +6163,7 @@
       </c>
     </row>
     <row r="215">
-      <c r="A215" s="1" t="n">
+      <c r="A215" s="2" t="n">
         <v>45230</v>
       </c>
       <c r="B215" t="n">
@@ -6180,11 +6192,11 @@
       </c>
     </row>
     <row r="216">
-      <c r="A216" s="1" t="n">
+      <c r="A216" s="2" t="n">
         <v>45260</v>
       </c>
       <c r="B216" t="n">
-        <v>69.69123840332031</v>
+        <v>69.69123077392578</v>
       </c>
       <c r="C216" t="n">
         <v>76.59999847412109</v>
@@ -6209,7 +6221,7 @@
       </c>
     </row>
     <row r="217">
-      <c r="A217" s="1" t="n">
+      <c r="A217" s="2" t="n">
         <v>45291</v>
       </c>
       <c r="B217" t="n">
@@ -6238,7 +6250,7 @@
       </c>
     </row>
     <row r="218">
-      <c r="A218" s="1" t="n">
+      <c r="A218" s="2" t="n">
         <v>45322</v>
       </c>
       <c r="B218" t="n">
@@ -6267,7 +6279,7 @@
       </c>
     </row>
     <row r="219">
-      <c r="A219" s="1" t="n">
+      <c r="A219" s="2" t="n">
         <v>45351</v>
       </c>
       <c r="B219" t="n">
@@ -6296,11 +6308,11 @@
       </c>
     </row>
     <row r="220">
-      <c r="A220" s="1" t="n">
+      <c r="A220" s="2" t="n">
         <v>45382</v>
       </c>
       <c r="B220" t="n">
-        <v>67.93928527832031</v>
+        <v>67.93927764892578</v>
       </c>
       <c r="C220" t="n">
         <v>73.25</v>
@@ -6325,7 +6337,7 @@
       </c>
     </row>
     <row r="221">
-      <c r="A221" s="1" t="n">
+      <c r="A221" s="2" t="n">
         <v>45412</v>
       </c>
       <c r="B221" t="n">
@@ -6354,11 +6366,11 @@
       </c>
     </row>
     <row r="222">
-      <c r="A222" s="1" t="n">
+      <c r="A222" s="2" t="n">
         <v>45443</v>
       </c>
       <c r="B222" t="n">
-        <v>59.6103401184082</v>
+        <v>59.61034774780273</v>
       </c>
       <c r="C222" t="n">
         <v>64.26999664306641</v>
@@ -6383,11 +6395,11 @@
       </c>
     </row>
     <row r="223">
-      <c r="A223" s="1" t="n">
+      <c r="A223" s="2" t="n">
         <v>45473</v>
       </c>
       <c r="B223" t="n">
-        <v>64.41604614257812</v>
+        <v>64.41606140136719</v>
       </c>
       <c r="C223" t="n">
         <v>68.61000061035156</v>
@@ -6412,11 +6424,11 @@
       </c>
     </row>
     <row r="224">
-      <c r="A224" s="1" t="n">
+      <c r="A224" s="2" t="n">
         <v>45504</v>
       </c>
       <c r="B224" t="n">
-        <v>71.41065979003906</v>
+        <v>71.41065216064453</v>
       </c>
       <c r="C224" t="n">
         <v>76.05999755859375</v>
@@ -6441,7 +6453,7 @@
       </c>
     </row>
     <row r="225">
-      <c r="A225" s="1" t="n">
+      <c r="A225" s="2" t="n">
         <v>45535</v>
       </c>
       <c r="B225" t="n">
@@ -6470,11 +6482,11 @@
       </c>
     </row>
     <row r="226">
-      <c r="A226" s="1" t="n">
+      <c r="A226" s="2" t="n">
         <v>45565</v>
       </c>
       <c r="B226" t="n">
-        <v>79.45075225830078</v>
+        <v>79.45074462890625</v>
       </c>
       <c r="C226" t="n">
         <v>83.83999633789062</v>
@@ -6499,11 +6511,11 @@
       </c>
     </row>
     <row r="227">
-      <c r="A227" s="1" t="n">
+      <c r="A227" s="2" t="n">
         <v>45596</v>
       </c>
       <c r="B227" t="n">
-        <v>84.17002868652344</v>
+        <v>84.17002105712891</v>
       </c>
       <c r="C227" t="n">
         <v>88.81999969482422</v>
@@ -6528,11 +6540,11 @@
       </c>
     </row>
     <row r="228">
-      <c r="A228" s="1" t="n">
+      <c r="A228" s="2" t="n">
         <v>45626</v>
       </c>
       <c r="B228" t="n">
-        <v>87.73316955566406</v>
+        <v>87.73317718505859</v>
       </c>
       <c r="C228" t="n">
         <v>92.58000183105469</v>
@@ -6557,7 +6569,7 @@
       </c>
     </row>
     <row r="229">
-      <c r="A229" s="1" t="n">
+      <c r="A229" s="2" t="n">
         <v>45657</v>
       </c>
       <c r="B229" t="n">
@@ -6586,11 +6598,11 @@
       </c>
     </row>
     <row r="230">
-      <c r="A230" s="1" t="n">
+      <c r="A230" s="2" t="n">
         <v>45688</v>
       </c>
       <c r="B230" t="n">
-        <v>92.88552093505859</v>
+        <v>92.88551330566406</v>
       </c>
       <c r="C230" t="n">
         <v>97.19999694824219</v>
@@ -6615,11 +6627,11 @@
       </c>
     </row>
     <row r="231">
-      <c r="A231" s="1" t="n">
+      <c r="A231" s="2" t="n">
         <v>45716</v>
       </c>
       <c r="B231" t="n">
-        <v>109.2360534667969</v>
+        <v>109.2360458374023</v>
       </c>
       <c r="C231" t="n">
         <v>114.3099975585938</v>
@@ -6644,7 +6656,7 @@
       </c>
     </row>
     <row r="232">
-      <c r="A232" s="1" t="n">
+      <c r="A232" s="2" t="n">
         <v>45747</v>
       </c>
       <c r="B232" t="n">
@@ -6673,7 +6685,7 @@
       </c>
     </row>
     <row r="233">
-      <c r="A233" s="1" t="n">
+      <c r="A233" s="2" t="n">
         <v>45777</v>
       </c>
       <c r="B233" t="n">
@@ -6702,7 +6714,7 @@
       </c>
     </row>
     <row r="234">
-      <c r="A234" s="1" t="n">
+      <c r="A234" s="2" t="n">
         <v>45808</v>
       </c>
       <c r="B234" t="n">
@@ -6731,7 +6743,7 @@
       </c>
     </row>
     <row r="235">
-      <c r="A235" s="1" t="n">
+      <c r="A235" s="2" t="n">
         <v>45838</v>
       </c>
       <c r="B235" t="n">
@@ -6760,7 +6772,7 @@
       </c>
     </row>
     <row r="236">
-      <c r="A236" s="1" t="n">
+      <c r="A236" s="2" t="n">
         <v>45869</v>
       </c>
       <c r="B236" t="n">
@@ -6789,11 +6801,11 @@
       </c>
     </row>
     <row r="237">
-      <c r="A237" s="1" t="n">
+      <c r="A237" s="2" t="n">
         <v>45900</v>
       </c>
       <c r="B237" t="n">
-        <v>109.4851226806641</v>
+        <v>109.4851303100586</v>
       </c>
       <c r="C237" t="n">
         <v>112.9700012207031</v>
@@ -6818,7 +6830,7 @@
       </c>
     </row>
     <row r="238">
-      <c r="A238" s="1" t="n">
+      <c r="A238" s="2" t="n">
         <v>45930</v>
       </c>
       <c r="B238" t="n">
@@ -6847,7 +6859,7 @@
       </c>
     </row>
     <row r="239">
-      <c r="A239" s="1" t="n">
+      <c r="A239" s="2" t="n">
         <v>45961</v>
       </c>
       <c r="B239" t="n">
@@ -6876,7 +6888,7 @@
       </c>
     </row>
     <row r="240">
-      <c r="A240" s="1" t="n">
+      <c r="A240" s="2" t="n">
         <v>45991</v>
       </c>
       <c r="B240" t="n">
@@ -6905,11 +6917,11 @@
       </c>
     </row>
     <row r="241">
-      <c r="A241" s="1" t="n">
+      <c r="A241" s="2" t="n">
         <v>46022</v>
       </c>
       <c r="B241" t="n">
-        <v>120.570930480957</v>
+        <v>120.5709228515625</v>
       </c>
       <c r="C241" t="n">
         <v>122.7399978637695</v>
@@ -6934,7 +6946,7 @@
       </c>
     </row>
     <row r="242">
-      <c r="A242" s="1" t="n">
+      <c r="A242" s="2" t="n">
         <v>46053</v>
       </c>
       <c r="B242" t="n">
@@ -6963,11 +6975,11 @@
       </c>
     </row>
     <row r="243">
-      <c r="A243" s="1" t="n">
+      <c r="A243" s="2" t="n">
         <v>46081</v>
       </c>
       <c r="B243" t="n">
-        <v>146.3177337646484</v>
+        <v>146.3177490234375</v>
       </c>
       <c r="C243" t="n">
         <v>148.9499969482422</v>
@@ -6992,7 +7004,7 @@
       </c>
     </row>
     <row r="244">
-      <c r="A244" s="1" t="n">
+      <c r="A244" s="2" t="n">
         <v>46112</v>
       </c>
       <c r="B244" t="n">
@@ -7021,7 +7033,7 @@
       </c>
     </row>
     <row r="245">
-      <c r="A245" s="1" t="n">
+      <c r="A245" s="2" t="n">
         <v>46142</v>
       </c>
       <c r="B245" t="n">
@@ -7050,7 +7062,7 @@
       </c>
     </row>
     <row r="246">
-      <c r="A246" s="1" t="n">
+      <c r="A246" s="2" t="n">
         <v>46173</v>
       </c>
       <c r="B246" t="n">
@@ -7079,7 +7091,7 @@
       </c>
     </row>
     <row r="247">
-      <c r="A247" s="1" t="n">
+      <c r="A247" s="2" t="n">
         <v>46203</v>
       </c>
       <c r="B247" t="n">
@@ -7108,7 +7120,7 @@
       </c>
     </row>
     <row r="248">
-      <c r="A248" s="1" t="n">
+      <c r="A248" s="2" t="n">
         <v>46234</v>
       </c>
       <c r="B248" t="n">
@@ -7137,7 +7149,7 @@
       </c>
     </row>
     <row r="249">
-      <c r="A249" s="1" t="n">
+      <c r="A249" s="2" t="n">
         <v>46265</v>
       </c>
       <c r="B249" t="n">
@@ -7164,17 +7176,17 @@
       </c>
     </row>
     <row r="250">
-      <c r="A250" s="1" t="n">
+      <c r="A250" s="2" t="n">
         <v>46295</v>
       </c>
       <c r="B250" t="n">
-        <v>151.3699951171875</v>
+        <v>149.6900024414062</v>
       </c>
       <c r="C250" t="n">
-        <v>151.3699951171875</v>
+        <v>149.6900024414062</v>
       </c>
       <c r="D250" t="n">
-        <v>97090200</v>
+        <v>102164900</v>
       </c>
       <c r="E250" t="n">
         <v>-2.66</v>
@@ -7184,10 +7196,10 @@
         <v>1239955155</v>
       </c>
       <c r="H250" t="n">
-        <v>187692005757.8815</v>
+        <v>185608890179.1843</v>
       </c>
       <c r="I250" t="n">
-        <v>0.07830138018176956</v>
+        <v>0.08239402819370512</v>
       </c>
     </row>
   </sheetData>
@@ -7219,75 +7231,75 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>start</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>end</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>filed</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>form</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>fy</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>fp</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>eps_trimestral</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>origen</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>eps_ttm</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>filed_ttm</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>factor</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>tag</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="1" t="n">
+      <c r="A2" s="2" t="n">
         <v>39539</v>
       </c>
-      <c r="B2" s="1" t="n">
+      <c r="B2" s="2" t="n">
         <v>39629</v>
       </c>
-      <c r="C2" s="1" t="n">
+      <c r="C2" s="2" t="n">
         <v>40030</v>
       </c>
       <c r="D2" t="inlineStr">
@@ -7323,13 +7335,13 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="1" t="n">
+      <c r="A3" s="2" t="n">
         <v>39630</v>
       </c>
-      <c r="B3" s="1" t="n">
+      <c r="B3" s="2" t="n">
         <v>39721</v>
       </c>
-      <c r="C3" s="1" t="n">
+      <c r="C3" s="2" t="n">
         <v>40122</v>
       </c>
       <c r="D3" t="inlineStr">
@@ -7365,13 +7377,13 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="1" t="n">
+      <c r="A4" s="2" t="n">
         <v>39814</v>
       </c>
-      <c r="B4" s="1" t="n">
+      <c r="B4" s="2" t="n">
         <v>39903</v>
       </c>
-      <c r="C4" s="1" t="n">
+      <c r="C4" s="2" t="n">
         <v>40308</v>
       </c>
       <c r="D4" t="inlineStr">
@@ -7407,13 +7419,13 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="1" t="n">
+      <c r="A5" s="2" t="n">
         <v>39904</v>
       </c>
-      <c r="B5" s="1" t="n">
+      <c r="B5" s="2" t="n">
         <v>39994</v>
       </c>
-      <c r="C5" s="1" t="n">
+      <c r="C5" s="2" t="n">
         <v>40030</v>
       </c>
       <c r="D5" t="inlineStr">
@@ -7449,13 +7461,13 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="1" t="n">
+      <c r="A6" s="2" t="n">
         <v>39995</v>
       </c>
-      <c r="B6" s="1" t="n">
+      <c r="B6" s="2" t="n">
         <v>40086</v>
       </c>
-      <c r="C6" s="1" t="n">
+      <c r="C6" s="2" t="n">
         <v>40122</v>
       </c>
       <c r="D6" t="inlineStr">
@@ -7491,13 +7503,13 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="1" t="n">
+      <c r="A7" s="2" t="n">
         <v>40087</v>
       </c>
-      <c r="B7" s="1" t="n">
+      <c r="B7" s="2" t="n">
         <v>40178</v>
       </c>
-      <c r="C7" s="1" t="n">
+      <c r="C7" s="2" t="n">
         <v>40602</v>
       </c>
       <c r="D7" t="inlineStr">
@@ -7524,7 +7536,7 @@
       <c r="I7" t="n">
         <v>1.415</v>
       </c>
-      <c r="J7" s="1" t="n">
+      <c r="J7" s="2" t="n">
         <v>40602</v>
       </c>
       <c r="K7" t="n">
@@ -7537,13 +7549,13 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="1" t="n">
+      <c r="A8" s="2" t="n">
         <v>40179</v>
       </c>
-      <c r="B8" s="1" t="n">
+      <c r="B8" s="2" t="n">
         <v>40268</v>
       </c>
-      <c r="C8" s="1" t="n">
+      <c r="C8" s="2" t="n">
         <v>40308</v>
       </c>
       <c r="D8" t="inlineStr">
@@ -7570,7 +7582,7 @@
       <c r="I8" t="n">
         <v>1.56</v>
       </c>
-      <c r="J8" s="1" t="n">
+      <c r="J8" s="2" t="n">
         <v>40602</v>
       </c>
       <c r="K8" t="n">
@@ -7583,13 +7595,13 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="1" t="n">
+      <c r="A9" s="2" t="n">
         <v>40269</v>
       </c>
-      <c r="B9" s="1" t="n">
+      <c r="B9" s="2" t="n">
         <v>40359</v>
       </c>
-      <c r="C9" s="1" t="n">
+      <c r="C9" s="2" t="n">
         <v>40399</v>
       </c>
       <c r="D9" t="inlineStr">
@@ -7616,7 +7628,7 @@
       <c r="I9" t="n">
         <v>1.65113831608907</v>
       </c>
-      <c r="J9" s="1" t="n">
+      <c r="J9" s="2" t="n">
         <v>40602</v>
       </c>
       <c r="K9" t="n">
@@ -7629,13 +7641,13 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="1" t="n">
+      <c r="A10" s="2" t="n">
         <v>40360</v>
       </c>
-      <c r="B10" s="1" t="n">
+      <c r="B10" s="2" t="n">
         <v>40451</v>
       </c>
-      <c r="C10" s="1" t="n">
+      <c r="C10" s="2" t="n">
         <v>40490</v>
       </c>
       <c r="D10" t="inlineStr">
@@ -7662,7 +7674,7 @@
       <c r="I10" t="n">
         <v>1.70613831608907</v>
       </c>
-      <c r="J10" s="1" t="n">
+      <c r="J10" s="2" t="n">
         <v>40602</v>
       </c>
       <c r="K10" t="n">
@@ -7675,13 +7687,13 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="1" t="n">
+      <c r="A11" s="2" t="n">
         <v>40452</v>
       </c>
-      <c r="B11" s="1" t="n">
+      <c r="B11" s="2" t="n">
         <v>40543</v>
       </c>
-      <c r="C11" s="1" t="n">
+      <c r="C11" s="2" t="n">
         <v>40602</v>
       </c>
       <c r="D11" t="inlineStr">
@@ -7708,7 +7720,7 @@
       <c r="I11" t="n">
         <v>1.65113831608907</v>
       </c>
-      <c r="J11" s="1" t="n">
+      <c r="J11" s="2" t="n">
         <v>40602</v>
       </c>
       <c r="K11" t="n">
@@ -7721,13 +7733,13 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="1" t="n">
+      <c r="A12" s="2" t="n">
         <v>40544</v>
       </c>
-      <c r="B12" s="1" t="n">
+      <c r="B12" s="2" t="n">
         <v>40633</v>
       </c>
-      <c r="C12" s="1" t="n">
+      <c r="C12" s="2" t="n">
         <v>40672</v>
       </c>
       <c r="D12" t="inlineStr">
@@ -7754,7 +7766,7 @@
       <c r="I12" t="n">
         <v>1.59113831608907</v>
       </c>
-      <c r="J12" s="1" t="n">
+      <c r="J12" s="2" t="n">
         <v>40672</v>
       </c>
       <c r="K12" t="n">
@@ -7767,13 +7779,13 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="1" t="n">
+      <c r="A13" s="2" t="n">
         <v>40634</v>
       </c>
-      <c r="B13" s="1" t="n">
+      <c r="B13" s="2" t="n">
         <v>40724</v>
       </c>
-      <c r="C13" s="1" t="n">
+      <c r="C13" s="2" t="n">
         <v>40760</v>
       </c>
       <c r="D13" t="inlineStr">
@@ -7800,7 +7812,7 @@
       <c r="I13" t="n">
         <v>1.66</v>
       </c>
-      <c r="J13" s="1" t="n">
+      <c r="J13" s="2" t="n">
         <v>40760</v>
       </c>
       <c r="K13" t="n">
@@ -7813,13 +7825,13 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="1" t="n">
+      <c r="A14" s="2" t="n">
         <v>40725</v>
       </c>
-      <c r="B14" s="1" t="n">
+      <c r="B14" s="2" t="n">
         <v>40816</v>
       </c>
-      <c r="C14" s="1" t="n">
+      <c r="C14" s="2" t="n">
         <v>40851</v>
       </c>
       <c r="D14" t="inlineStr">
@@ -7846,7 +7858,7 @@
       <c r="I14" t="n">
         <v>1.72</v>
       </c>
-      <c r="J14" s="1" t="n">
+      <c r="J14" s="2" t="n">
         <v>40851</v>
       </c>
       <c r="K14" t="n">
@@ -7859,13 +7871,13 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="1" t="n">
+      <c r="A15" s="2" t="n">
         <v>40817</v>
       </c>
-      <c r="B15" s="1" t="n">
+      <c r="B15" s="2" t="n">
         <v>40908</v>
       </c>
-      <c r="C15" s="1" t="n">
+      <c r="C15" s="2" t="n">
         <v>40962</v>
       </c>
       <c r="D15" t="inlineStr">
@@ -7892,7 +7904,7 @@
       <c r="I15" t="n">
         <v>1.775</v>
       </c>
-      <c r="J15" s="1" t="n">
+      <c r="J15" s="2" t="n">
         <v>40962</v>
       </c>
       <c r="K15" t="n">
@@ -7905,13 +7917,13 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="1" t="n">
+      <c r="A16" s="2" t="n">
         <v>40909</v>
       </c>
-      <c r="B16" s="1" t="n">
+      <c r="B16" s="2" t="n">
         <v>40999</v>
       </c>
-      <c r="C16" s="1" t="n">
+      <c r="C16" s="2" t="n">
         <v>41033</v>
       </c>
       <c r="D16" t="inlineStr">
@@ -7938,7 +7950,7 @@
       <c r="I16" t="n">
         <v>1.66</v>
       </c>
-      <c r="J16" s="1" t="n">
+      <c r="J16" s="2" t="n">
         <v>41033</v>
       </c>
       <c r="K16" t="n">
@@ -7951,13 +7963,13 @@
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="1" t="n">
+      <c r="A17" s="2" t="n">
         <v>41000</v>
       </c>
-      <c r="B17" s="1" t="n">
+      <c r="B17" s="2" t="n">
         <v>41090</v>
       </c>
-      <c r="C17" s="1" t="n">
+      <c r="C17" s="2" t="n">
         <v>41122</v>
       </c>
       <c r="D17" t="inlineStr">
@@ -7984,7 +7996,7 @@
       <c r="I17" t="n">
         <v>1.65</v>
       </c>
-      <c r="J17" s="1" t="n">
+      <c r="J17" s="2" t="n">
         <v>41122</v>
       </c>
       <c r="K17" t="n">
@@ -7997,13 +8009,13 @@
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="1" t="n">
+      <c r="A18" s="2" t="n">
         <v>41091</v>
       </c>
-      <c r="B18" s="1" t="n">
+      <c r="B18" s="2" t="n">
         <v>41182</v>
       </c>
-      <c r="C18" s="1" t="n">
+      <c r="C18" s="2" t="n">
         <v>41219</v>
       </c>
       <c r="D18" t="inlineStr">
@@ -8030,7 +8042,7 @@
       <c r="I18" t="n">
         <v>1.6</v>
       </c>
-      <c r="J18" s="1" t="n">
+      <c r="J18" s="2" t="n">
         <v>41219</v>
       </c>
       <c r="K18" t="n">
@@ -8043,13 +8055,13 @@
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="1" t="n">
+      <c r="A19" s="2" t="n">
         <v>41183</v>
       </c>
-      <c r="B19" s="1" t="n">
+      <c r="B19" s="2" t="n">
         <v>41274</v>
       </c>
-      <c r="C19" s="1" t="n">
+      <c r="C19" s="2" t="n">
         <v>41332</v>
       </c>
       <c r="D19" t="inlineStr">
@@ -8076,7 +8088,7 @@
       <c r="I19" t="n">
         <v>1.635</v>
       </c>
-      <c r="J19" s="1" t="n">
+      <c r="J19" s="2" t="n">
         <v>41332</v>
       </c>
       <c r="K19" t="n">
@@ -8089,13 +8101,13 @@
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="1" t="n">
+      <c r="A20" s="2" t="n">
         <v>41275</v>
       </c>
-      <c r="B20" s="1" t="n">
+      <c r="B20" s="2" t="n">
         <v>41364</v>
       </c>
-      <c r="C20" s="1" t="n">
+      <c r="C20" s="2" t="n">
         <v>41402</v>
       </c>
       <c r="D20" t="inlineStr">
@@ -8122,7 +8134,7 @@
       <c r="I20" t="n">
         <v>1.78</v>
       </c>
-      <c r="J20" s="1" t="n">
+      <c r="J20" s="2" t="n">
         <v>41402</v>
       </c>
       <c r="K20" t="n">
@@ -8135,13 +8147,13 @@
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="1" t="n">
+      <c r="A21" s="2" t="n">
         <v>41365</v>
       </c>
-      <c r="B21" s="1" t="n">
+      <c r="B21" s="2" t="n">
         <v>41455</v>
       </c>
-      <c r="C21" s="1" t="n">
+      <c r="C21" s="2" t="n">
         <v>41487</v>
       </c>
       <c r="D21" t="inlineStr">
@@ -8168,7 +8180,7 @@
       <c r="I21" t="n">
         <v>1.785</v>
       </c>
-      <c r="J21" s="1" t="n">
+      <c r="J21" s="2" t="n">
         <v>41487</v>
       </c>
       <c r="K21" t="n">
@@ -8181,13 +8193,13 @@
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="1" t="n">
+      <c r="A22" s="2" t="n">
         <v>41456</v>
       </c>
-      <c r="B22" s="1" t="n">
+      <c r="B22" s="2" t="n">
         <v>41547</v>
       </c>
-      <c r="C22" s="1" t="n">
+      <c r="C22" s="2" t="n">
         <v>41578</v>
       </c>
       <c r="D22" t="inlineStr">
@@ -8214,7 +8226,7 @@
       <c r="I22" t="n">
         <v>1.83</v>
       </c>
-      <c r="J22" s="1" t="n">
+      <c r="J22" s="2" t="n">
         <v>41578</v>
       </c>
       <c r="K22" t="n">
@@ -8227,13 +8239,13 @@
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="1" t="n">
+      <c r="A23" s="2" t="n">
         <v>41548</v>
       </c>
-      <c r="B23" s="1" t="n">
+      <c r="B23" s="2" t="n">
         <v>41639</v>
       </c>
-      <c r="C23" s="1" t="n">
+      <c r="C23" s="2" t="n">
         <v>41695</v>
       </c>
       <c r="D23" t="inlineStr">
@@ -8260,7 +8272,7 @@
       <c r="I23" t="n">
         <v>1.83</v>
       </c>
-      <c r="J23" s="1" t="n">
+      <c r="J23" s="2" t="n">
         <v>41695</v>
       </c>
       <c r="K23" t="n">
@@ -8273,13 +8285,13 @@
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="1" t="n">
+      <c r="A24" s="2" t="n">
         <v>41640</v>
       </c>
-      <c r="B24" s="1" t="n">
+      <c r="B24" s="2" t="n">
         <v>41729</v>
       </c>
-      <c r="C24" s="1" t="n">
+      <c r="C24" s="2" t="n">
         <v>41766</v>
       </c>
       <c r="D24" t="inlineStr">
@@ -8306,7 +8318,7 @@
       <c r="I24" t="n">
         <v>2.73</v>
       </c>
-      <c r="J24" s="1" t="n">
+      <c r="J24" s="2" t="n">
         <v>41766</v>
       </c>
       <c r="K24" t="n">
@@ -8319,13 +8331,13 @@
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="1" t="n">
+      <c r="A25" s="2" t="n">
         <v>41730</v>
       </c>
-      <c r="B25" s="1" t="n">
+      <c r="B25" s="2" t="n">
         <v>41820</v>
       </c>
-      <c r="C25" s="1" t="n">
+      <c r="C25" s="2" t="n">
         <v>41855</v>
       </c>
       <c r="D25" t="inlineStr">
@@ -8352,7 +8364,7 @@
       <c r="I25" t="n">
         <v>4.470000000000001</v>
       </c>
-      <c r="J25" s="1" t="n">
+      <c r="J25" s="2" t="n">
         <v>41855</v>
       </c>
       <c r="K25" t="n">
@@ -8365,13 +8377,13 @@
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="1" t="n">
+      <c r="A26" s="2" t="n">
         <v>41821</v>
       </c>
-      <c r="B26" s="1" t="n">
+      <c r="B26" s="2" t="n">
         <v>41912</v>
       </c>
-      <c r="C26" s="1" t="n">
+      <c r="C26" s="2" t="n">
         <v>41948</v>
       </c>
       <c r="D26" t="inlineStr">
@@ -8398,7 +8410,7 @@
       <c r="I26" t="n">
         <v>5.67</v>
       </c>
-      <c r="J26" s="1" t="n">
+      <c r="J26" s="2" t="n">
         <v>41948</v>
       </c>
       <c r="K26" t="n">
@@ -8411,13 +8423,13 @@
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="1" t="n">
+      <c r="A27" s="2" t="n">
         <v>41913</v>
       </c>
-      <c r="B27" s="1" t="n">
+      <c r="B27" s="2" t="n">
         <v>42004</v>
       </c>
-      <c r="C27" s="1" t="n">
+      <c r="C27" s="2" t="n">
         <v>42060</v>
       </c>
       <c r="D27" t="inlineStr">
@@ -8444,7 +8456,7 @@
       <c r="I27" t="n">
         <v>7.380000000000001</v>
       </c>
-      <c r="J27" s="1" t="n">
+      <c r="J27" s="2" t="n">
         <v>42060</v>
       </c>
       <c r="K27" t="n">
@@ -8457,13 +8469,13 @@
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="1" t="n">
+      <c r="A28" s="2" t="n">
         <v>42005</v>
       </c>
-      <c r="B28" s="1" t="n">
+      <c r="B28" s="2" t="n">
         <v>42094</v>
       </c>
-      <c r="C28" s="1" t="n">
+      <c r="C28" s="2" t="n">
         <v>42132</v>
       </c>
       <c r="D28" t="inlineStr">
@@ -8490,7 +8502,7 @@
       <c r="I28" t="n">
         <v>8.81</v>
       </c>
-      <c r="J28" s="1" t="n">
+      <c r="J28" s="2" t="n">
         <v>42132</v>
       </c>
       <c r="K28" t="n">
@@ -8503,13 +8515,13 @@
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="1" t="n">
+      <c r="A29" s="2" t="n">
         <v>42095</v>
       </c>
-      <c r="B29" s="1" t="n">
+      <c r="B29" s="2" t="n">
         <v>42185</v>
       </c>
-      <c r="C29" s="1" t="n">
+      <c r="C29" s="2" t="n">
         <v>42221</v>
       </c>
       <c r="D29" t="inlineStr">
@@ -8536,7 +8548,7 @@
       <c r="I29" t="n">
         <v>9.529999999999999</v>
       </c>
-      <c r="J29" s="1" t="n">
+      <c r="J29" s="2" t="n">
         <v>42221</v>
       </c>
       <c r="K29" t="n">
@@ -8549,13 +8561,13 @@
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="1" t="n">
+      <c r="A30" s="2" t="n">
         <v>42186</v>
       </c>
-      <c r="B30" s="1" t="n">
+      <c r="B30" s="2" t="n">
         <v>42277</v>
       </c>
-      <c r="C30" s="1" t="n">
+      <c r="C30" s="2" t="n">
         <v>42312</v>
       </c>
       <c r="D30" t="inlineStr">
@@ -8582,7 +8594,7 @@
       <c r="I30" t="n">
         <v>10.92</v>
       </c>
-      <c r="J30" s="1" t="n">
+      <c r="J30" s="2" t="n">
         <v>42312</v>
       </c>
       <c r="K30" t="n">
@@ -8595,13 +8607,13 @@
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="1" t="n">
+      <c r="A31" s="2" t="n">
         <v>42278</v>
       </c>
-      <c r="B31" s="1" t="n">
+      <c r="B31" s="2" t="n">
         <v>42369</v>
       </c>
-      <c r="C31" s="1" t="n">
+      <c r="C31" s="2" t="n">
         <v>42424</v>
       </c>
       <c r="D31" t="inlineStr">
@@ -8628,7 +8640,7 @@
       <c r="I31" t="n">
         <v>11.92</v>
       </c>
-      <c r="J31" s="1" t="n">
+      <c r="J31" s="2" t="n">
         <v>42424</v>
       </c>
       <c r="K31" t="n">
@@ -8641,13 +8653,13 @@
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="1" t="n">
+      <c r="A32" s="2" t="n">
         <v>42370</v>
       </c>
-      <c r="B32" s="1" t="n">
+      <c r="B32" s="2" t="n">
         <v>42460</v>
       </c>
-      <c r="C32" s="1" t="n">
+      <c r="C32" s="2" t="n">
         <v>42496</v>
       </c>
       <c r="D32" t="inlineStr">
@@ -8674,7 +8686,7 @@
       <c r="I32" t="n">
         <v>11.69</v>
       </c>
-      <c r="J32" s="1" t="n">
+      <c r="J32" s="2" t="n">
         <v>42496</v>
       </c>
       <c r="K32" t="n">
@@ -8687,13 +8699,13 @@
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="1" t="n">
+      <c r="A33" s="2" t="n">
         <v>42461</v>
       </c>
-      <c r="B33" s="1" t="n">
+      <c r="B33" s="2" t="n">
         <v>42551</v>
       </c>
-      <c r="C33" s="1" t="n">
+      <c r="C33" s="2" t="n">
         <v>42587</v>
       </c>
       <c r="D33" t="inlineStr">
@@ -8720,7 +8732,7 @@
       <c r="I33" t="n">
         <v>11.35</v>
       </c>
-      <c r="J33" s="1" t="n">
+      <c r="J33" s="2" t="n">
         <v>42587</v>
       </c>
       <c r="K33" t="n">
@@ -8733,13 +8745,13 @@
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="1" t="n">
+      <c r="A34" s="2" t="n">
         <v>42552</v>
       </c>
-      <c r="B34" s="1" t="n">
+      <c r="B34" s="2" t="n">
         <v>42643</v>
       </c>
-      <c r="C34" s="1" t="n">
+      <c r="C34" s="2" t="n">
         <v>42681</v>
       </c>
       <c r="D34" t="inlineStr">
@@ -8766,7 +8778,7 @@
       <c r="I34" t="n">
         <v>10.78</v>
       </c>
-      <c r="J34" s="1" t="n">
+      <c r="J34" s="2" t="n">
         <v>42681</v>
       </c>
       <c r="K34" t="n">
@@ -8779,13 +8791,13 @@
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="1" t="n">
+      <c r="A35" s="2" t="n">
         <v>42644</v>
       </c>
-      <c r="B35" s="1" t="n">
+      <c r="B35" s="2" t="n">
         <v>42735</v>
       </c>
-      <c r="C35" s="1" t="n">
+      <c r="C35" s="2" t="n">
         <v>42793</v>
       </c>
       <c r="D35" t="inlineStr">
@@ -8812,7 +8824,7 @@
       <c r="I35" t="n">
         <v>9.94</v>
       </c>
-      <c r="J35" s="1" t="n">
+      <c r="J35" s="2" t="n">
         <v>42793</v>
       </c>
       <c r="K35" t="n">
@@ -8825,13 +8837,13 @@
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="1" t="n">
+      <c r="A36" s="2" t="n">
         <v>42736</v>
       </c>
-      <c r="B36" s="1" t="n">
+      <c r="B36" s="2" t="n">
         <v>42825</v>
       </c>
-      <c r="C36" s="1" t="n">
+      <c r="C36" s="2" t="n">
         <v>42865</v>
       </c>
       <c r="D36" t="inlineStr">
@@ -8858,7 +8870,7 @@
       <c r="I36" t="n">
         <v>9.460000000000001</v>
       </c>
-      <c r="J36" s="1" t="n">
+      <c r="J36" s="2" t="n">
         <v>42865</v>
       </c>
       <c r="K36" t="n">
@@ -8871,13 +8883,13 @@
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="1" t="n">
+      <c r="A37" s="2" t="n">
         <v>42826</v>
       </c>
-      <c r="B37" s="1" t="n">
+      <c r="B37" s="2" t="n">
         <v>42916</v>
       </c>
-      <c r="C37" s="1" t="n">
+      <c r="C37" s="2" t="n">
         <v>42954</v>
       </c>
       <c r="D37" t="inlineStr">
@@ -8904,7 +8916,7 @@
       <c r="I37" t="n">
         <v>9.210000000000001</v>
       </c>
-      <c r="J37" s="1" t="n">
+      <c r="J37" s="2" t="n">
         <v>42954</v>
       </c>
       <c r="K37" t="n">
@@ -8917,13 +8929,13 @@
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="1" t="n">
+      <c r="A38" s="2" t="n">
         <v>42917</v>
       </c>
-      <c r="B38" s="1" t="n">
+      <c r="B38" s="2" t="n">
         <v>43008</v>
       </c>
-      <c r="C38" s="1" t="n">
+      <c r="C38" s="2" t="n">
         <v>43046</v>
       </c>
       <c r="D38" t="inlineStr">
@@ -8950,7 +8962,7 @@
       <c r="I38" t="n">
         <v>8.780000000000001</v>
       </c>
-      <c r="J38" s="1" t="n">
+      <c r="J38" s="2" t="n">
         <v>43046</v>
       </c>
       <c r="K38" t="n">
@@ -8963,13 +8975,13 @@
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="1" t="n">
+      <c r="A39" s="2" t="n">
         <v>43009</v>
       </c>
-      <c r="B39" s="1" t="n">
+      <c r="B39" s="2" t="n">
         <v>43100</v>
       </c>
-      <c r="C39" s="1" t="n">
+      <c r="C39" s="2" t="n">
         <v>43158</v>
       </c>
       <c r="D39" t="inlineStr">
@@ -8996,7 +9008,7 @@
       <c r="I39" t="n">
         <v>3.48</v>
       </c>
-      <c r="J39" s="1" t="n">
+      <c r="J39" s="2" t="n">
         <v>43158</v>
       </c>
       <c r="K39" t="n">
@@ -9009,13 +9021,13 @@
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="1" t="n">
+      <c r="A40" s="2" t="n">
         <v>43101</v>
       </c>
-      <c r="B40" s="1" t="n">
+      <c r="B40" s="2" t="n">
         <v>43190</v>
       </c>
-      <c r="C40" s="1" t="n">
+      <c r="C40" s="2" t="n">
         <v>43229</v>
       </c>
       <c r="D40" t="inlineStr">
@@ -9042,7 +9054,7 @@
       <c r="I40" t="n">
         <v>2.6</v>
       </c>
-      <c r="J40" s="1" t="n">
+      <c r="J40" s="2" t="n">
         <v>43229</v>
       </c>
       <c r="K40" t="n">
@@ -9055,13 +9067,13 @@
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="1" t="n">
+      <c r="A41" s="2" t="n">
         <v>43191</v>
       </c>
-      <c r="B41" s="1" t="n">
+      <c r="B41" s="2" t="n">
         <v>43281</v>
       </c>
-      <c r="C41" s="1" t="n">
+      <c r="C41" s="2" t="n">
         <v>43318</v>
       </c>
       <c r="D41" t="inlineStr">
@@ -9088,7 +9100,7 @@
       <c r="I41" t="n">
         <v>1.66</v>
       </c>
-      <c r="J41" s="1" t="n">
+      <c r="J41" s="2" t="n">
         <v>43318</v>
       </c>
       <c r="K41" t="n">
@@ -9101,13 +9113,13 @@
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="1" t="n">
+      <c r="A42" s="2" t="n">
         <v>43282</v>
       </c>
-      <c r="B42" s="1" t="n">
+      <c r="B42" s="2" t="n">
         <v>43373</v>
       </c>
-      <c r="C42" s="1" t="n">
+      <c r="C42" s="2" t="n">
         <v>43410</v>
       </c>
       <c r="D42" t="inlineStr">
@@ -9134,7 +9146,7 @@
       <c r="I42" t="n">
         <v>1.2</v>
       </c>
-      <c r="J42" s="1" t="n">
+      <c r="J42" s="2" t="n">
         <v>43410</v>
       </c>
       <c r="K42" t="n">
@@ -9147,13 +9159,13 @@
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="1" t="n">
+      <c r="A43" s="2" t="n">
         <v>43374</v>
       </c>
-      <c r="B43" s="1" t="n">
+      <c r="B43" s="2" t="n">
         <v>43465</v>
       </c>
-      <c r="C43" s="1" t="n">
+      <c r="C43" s="2" t="n">
         <v>43522</v>
       </c>
       <c r="D43" t="inlineStr">
@@ -9180,7 +9192,7 @@
       <c r="I43" t="n">
         <v>4.16</v>
       </c>
-      <c r="J43" s="1" t="n">
+      <c r="J43" s="2" t="n">
         <v>43522</v>
       </c>
       <c r="K43" t="n">
@@ -9193,13 +9205,13 @@
       </c>
     </row>
     <row r="44">
-      <c r="A44" s="1" t="n">
+      <c r="A44" s="2" t="n">
         <v>43466</v>
       </c>
-      <c r="B44" s="1" t="n">
+      <c r="B44" s="2" t="n">
         <v>43555</v>
       </c>
-      <c r="C44" s="1" t="n">
+      <c r="C44" s="2" t="n">
         <v>43593</v>
       </c>
       <c r="D44" t="inlineStr">
@@ -9226,7 +9238,7 @@
       <c r="I44" t="n">
         <v>4.53</v>
       </c>
-      <c r="J44" s="1" t="n">
+      <c r="J44" s="2" t="n">
         <v>43593</v>
       </c>
       <c r="K44" t="n">
@@ -9239,13 +9251,13 @@
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="1" t="n">
+      <c r="A45" s="2" t="n">
         <v>43556</v>
       </c>
-      <c r="B45" s="1" t="n">
+      <c r="B45" s="2" t="n">
         <v>43646</v>
       </c>
-      <c r="C45" s="1" t="n">
+      <c r="C45" s="2" t="n">
         <v>43683</v>
       </c>
       <c r="D45" t="inlineStr">
@@ -9272,7 +9284,7 @@
       <c r="I45" t="n">
         <v>4.61</v>
       </c>
-      <c r="J45" s="1" t="n">
+      <c r="J45" s="2" t="n">
         <v>43683</v>
       </c>
       <c r="K45" t="n">
@@ -9285,13 +9297,13 @@
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="1" t="n">
+      <c r="A46" s="2" t="n">
         <v>43647</v>
       </c>
-      <c r="B46" s="1" t="n">
+      <c r="B46" s="2" t="n">
         <v>43738</v>
       </c>
-      <c r="C46" s="1" t="n">
+      <c r="C46" s="2" t="n">
         <v>43774</v>
       </c>
       <c r="D46" t="inlineStr">
@@ -9318,7 +9330,7 @@
       <c r="I46" t="n">
         <v>2.09</v>
       </c>
-      <c r="J46" s="1" t="n">
+      <c r="J46" s="2" t="n">
         <v>43774</v>
       </c>
       <c r="K46" t="n">
@@ -9331,13 +9343,13 @@
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="1" t="n">
+      <c r="A47" s="2" t="n">
         <v>43739</v>
       </c>
-      <c r="B47" s="1" t="n">
+      <c r="B47" s="2" t="n">
         <v>43830</v>
       </c>
-      <c r="C47" s="1" t="n">
+      <c r="C47" s="2" t="n">
         <v>43886</v>
       </c>
       <c r="D47" t="inlineStr">
@@ -9364,7 +9376,7 @@
       <c r="I47" t="n">
         <v>4.21</v>
       </c>
-      <c r="J47" s="1" t="n">
+      <c r="J47" s="2" t="n">
         <v>43886</v>
       </c>
       <c r="K47" t="n">
@@ -9377,13 +9389,13 @@
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="1" t="n">
+      <c r="A48" s="2" t="n">
         <v>43831</v>
       </c>
-      <c r="B48" s="1" t="n">
+      <c r="B48" s="2" t="n">
         <v>43921</v>
       </c>
-      <c r="C48" s="1" t="n">
+      <c r="C48" s="2" t="n">
         <v>43957</v>
       </c>
       <c r="D48" t="inlineStr">
@@ -9410,7 +9422,7 @@
       <c r="I48" t="n">
         <v>3.89</v>
       </c>
-      <c r="J48" s="1" t="n">
+      <c r="J48" s="2" t="n">
         <v>43957</v>
       </c>
       <c r="K48" t="n">
@@ -9423,13 +9435,13 @@
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="1" t="n">
+      <c r="A49" s="2" t="n">
         <v>43922</v>
       </c>
-      <c r="B49" s="1" t="n">
+      <c r="B49" s="2" t="n">
         <v>44012</v>
       </c>
-      <c r="C49" s="1" t="n">
+      <c r="C49" s="2" t="n">
         <v>44049</v>
       </c>
       <c r="D49" t="inlineStr">
@@ -9456,7 +9468,7 @@
       <c r="I49" t="n">
         <v>-0.2400000000000002</v>
       </c>
-      <c r="J49" s="1" t="n">
+      <c r="J49" s="2" t="n">
         <v>44049</v>
       </c>
       <c r="K49" t="n">
@@ -9469,13 +9481,13 @@
       </c>
     </row>
     <row r="50">
-      <c r="A50" s="1" t="n">
+      <c r="A50" s="2" t="n">
         <v>44013</v>
       </c>
-      <c r="B50" s="1" t="n">
+      <c r="B50" s="2" t="n">
         <v>44104</v>
       </c>
-      <c r="C50" s="1" t="n">
+      <c r="C50" s="2" t="n">
         <v>44139</v>
       </c>
       <c r="D50" t="inlineStr">
@@ -9502,7 +9514,7 @@
       <c r="I50" t="n">
         <v>0.9699999999999998</v>
       </c>
-      <c r="J50" s="1" t="n">
+      <c r="J50" s="2" t="n">
         <v>44139</v>
       </c>
       <c r="K50" t="n">
@@ -9515,13 +9527,13 @@
       </c>
     </row>
     <row r="51">
-      <c r="A51" s="1" t="n">
+      <c r="A51" s="2" t="n">
         <v>44105</v>
       </c>
-      <c r="B51" s="1" t="n">
+      <c r="B51" s="2" t="n">
         <v>44196</v>
       </c>
-      <c r="C51" s="1" t="n">
+      <c r="C51" s="2" t="n">
         <v>44252</v>
       </c>
       <c r="D51" t="inlineStr">
@@ -9548,7 +9560,7 @@
       <c r="I51" t="n">
         <v>0.07999999999999963</v>
       </c>
-      <c r="J51" s="1" t="n">
+      <c r="J51" s="2" t="n">
         <v>44252</v>
       </c>
       <c r="K51" t="n">
@@ -9561,13 +9573,13 @@
       </c>
     </row>
     <row r="52">
-      <c r="A52" s="1" t="n">
+      <c r="A52" s="2" t="n">
         <v>44197</v>
       </c>
-      <c r="B52" s="1" t="n">
+      <c r="B52" s="2" t="n">
         <v>44286</v>
       </c>
-      <c r="C52" s="1" t="n">
+      <c r="C52" s="2" t="n">
         <v>44322</v>
       </c>
       <c r="D52" t="inlineStr">
@@ -9594,7 +9606,7 @@
       <c r="I52" t="n">
         <v>0.2299999999999998</v>
       </c>
-      <c r="J52" s="1" t="n">
+      <c r="J52" s="2" t="n">
         <v>44322</v>
       </c>
       <c r="K52" t="n">
@@ -9607,13 +9619,13 @@
       </c>
     </row>
     <row r="53">
-      <c r="A53" s="1" t="n">
+      <c r="A53" s="2" t="n">
         <v>44287</v>
       </c>
-      <c r="B53" s="1" t="n">
+      <c r="B53" s="2" t="n">
         <v>44377</v>
       </c>
-      <c r="C53" s="1" t="n">
+      <c r="C53" s="2" t="n">
         <v>44413</v>
       </c>
       <c r="D53" t="inlineStr">
@@ -9640,7 +9652,7 @@
       <c r="I53" t="n">
         <v>4.1</v>
       </c>
-      <c r="J53" s="1" t="n">
+      <c r="J53" s="2" t="n">
         <v>44413</v>
       </c>
       <c r="K53" t="n">
@@ -9653,13 +9665,13 @@
       </c>
     </row>
     <row r="54">
-      <c r="A54" s="1" t="n">
+      <c r="A54" s="2" t="n">
         <v>44378</v>
       </c>
-      <c r="B54" s="1" t="n">
+      <c r="B54" s="2" t="n">
         <v>44469</v>
       </c>
-      <c r="C54" s="1" t="n">
+      <c r="C54" s="2" t="n">
         <v>44503</v>
       </c>
       <c r="D54" t="inlineStr">
@@ -9686,7 +9698,7 @@
       <c r="I54" t="n">
         <v>5.859999999999999</v>
       </c>
-      <c r="J54" s="1" t="n">
+      <c r="J54" s="2" t="n">
         <v>44503</v>
       </c>
       <c r="K54" t="n">
@@ -9699,13 +9711,13 @@
       </c>
     </row>
     <row r="55">
-      <c r="A55" s="1" t="n">
+      <c r="A55" s="2" t="n">
         <v>44470</v>
       </c>
-      <c r="B55" s="1" t="n">
+      <c r="B55" s="2" t="n">
         <v>44561</v>
       </c>
-      <c r="C55" s="1" t="n">
+      <c r="C55" s="2" t="n">
         <v>44615</v>
       </c>
       <c r="D55" t="inlineStr">
@@ -9732,7 +9744,7 @@
       <c r="I55" t="n">
         <v>4.929999999999999</v>
       </c>
-      <c r="J55" s="1" t="n">
+      <c r="J55" s="2" t="n">
         <v>44615</v>
       </c>
       <c r="K55" t="n">
@@ -9745,13 +9757,13 @@
       </c>
     </row>
     <row r="56">
-      <c r="A56" s="1" t="n">
+      <c r="A56" s="2" t="n">
         <v>44562</v>
       </c>
-      <c r="B56" s="1" t="n">
+      <c r="B56" s="2" t="n">
         <v>44651</v>
       </c>
-      <c r="C56" s="1" t="n">
+      <c r="C56" s="2" t="n">
         <v>44685</v>
       </c>
       <c r="D56" t="inlineStr">
@@ -9778,7 +9790,7 @@
       <c r="I56" t="n">
         <v>3.579999999999999</v>
       </c>
-      <c r="J56" s="1" t="n">
+      <c r="J56" s="2" t="n">
         <v>44685</v>
       </c>
       <c r="K56" t="n">
@@ -9791,13 +9803,13 @@
       </c>
     </row>
     <row r="57">
-      <c r="A57" s="1" t="n">
+      <c r="A57" s="2" t="n">
         <v>44652</v>
       </c>
-      <c r="B57" s="1" t="n">
+      <c r="B57" s="2" t="n">
         <v>44742</v>
       </c>
-      <c r="C57" s="1" t="n">
+      <c r="C57" s="2" t="n">
         <v>44781</v>
       </c>
       <c r="D57" t="inlineStr">
@@ -9824,7 +9836,7 @@
       <c r="I57" t="n">
         <v>3.279999999999999</v>
       </c>
-      <c r="J57" s="1" t="n">
+      <c r="J57" s="2" t="n">
         <v>44781</v>
       </c>
       <c r="K57" t="n">
@@ -9837,13 +9849,13 @@
       </c>
     </row>
     <row r="58">
-      <c r="A58" s="1" t="n">
+      <c r="A58" s="2" t="n">
         <v>44743</v>
       </c>
-      <c r="B58" s="1" t="n">
+      <c r="B58" s="2" t="n">
         <v>44834</v>
       </c>
-      <c r="C58" s="1" t="n">
+      <c r="C58" s="2" t="n">
         <v>44867</v>
       </c>
       <c r="D58" t="inlineStr">
@@ -9870,7 +9882,7 @@
       <c r="I58" t="n">
         <v>2.649999999999999</v>
       </c>
-      <c r="J58" s="1" t="n">
+      <c r="J58" s="2" t="n">
         <v>44867</v>
       </c>
       <c r="K58" t="n">
@@ -9883,13 +9895,13 @@
       </c>
     </row>
     <row r="59">
-      <c r="A59" s="1" t="n">
+      <c r="A59" s="2" t="n">
         <v>44835</v>
       </c>
-      <c r="B59" s="1" t="n">
+      <c r="B59" s="2" t="n">
         <v>44926</v>
       </c>
-      <c r="C59" s="1" t="n">
+      <c r="C59" s="2" t="n">
         <v>44979</v>
       </c>
       <c r="D59" t="inlineStr">
@@ -9916,7 +9928,7 @@
       <c r="I59" t="n">
         <v>3.64</v>
       </c>
-      <c r="J59" s="1" t="n">
+      <c r="J59" s="2" t="n">
         <v>44979</v>
       </c>
       <c r="K59" t="n">
@@ -9929,13 +9941,13 @@
       </c>
     </row>
     <row r="60">
-      <c r="A60" s="1" t="n">
+      <c r="A60" s="2" t="n">
         <v>44927</v>
       </c>
-      <c r="B60" s="1" t="n">
+      <c r="B60" s="2" t="n">
         <v>45016</v>
       </c>
-      <c r="C60" s="1" t="n">
+      <c r="C60" s="2" t="n">
         <v>45049</v>
       </c>
       <c r="D60" t="inlineStr">
@@ -9962,7 +9974,7 @@
       <c r="I60" t="n">
         <v>4.42</v>
       </c>
-      <c r="J60" s="1" t="n">
+      <c r="J60" s="2" t="n">
         <v>45049</v>
       </c>
       <c r="K60" t="n">
@@ -9975,13 +9987,13 @@
       </c>
     </row>
     <row r="61">
-      <c r="A61" s="1" t="n">
+      <c r="A61" s="2" t="n">
         <v>45017</v>
       </c>
-      <c r="B61" s="1" t="n">
+      <c r="B61" s="2" t="n">
         <v>45107</v>
       </c>
-      <c r="C61" s="1" t="n">
+      <c r="C61" s="2" t="n">
         <v>45142</v>
       </c>
       <c r="D61" t="inlineStr">
@@ -10008,7 +10020,7 @@
       <c r="I61" t="n">
         <v>4.34</v>
       </c>
-      <c r="J61" s="1" t="n">
+      <c r="J61" s="2" t="n">
         <v>45142</v>
       </c>
       <c r="K61" t="n">
@@ -10021,13 +10033,13 @@
       </c>
     </row>
     <row r="62">
-      <c r="A62" s="1" t="n">
+      <c r="A62" s="2" t="n">
         <v>45108</v>
       </c>
-      <c r="B62" s="1" t="n">
+      <c r="B62" s="2" t="n">
         <v>45199</v>
       </c>
-      <c r="C62" s="1" t="n">
+      <c r="C62" s="2" t="n">
         <v>45237</v>
       </c>
       <c r="D62" t="inlineStr">
@@ -10054,7 +10066,7 @@
       <c r="I62" t="n">
         <v>4.649999999999999</v>
       </c>
-      <c r="J62" s="1" t="n">
+      <c r="J62" s="2" t="n">
         <v>45237</v>
       </c>
       <c r="K62" t="n">
@@ -10067,13 +10079,13 @@
       </c>
     </row>
     <row r="63">
-      <c r="A63" s="1" t="n">
+      <c r="A63" s="2" t="n">
         <v>45200</v>
       </c>
-      <c r="B63" s="1" t="n">
+      <c r="B63" s="2" t="n">
         <v>45291</v>
       </c>
-      <c r="C63" s="1" t="n">
+      <c r="C63" s="2" t="n">
         <v>45345</v>
       </c>
       <c r="D63" t="inlineStr">
@@ -10100,7 +10112,7 @@
       <c r="I63" t="n">
         <v>4.5</v>
       </c>
-      <c r="J63" s="1" t="n">
+      <c r="J63" s="2" t="n">
         <v>45345</v>
       </c>
       <c r="K63" t="n">
@@ -10113,13 +10125,13 @@
       </c>
     </row>
     <row r="64">
-      <c r="A64" s="1" t="n">
+      <c r="A64" s="2" t="n">
         <v>45292</v>
       </c>
-      <c r="B64" s="1" t="n">
+      <c r="B64" s="2" t="n">
         <v>45382</v>
       </c>
-      <c r="C64" s="1" t="n">
+      <c r="C64" s="2" t="n">
         <v>45420</v>
       </c>
       <c r="D64" t="inlineStr">
@@ -10146,7 +10158,7 @@
       <c r="I64" t="n">
         <v>0.3599999999999999</v>
       </c>
-      <c r="J64" s="1" t="n">
+      <c r="J64" s="2" t="n">
         <v>45420</v>
       </c>
       <c r="K64" t="n">
@@ -10159,13 +10171,13 @@
       </c>
     </row>
     <row r="65">
-      <c r="A65" s="1" t="n">
+      <c r="A65" s="2" t="n">
         <v>45383</v>
       </c>
-      <c r="B65" s="1" t="n">
+      <c r="B65" s="2" t="n">
         <v>45473</v>
       </c>
-      <c r="C65" s="1" t="n">
+      <c r="C65" s="2" t="n">
         <v>45512</v>
       </c>
       <c r="D65" t="inlineStr">
@@ -10192,7 +10204,7 @@
       <c r="I65" t="n">
         <v>0.8199999999999997</v>
       </c>
-      <c r="J65" s="1" t="n">
+      <c r="J65" s="2" t="n">
         <v>45512</v>
       </c>
       <c r="K65" t="n">
@@ -10205,13 +10217,13 @@
       </c>
     </row>
     <row r="66">
-      <c r="A66" s="1" t="n">
+      <c r="A66" s="2" t="n">
         <v>45474</v>
       </c>
-      <c r="B66" s="1" t="n">
+      <c r="B66" s="2" t="n">
         <v>45565</v>
       </c>
-      <c r="C66" s="1" t="n">
+      <c r="C66" s="2" t="n">
         <v>45608</v>
       </c>
       <c r="D66" t="inlineStr">
@@ -10238,7 +10250,7 @@
       <c r="I66" t="n">
         <v>0.08999999999999975</v>
       </c>
-      <c r="J66" s="1" t="n">
+      <c r="J66" s="2" t="n">
         <v>45608</v>
       </c>
       <c r="K66" t="n">
@@ -10251,13 +10263,13 @@
       </c>
     </row>
     <row r="67">
-      <c r="A67" s="1" t="n">
+      <c r="A67" s="2" t="n">
         <v>45566</v>
       </c>
-      <c r="B67" s="1" t="n">
+      <c r="B67" s="2" t="n">
         <v>45657</v>
       </c>
-      <c r="C67" s="1" t="n">
+      <c r="C67" s="2" t="n">
         <v>45716</v>
       </c>
       <c r="D67" t="inlineStr">
@@ -10284,7 +10296,7 @@
       <c r="I67" t="n">
         <v>0.3799999999999994</v>
       </c>
-      <c r="J67" s="1" t="n">
+      <c r="J67" s="2" t="n">
         <v>45716</v>
       </c>
       <c r="K67" t="n">
@@ -10297,13 +10309,13 @@
       </c>
     </row>
     <row r="68">
-      <c r="A68" s="1" t="n">
+      <c r="A68" s="2" t="n">
         <v>45658</v>
       </c>
-      <c r="B68" s="1" t="n">
+      <c r="B68" s="2" t="n">
         <v>45747</v>
       </c>
-      <c r="C68" s="1" t="n">
+      <c r="C68" s="2" t="n">
         <v>45784</v>
       </c>
       <c r="D68" t="inlineStr">
@@ -10330,7 +10342,7 @@
       <c r="I68" t="n">
         <v>4.76</v>
       </c>
-      <c r="J68" s="1" t="n">
+      <c r="J68" s="2" t="n">
         <v>45784</v>
       </c>
       <c r="K68" t="n">
@@ -10343,13 +10355,13 @@
       </c>
     </row>
     <row r="69">
-      <c r="A69" s="1" t="n">
+      <c r="A69" s="2" t="n">
         <v>45748</v>
       </c>
-      <c r="B69" s="1" t="n">
+      <c r="B69" s="2" t="n">
         <v>45838</v>
       </c>
-      <c r="C69" s="1" t="n">
+      <c r="C69" s="2" t="n">
         <v>45876</v>
       </c>
       <c r="D69" t="inlineStr">
@@ -10376,7 +10388,7 @@
       <c r="I69" t="n">
         <v>5.029999999999999</v>
       </c>
-      <c r="J69" s="1" t="n">
+      <c r="J69" s="2" t="n">
         <v>45876</v>
       </c>
       <c r="K69" t="n">
@@ -10389,13 +10401,13 @@
       </c>
     </row>
     <row r="70">
-      <c r="A70" s="1" t="n">
+      <c r="A70" s="2" t="n">
         <v>45839</v>
       </c>
-      <c r="B70" s="1" t="n">
+      <c r="B70" s="2" t="n">
         <v>45930</v>
       </c>
-      <c r="C70" s="1" t="n">
+      <c r="C70" s="2" t="n">
         <v>45968</v>
       </c>
       <c r="D70" t="inlineStr">
@@ -10422,7 +10434,7 @@
       <c r="I70" t="n">
         <v>6.459999999999999</v>
       </c>
-      <c r="J70" s="1" t="n">
+      <c r="J70" s="2" t="n">
         <v>45968</v>
       </c>
       <c r="K70" t="n">
@@ -10435,13 +10447,13 @@
       </c>
     </row>
     <row r="71">
-      <c r="A71" s="1" t="n">
+      <c r="A71" s="2" t="n">
         <v>45931</v>
       </c>
-      <c r="B71" s="1" t="n">
+      <c r="B71" s="2" t="n">
         <v>46022</v>
       </c>
-      <c r="C71" s="1" t="n">
+      <c r="C71" s="2" t="n">
         <v>46077</v>
       </c>
       <c r="D71" t="inlineStr">
@@ -10468,7 +10480,7 @@
       <c r="I71" t="n">
         <v>6.779999999999999</v>
       </c>
-      <c r="J71" s="1" t="n">
+      <c r="J71" s="2" t="n">
         <v>46077</v>
       </c>
       <c r="K71" t="n">
@@ -10481,13 +10493,13 @@
       </c>
     </row>
     <row r="72">
-      <c r="A72" s="1" t="n">
+      <c r="A72" s="2" t="n">
         <v>46023</v>
       </c>
-      <c r="B72" s="1" t="n">
+      <c r="B72" s="2" t="n">
         <v>46112</v>
       </c>
-      <c r="C72" s="1" t="n">
+      <c r="C72" s="2" t="n">
         <v>46149</v>
       </c>
       <c r="D72" t="inlineStr">
@@ -10514,7 +10526,7 @@
       <c r="I72" t="n">
         <v>7.35</v>
       </c>
-      <c r="J72" s="1" t="n">
+      <c r="J72" s="2" t="n">
         <v>46149</v>
       </c>
       <c r="K72" t="n">
@@ -10527,13 +10539,13 @@
       </c>
     </row>
     <row r="73">
-      <c r="A73" s="1" t="n">
+      <c r="A73" s="2" t="n">
         <v>46113</v>
       </c>
-      <c r="B73" s="1" t="n">
+      <c r="B73" s="2" t="n">
         <v>46203</v>
       </c>
-      <c r="C73" s="1" t="n">
+      <c r="C73" s="2" t="n">
         <v>46240</v>
       </c>
       <c r="D73" t="inlineStr">
@@ -10560,7 +10572,7 @@
       <c r="I73" t="n">
         <v>-2.66</v>
       </c>
-      <c r="J73" s="1" t="n">
+      <c r="J73" s="2" t="n">
         <v>46240</v>
       </c>
       <c r="K73" t="n">
@@ -10597,52 +10609,52 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>end</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>filed</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>acciones</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>form</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>fy</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>fp</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>tag</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>factor</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="1" t="n">
+      <c r="A2" s="2" t="n">
         <v>40025</v>
       </c>
-      <c r="B2" s="1" t="n">
+      <c r="B2" s="2" t="n">
         <v>40030</v>
       </c>
       <c r="C2" t="n">
@@ -10671,10 +10683,10 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="1" t="n">
+      <c r="A3" s="2" t="n">
         <v>40116</v>
       </c>
-      <c r="B3" s="1" t="n">
+      <c r="B3" s="2" t="n">
         <v>40122</v>
       </c>
       <c r="C3" t="n">
@@ -10703,10 +10715,10 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="1" t="n">
+      <c r="A4" s="2" t="n">
         <v>40228</v>
       </c>
-      <c r="B4" s="1" t="n">
+      <c r="B4" s="2" t="n">
         <v>40238</v>
       </c>
       <c r="C4" t="n">
@@ -10735,10 +10747,10 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="1" t="n">
+      <c r="A5" s="2" t="n">
         <v>40298</v>
       </c>
-      <c r="B5" s="1" t="n">
+      <c r="B5" s="2" t="n">
         <v>40308</v>
       </c>
       <c r="C5" t="n">
@@ -10767,10 +10779,10 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="1" t="n">
+      <c r="A6" s="2" t="n">
         <v>40390</v>
       </c>
-      <c r="B6" s="1" t="n">
+      <c r="B6" s="2" t="n">
         <v>40399</v>
       </c>
       <c r="C6" t="n">
@@ -10799,10 +10811,10 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="1" t="n">
+      <c r="A7" s="2" t="n">
         <v>40480</v>
       </c>
-      <c r="B7" s="1" t="n">
+      <c r="B7" s="2" t="n">
         <v>40490</v>
       </c>
       <c r="C7" t="n">
@@ -10831,10 +10843,10 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="1" t="n">
+      <c r="A8" s="2" t="n">
         <v>40592</v>
       </c>
-      <c r="B8" s="1" t="n">
+      <c r="B8" s="2" t="n">
         <v>40602</v>
       </c>
       <c r="C8" t="n">
@@ -10863,10 +10875,10 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="1" t="n">
+      <c r="A9" s="2" t="n">
         <v>40662</v>
       </c>
-      <c r="B9" s="1" t="n">
+      <c r="B9" s="2" t="n">
         <v>40672</v>
       </c>
       <c r="C9" t="n">
@@ -10895,10 +10907,10 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="1" t="n">
+      <c r="A10" s="2" t="n">
         <v>40753</v>
       </c>
-      <c r="B10" s="1" t="n">
+      <c r="B10" s="2" t="n">
         <v>40760</v>
       </c>
       <c r="C10" t="n">
@@ -10927,10 +10939,10 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="1" t="n">
+      <c r="A11" s="2" t="n">
         <v>40844</v>
       </c>
-      <c r="B11" s="1" t="n">
+      <c r="B11" s="2" t="n">
         <v>40851</v>
       </c>
       <c r="C11" t="n">
@@ -10959,10 +10971,10 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="1" t="n">
+      <c r="A12" s="2" t="n">
         <v>40949</v>
       </c>
-      <c r="B12" s="1" t="n">
+      <c r="B12" s="2" t="n">
         <v>40962</v>
       </c>
       <c r="C12" t="n">
@@ -10991,10 +11003,10 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="1" t="n">
+      <c r="A13" s="2" t="n">
         <v>41026</v>
       </c>
-      <c r="B13" s="1" t="n">
+      <c r="B13" s="2" t="n">
         <v>41033</v>
       </c>
       <c r="C13" t="n">
@@ -11023,10 +11035,10 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="1" t="n">
+      <c r="A14" s="2" t="n">
         <v>41110</v>
       </c>
-      <c r="B14" s="1" t="n">
+      <c r="B14" s="2" t="n">
         <v>41122</v>
       </c>
       <c r="C14" t="n">
@@ -11055,10 +11067,10 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="1" t="n">
+      <c r="A15" s="2" t="n">
         <v>41208</v>
       </c>
-      <c r="B15" s="1" t="n">
+      <c r="B15" s="2" t="n">
         <v>41219</v>
       </c>
       <c r="C15" t="n">
@@ -11087,10 +11099,10 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="1" t="n">
+      <c r="A16" s="2" t="n">
         <v>41320</v>
       </c>
-      <c r="B16" s="1" t="n">
+      <c r="B16" s="2" t="n">
         <v>41332</v>
       </c>
       <c r="C16" t="n">
@@ -11119,10 +11131,10 @@
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="1" t="n">
+      <c r="A17" s="2" t="n">
         <v>41390</v>
       </c>
-      <c r="B17" s="1" t="n">
+      <c r="B17" s="2" t="n">
         <v>41402</v>
       </c>
       <c r="C17" t="n">
@@ -11151,10 +11163,10 @@
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="1" t="n">
+      <c r="A18" s="2" t="n">
         <v>41474</v>
       </c>
-      <c r="B18" s="1" t="n">
+      <c r="B18" s="2" t="n">
         <v>41487</v>
       </c>
       <c r="C18" t="n">
@@ -11183,10 +11195,10 @@
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="1" t="n">
+      <c r="A19" s="2" t="n">
         <v>41565</v>
       </c>
-      <c r="B19" s="1" t="n">
+      <c r="B19" s="2" t="n">
         <v>41578</v>
       </c>
       <c r="C19" t="n">
@@ -11215,10 +11227,10 @@
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="1" t="n">
+      <c r="A20" s="2" t="n">
         <v>41684</v>
       </c>
-      <c r="B20" s="1" t="n">
+      <c r="B20" s="2" t="n">
         <v>41695</v>
       </c>
       <c r="C20" t="n">
@@ -11247,10 +11259,10 @@
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="1" t="n">
+      <c r="A21" s="2" t="n">
         <v>41754</v>
       </c>
-      <c r="B21" s="1" t="n">
+      <c r="B21" s="2" t="n">
         <v>41766</v>
       </c>
       <c r="C21" t="n">
@@ -11279,10 +11291,10 @@
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="1" t="n">
+      <c r="A22" s="2" t="n">
         <v>41845</v>
       </c>
-      <c r="B22" s="1" t="n">
+      <c r="B22" s="2" t="n">
         <v>41855</v>
       </c>
       <c r="C22" t="n">
@@ -11311,10 +11323,10 @@
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="1" t="n">
+      <c r="A23" s="2" t="n">
         <v>41943</v>
       </c>
-      <c r="B23" s="1" t="n">
+      <c r="B23" s="2" t="n">
         <v>41948</v>
       </c>
       <c r="C23" t="n">
@@ -11343,10 +11355,10 @@
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="1" t="n">
+      <c r="A24" s="2" t="n">
         <v>42048</v>
       </c>
-      <c r="B24" s="1" t="n">
+      <c r="B24" s="2" t="n">
         <v>42060</v>
       </c>
       <c r="C24" t="n">
@@ -11375,10 +11387,10 @@
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="1" t="n">
+      <c r="A25" s="2" t="n">
         <v>42124</v>
       </c>
-      <c r="B25" s="1" t="n">
+      <c r="B25" s="2" t="n">
         <v>42132</v>
       </c>
       <c r="C25" t="n">
@@ -11407,10 +11419,10 @@
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="1" t="n">
+      <c r="A26" s="2" t="n">
         <v>42216</v>
       </c>
-      <c r="B26" s="1" t="n">
+      <c r="B26" s="2" t="n">
         <v>42221</v>
       </c>
       <c r="C26" t="n">
@@ -11439,10 +11451,10 @@
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="1" t="n">
+      <c r="A27" s="2" t="n">
         <v>42307</v>
       </c>
-      <c r="B27" s="1" t="n">
+      <c r="B27" s="2" t="n">
         <v>42312</v>
       </c>
       <c r="C27" t="n">
@@ -11471,10 +11483,10 @@
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="1" t="n">
+      <c r="A28" s="2" t="n">
         <v>42412</v>
       </c>
-      <c r="B28" s="1" t="n">
+      <c r="B28" s="2" t="n">
         <v>42424</v>
       </c>
       <c r="C28" t="n">
@@ -11503,10 +11515,10 @@
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="1" t="n">
+      <c r="A29" s="2" t="n">
         <v>42489</v>
       </c>
-      <c r="B29" s="1" t="n">
+      <c r="B29" s="2" t="n">
         <v>42496</v>
       </c>
       <c r="C29" t="n">
@@ -11535,10 +11547,10 @@
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="1" t="n">
+      <c r="A30" s="2" t="n">
         <v>42582</v>
       </c>
-      <c r="B30" s="1" t="n">
+      <c r="B30" s="2" t="n">
         <v>42587</v>
       </c>
       <c r="C30" t="n">
@@ -11567,10 +11579,10 @@
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="1" t="n">
+      <c r="A31" s="2" t="n">
         <v>42674</v>
       </c>
-      <c r="B31" s="1" t="n">
+      <c r="B31" s="2" t="n">
         <v>42681</v>
       </c>
       <c r="C31" t="n">
@@ -11599,10 +11611,10 @@
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="1" t="n">
+      <c r="A32" s="2" t="n">
         <v>42782</v>
       </c>
-      <c r="B32" s="1" t="n">
+      <c r="B32" s="2" t="n">
         <v>42793</v>
       </c>
       <c r="C32" t="n">
@@ -11631,10 +11643,10 @@
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="1" t="n">
+      <c r="A33" s="2" t="n">
         <v>42853</v>
       </c>
-      <c r="B33" s="1" t="n">
+      <c r="B33" s="2" t="n">
         <v>42865</v>
       </c>
       <c r="C33" t="n">
@@ -11663,10 +11675,10 @@
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="1" t="n">
+      <c r="A34" s="2" t="n">
         <v>42947</v>
       </c>
-      <c r="B34" s="1" t="n">
+      <c r="B34" s="2" t="n">
         <v>42954</v>
       </c>
       <c r="C34" t="n">
@@ -11695,10 +11707,10 @@
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="1" t="n">
+      <c r="A35" s="2" t="n">
         <v>43039</v>
       </c>
-      <c r="B35" s="1" t="n">
+      <c r="B35" s="2" t="n">
         <v>43046</v>
       </c>
       <c r="C35" t="n">
@@ -11727,10 +11739,10 @@
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="1" t="n">
+      <c r="A36" s="2" t="n">
         <v>43146</v>
       </c>
-      <c r="B36" s="1" t="n">
+      <c r="B36" s="2" t="n">
         <v>43158</v>
       </c>
       <c r="C36" t="n">
@@ -11759,10 +11771,10 @@
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="1" t="n">
+      <c r="A37" s="2" t="n">
         <v>43220</v>
       </c>
-      <c r="B37" s="1" t="n">
+      <c r="B37" s="2" t="n">
         <v>43229</v>
       </c>
       <c r="C37" t="n">
@@ -11791,10 +11803,10 @@
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="1" t="n">
+      <c r="A38" s="2" t="n">
         <v>43311</v>
       </c>
-      <c r="B38" s="1" t="n">
+      <c r="B38" s="2" t="n">
         <v>43318</v>
       </c>
       <c r="C38" t="n">
@@ -11823,10 +11835,10 @@
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="1" t="n">
+      <c r="A39" s="2" t="n">
         <v>43403</v>
       </c>
-      <c r="B39" s="1" t="n">
+      <c r="B39" s="2" t="n">
         <v>43410</v>
       </c>
       <c r="C39" t="n">
@@ -11855,10 +11867,10 @@
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="1" t="n">
+      <c r="A40" s="2" t="n">
         <v>43511</v>
       </c>
-      <c r="B40" s="1" t="n">
+      <c r="B40" s="2" t="n">
         <v>43522</v>
       </c>
       <c r="C40" t="n">
@@ -11887,10 +11899,10 @@
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="1" t="n">
+      <c r="A41" s="2" t="n">
         <v>43585</v>
       </c>
-      <c r="B41" s="1" t="n">
+      <c r="B41" s="2" t="n">
         <v>43593</v>
       </c>
       <c r="C41" t="n">
@@ -11919,10 +11931,10 @@
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="1" t="n">
+      <c r="A42" s="2" t="n">
         <v>43676</v>
       </c>
-      <c r="B42" s="1" t="n">
+      <c r="B42" s="2" t="n">
         <v>43683</v>
       </c>
       <c r="C42" t="n">
@@ -11951,10 +11963,10 @@
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="1" t="n">
+      <c r="A43" s="2" t="n">
         <v>43767</v>
       </c>
-      <c r="B43" s="1" t="n">
+      <c r="B43" s="2" t="n">
         <v>43774</v>
       </c>
       <c r="C43" t="n">
@@ -11983,10 +11995,10 @@
       </c>
     </row>
     <row r="44">
-      <c r="A44" s="1" t="n">
+      <c r="A44" s="2" t="n">
         <v>43879</v>
       </c>
-      <c r="B44" s="1" t="n">
+      <c r="B44" s="2" t="n">
         <v>43886</v>
       </c>
       <c r="C44" t="n">
@@ -12015,10 +12027,10 @@
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="1" t="n">
+      <c r="A45" s="2" t="n">
         <v>43951</v>
       </c>
-      <c r="B45" s="1" t="n">
+      <c r="B45" s="2" t="n">
         <v>43957</v>
       </c>
       <c r="C45" t="n">
@@ -12047,10 +12059,10 @@
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="1" t="n">
+      <c r="A46" s="2" t="n">
         <v>44043</v>
       </c>
-      <c r="B46" s="1" t="n">
+      <c r="B46" s="2" t="n">
         <v>44049</v>
       </c>
       <c r="C46" t="n">
@@ -12079,10 +12091,10 @@
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="1" t="n">
+      <c r="A47" s="2" t="n">
         <v>44134</v>
       </c>
-      <c r="B47" s="1" t="n">
+      <c r="B47" s="2" t="n">
         <v>44139</v>
       </c>
       <c r="C47" t="n">
@@ -12111,10 +12123,10 @@
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="1" t="n">
+      <c r="A48" s="2" t="n">
         <v>44245</v>
       </c>
-      <c r="B48" s="1" t="n">
+      <c r="B48" s="2" t="n">
         <v>44252</v>
       </c>
       <c r="C48" t="n">
@@ -12143,10 +12155,10 @@
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="1" t="n">
+      <c r="A49" s="2" t="n">
         <v>44316</v>
       </c>
-      <c r="B49" s="1" t="n">
+      <c r="B49" s="2" t="n">
         <v>44322</v>
       </c>
       <c r="C49" t="n">
@@ -12175,10 +12187,10 @@
       </c>
     </row>
     <row r="50">
-      <c r="A50" s="1" t="n">
+      <c r="A50" s="2" t="n">
         <v>44407</v>
       </c>
-      <c r="B50" s="1" t="n">
+      <c r="B50" s="2" t="n">
         <v>44413</v>
       </c>
       <c r="C50" t="n">
@@ -12207,10 +12219,10 @@
       </c>
     </row>
     <row r="51">
-      <c r="A51" s="1" t="n">
+      <c r="A51" s="2" t="n">
         <v>44498</v>
       </c>
-      <c r="B51" s="1" t="n">
+      <c r="B51" s="2" t="n">
         <v>44503</v>
       </c>
       <c r="C51" t="n">
@@ -12239,10 +12251,10 @@
       </c>
     </row>
     <row r="52">
-      <c r="A52" s="1" t="n">
+      <c r="A52" s="2" t="n">
         <v>44610</v>
       </c>
-      <c r="B52" s="1" t="n">
+      <c r="B52" s="2" t="n">
         <v>44615</v>
       </c>
       <c r="C52" t="n">
@@ -12271,10 +12283,10 @@
       </c>
     </row>
     <row r="53">
-      <c r="A53" s="1" t="n">
+      <c r="A53" s="2" t="n">
         <v>44680</v>
       </c>
-      <c r="B53" s="1" t="n">
+      <c r="B53" s="2" t="n">
         <v>44685</v>
       </c>
       <c r="C53" t="n">
@@ -12303,10 +12315,10 @@
       </c>
     </row>
     <row r="54">
-      <c r="A54" s="1" t="n">
+      <c r="A54" s="2" t="n">
         <v>44771</v>
       </c>
-      <c r="B54" s="1" t="n">
+      <c r="B54" s="2" t="n">
         <v>44781</v>
       </c>
       <c r="C54" t="n">
@@ -12335,10 +12347,10 @@
       </c>
     </row>
     <row r="55">
-      <c r="A55" s="1" t="n">
+      <c r="A55" s="2" t="n">
         <v>44865</v>
       </c>
-      <c r="B55" s="1" t="n">
+      <c r="B55" s="2" t="n">
         <v>44867</v>
       </c>
       <c r="C55" t="n">
@@ -12367,10 +12379,10 @@
       </c>
     </row>
     <row r="56">
-      <c r="A56" s="1" t="n">
+      <c r="A56" s="2" t="n">
         <v>44974</v>
       </c>
-      <c r="B56" s="1" t="n">
+      <c r="B56" s="2" t="n">
         <v>44979</v>
       </c>
       <c r="C56" t="n">
@@ -12399,10 +12411,10 @@
       </c>
     </row>
     <row r="57">
-      <c r="A57" s="1" t="n">
+      <c r="A57" s="2" t="n">
         <v>45044</v>
       </c>
-      <c r="B57" s="1" t="n">
+      <c r="B57" s="2" t="n">
         <v>45049</v>
       </c>
       <c r="C57" t="n">
@@ -12431,10 +12443,10 @@
       </c>
     </row>
     <row r="58">
-      <c r="A58" s="1" t="n">
+      <c r="A58" s="2" t="n">
         <v>45138</v>
       </c>
-      <c r="B58" s="1" t="n">
+      <c r="B58" s="2" t="n">
         <v>45142</v>
       </c>
       <c r="C58" t="n">
@@ -12463,10 +12475,10 @@
       </c>
     </row>
     <row r="59">
-      <c r="A59" s="1" t="n">
+      <c r="A59" s="2" t="n">
         <v>45230</v>
       </c>
-      <c r="B59" s="1" t="n">
+      <c r="B59" s="2" t="n">
         <v>45237</v>
       </c>
       <c r="C59" t="n">
@@ -12495,10 +12507,10 @@
       </c>
     </row>
     <row r="60">
-      <c r="A60" s="1" t="n">
+      <c r="A60" s="2" t="n">
         <v>45338</v>
       </c>
-      <c r="B60" s="1" t="n">
+      <c r="B60" s="2" t="n">
         <v>45345</v>
       </c>
       <c r="C60" t="n">
@@ -12527,10 +12539,10 @@
       </c>
     </row>
     <row r="61">
-      <c r="A61" s="1" t="n">
+      <c r="A61" s="2" t="n">
         <v>45412</v>
       </c>
-      <c r="B61" s="1" t="n">
+      <c r="B61" s="2" t="n">
         <v>45420</v>
       </c>
       <c r="C61" t="n">
@@ -12559,10 +12571,10 @@
       </c>
     </row>
     <row r="62">
-      <c r="A62" s="1" t="n">
+      <c r="A62" s="2" t="n">
         <v>45504</v>
       </c>
-      <c r="B62" s="1" t="n">
+      <c r="B62" s="2" t="n">
         <v>45512</v>
       </c>
       <c r="C62" t="n">
@@ -12591,10 +12603,10 @@
       </c>
     </row>
     <row r="63">
-      <c r="A63" s="1" t="n">
+      <c r="A63" s="2" t="n">
         <v>45596</v>
       </c>
-      <c r="B63" s="1" t="n">
+      <c r="B63" s="2" t="n">
         <v>45608</v>
       </c>
       <c r="C63" t="n">
@@ -12623,10 +12635,10 @@
       </c>
     </row>
     <row r="64">
-      <c r="A64" s="1" t="n">
+      <c r="A64" s="2" t="n">
         <v>45709</v>
       </c>
-      <c r="B64" s="1" t="n">
+      <c r="B64" s="2" t="n">
         <v>45716</v>
       </c>
       <c r="C64" t="n">
@@ -12655,10 +12667,10 @@
       </c>
     </row>
     <row r="65">
-      <c r="A65" s="1" t="n">
+      <c r="A65" s="2" t="n">
         <v>45777</v>
       </c>
-      <c r="B65" s="1" t="n">
+      <c r="B65" s="2" t="n">
         <v>45784</v>
       </c>
       <c r="C65" t="n">
@@ -12687,10 +12699,10 @@
       </c>
     </row>
     <row r="66">
-      <c r="A66" s="1" t="n">
+      <c r="A66" s="2" t="n">
         <v>45869</v>
       </c>
-      <c r="B66" s="1" t="n">
+      <c r="B66" s="2" t="n">
         <v>45876</v>
       </c>
       <c r="C66" t="n">
@@ -12719,10 +12731,10 @@
       </c>
     </row>
     <row r="67">
-      <c r="A67" s="1" t="n">
+      <c r="A67" s="2" t="n">
         <v>45961</v>
       </c>
-      <c r="B67" s="1" t="n">
+      <c r="B67" s="2" t="n">
         <v>45968</v>
       </c>
       <c r="C67" t="n">
@@ -12751,10 +12763,10 @@
       </c>
     </row>
     <row r="68">
-      <c r="A68" s="1" t="n">
+      <c r="A68" s="2" t="n">
         <v>46066</v>
       </c>
-      <c r="B68" s="1" t="n">
+      <c r="B68" s="2" t="n">
         <v>46077</v>
       </c>
       <c r="C68" t="n">
@@ -12783,10 +12795,10 @@
       </c>
     </row>
     <row r="69">
-      <c r="A69" s="1" t="n">
+      <c r="A69" s="2" t="n">
         <v>46142</v>
       </c>
-      <c r="B69" s="1" t="n">
+      <c r="B69" s="2" t="n">
         <v>46149</v>
       </c>
       <c r="C69" t="n">
@@ -12815,10 +12827,10 @@
       </c>
     </row>
     <row r="70">
-      <c r="A70" s="1" t="n">
+      <c r="A70" s="2" t="n">
         <v>46234</v>
       </c>
-      <c r="B70" s="1" t="n">
+      <c r="B70" s="2" t="n">
         <v>46240</v>
       </c>
       <c r="C70" t="n">
@@ -12865,12 +12877,12 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>campo</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>valor</t>
         </is>

--- a/salidas/empresas/GILD.xlsx
+++ b/salidas/empresas/GILD.xlsx
@@ -517,7 +517,7 @@
         <v>38776</v>
       </c>
       <c r="B3" t="n">
-        <v>10.62440967559814</v>
+        <v>10.62441158294678</v>
       </c>
       <c r="C3" t="n">
         <v>15.56750011444092</v>
@@ -536,7 +536,7 @@
         <v>38807</v>
       </c>
       <c r="B4" t="n">
-        <v>10.61587810516357</v>
+        <v>10.61588001251221</v>
       </c>
       <c r="C4" t="n">
         <v>15.55500030517578</v>
@@ -555,7 +555,7 @@
         <v>38837</v>
       </c>
       <c r="B5" t="n">
-        <v>9.810559272766113</v>
+        <v>9.81055736541748</v>
       </c>
       <c r="C5" t="n">
         <v>14.375</v>
@@ -574,7 +574,7 @@
         <v>38868</v>
       </c>
       <c r="B6" t="n">
-        <v>9.781558036804199</v>
+        <v>9.781556129455566</v>
       </c>
       <c r="C6" t="n">
         <v>14.33250045776367</v>
@@ -593,7 +593,7 @@
         <v>38898</v>
       </c>
       <c r="B7" t="n">
-        <v>10.09378910064697</v>
+        <v>10.09378433227539</v>
       </c>
       <c r="C7" t="n">
         <v>14.78999996185303</v>
@@ -631,7 +631,7 @@
         <v>38960</v>
       </c>
       <c r="B9" t="n">
-        <v>10.8172082901001</v>
+        <v>10.81720924377441</v>
       </c>
       <c r="C9" t="n">
         <v>15.85000038146973</v>
@@ -650,7 +650,7 @@
         <v>38990</v>
       </c>
       <c r="B10" t="n">
-        <v>11.73343086242676</v>
+        <v>11.73342800140381</v>
       </c>
       <c r="C10" t="n">
         <v>17.1924991607666</v>
@@ -669,7 +669,7 @@
         <v>39021</v>
       </c>
       <c r="B11" t="n">
-        <v>11.7556095123291</v>
+        <v>11.75561237335205</v>
       </c>
       <c r="C11" t="n">
         <v>17.22500038146973</v>
@@ -688,7 +688,7 @@
         <v>39051</v>
       </c>
       <c r="B12" t="n">
-        <v>11.25399208068848</v>
+        <v>11.25399398803711</v>
       </c>
       <c r="C12" t="n">
         <v>16.48999977111816</v>
@@ -707,7 +707,7 @@
         <v>39082</v>
       </c>
       <c r="B13" t="n">
-        <v>11.07825374603271</v>
+        <v>11.07825565338135</v>
       </c>
       <c r="C13" t="n">
         <v>16.23250007629395</v>
@@ -783,7 +783,7 @@
         <v>39202</v>
       </c>
       <c r="B17" t="n">
-        <v>13.94293689727783</v>
+        <v>13.94293975830078</v>
       </c>
       <c r="C17" t="n">
         <v>20.43000030517578</v>
@@ -802,7 +802,7 @@
         <v>39233</v>
       </c>
       <c r="B18" t="n">
-        <v>14.1220874786377</v>
+        <v>14.12208366394043</v>
       </c>
       <c r="C18" t="n">
         <v>20.6924991607666</v>
@@ -821,7 +821,7 @@
         <v>39263</v>
       </c>
       <c r="B19" t="n">
-        <v>13.23998928070068</v>
+        <v>13.23999118804932</v>
       </c>
       <c r="C19" t="n">
         <v>19.39999961853027</v>
@@ -840,7 +840,7 @@
         <v>39294</v>
       </c>
       <c r="B20" t="n">
-        <v>12.70424842834473</v>
+        <v>12.70424747467041</v>
       </c>
       <c r="C20" t="n">
         <v>18.61499977111816</v>
@@ -878,7 +878,7 @@
         <v>39355</v>
       </c>
       <c r="B22" t="n">
-        <v>13.94635200500488</v>
+        <v>13.94634819030762</v>
       </c>
       <c r="C22" t="n">
         <v>20.43499946594238</v>
@@ -916,7 +916,7 @@
         <v>39416</v>
       </c>
       <c r="B24" t="n">
-        <v>15.88116645812988</v>
+        <v>15.88116550445557</v>
       </c>
       <c r="C24" t="n">
         <v>23.27000045776367</v>
@@ -935,7 +935,7 @@
         <v>39447</v>
       </c>
       <c r="B25" t="n">
-        <v>15.70030975341797</v>
+        <v>15.7003059387207</v>
       </c>
       <c r="C25" t="n">
         <v>23.0049991607666</v>
@@ -954,7 +954,7 @@
         <v>39478</v>
       </c>
       <c r="B26" t="n">
-        <v>15.59111595153809</v>
+        <v>15.59111022949219</v>
       </c>
       <c r="C26" t="n">
         <v>22.84499931335449</v>
@@ -973,7 +973,7 @@
         <v>39507</v>
       </c>
       <c r="B27" t="n">
-        <v>16.1473331451416</v>
+        <v>16.1473274230957</v>
       </c>
       <c r="C27" t="n">
         <v>23.65999984741211</v>
@@ -992,7 +992,7 @@
         <v>39538</v>
       </c>
       <c r="B28" t="n">
-        <v>17.58392715454102</v>
+        <v>17.58394050598145</v>
       </c>
       <c r="C28" t="n">
         <v>25.76499938964844</v>
@@ -1011,7 +1011,7 @@
         <v>39568</v>
       </c>
       <c r="B29" t="n">
-        <v>17.66241836547852</v>
+        <v>17.66242027282715</v>
       </c>
       <c r="C29" t="n">
         <v>25.8799991607666</v>
@@ -1030,7 +1030,7 @@
         <v>39599</v>
       </c>
       <c r="B30" t="n">
-        <v>18.87722015380859</v>
+        <v>18.87722778320312</v>
       </c>
       <c r="C30" t="n">
         <v>27.65999984741211</v>
@@ -1049,7 +1049,7 @@
         <v>39629</v>
       </c>
       <c r="B31" t="n">
-        <v>18.06848907470703</v>
+        <v>18.06849098205566</v>
       </c>
       <c r="C31" t="n">
         <v>26.47500038146973</v>
@@ -1068,7 +1068,7 @@
         <v>39660</v>
       </c>
       <c r="B32" t="n">
-        <v>18.41996574401855</v>
+        <v>18.41996955871582</v>
       </c>
       <c r="C32" t="n">
         <v>26.98999977111816</v>
@@ -1106,7 +1106,7 @@
         <v>39721</v>
       </c>
       <c r="B34" t="n">
-        <v>15.57063293457031</v>
+        <v>15.57064247131348</v>
       </c>
       <c r="C34" t="n">
         <v>22.81500053405762</v>
@@ -1125,7 +1125,7 @@
         <v>39752</v>
       </c>
       <c r="B35" t="n">
-        <v>15.64570426940918</v>
+        <v>15.64571189880371</v>
       </c>
       <c r="C35" t="n">
         <v>22.92499923706055</v>
@@ -1144,7 +1144,7 @@
         <v>39782</v>
       </c>
       <c r="B36" t="n">
-        <v>15.28400325775146</v>
+        <v>15.28399562835693</v>
       </c>
       <c r="C36" t="n">
         <v>22.39500045776367</v>
@@ -1163,7 +1163,7 @@
         <v>39813</v>
       </c>
       <c r="B37" t="n">
-        <v>17.45085144042969</v>
+        <v>17.45085334777832</v>
       </c>
       <c r="C37" t="n">
         <v>25.56999969482422</v>
@@ -1201,7 +1201,7 @@
         <v>39872</v>
       </c>
       <c r="B39" t="n">
-        <v>15.28740787506104</v>
+        <v>15.28741073608398</v>
       </c>
       <c r="C39" t="n">
         <v>22.39999961853027</v>
@@ -1220,7 +1220,7 @@
         <v>39903</v>
       </c>
       <c r="B40" t="n">
-        <v>15.80608749389648</v>
+        <v>15.8060998916626</v>
       </c>
       <c r="C40" t="n">
         <v>23.15999984741211</v>
@@ -1239,7 +1239,7 @@
         <v>39933</v>
       </c>
       <c r="B41" t="n">
-        <v>15.62864971160889</v>
+        <v>15.62864398956299</v>
       </c>
       <c r="C41" t="n">
         <v>22.89999961853027</v>
@@ -1258,7 +1258,7 @@
         <v>39964</v>
       </c>
       <c r="B42" t="n">
-        <v>14.70730590820312</v>
+        <v>14.70730876922607</v>
       </c>
       <c r="C42" t="n">
         <v>21.54999923706055</v>
@@ -1277,7 +1277,7 @@
         <v>39994</v>
       </c>
       <c r="B43" t="n">
-        <v>15.98353290557861</v>
+        <v>15.98353004455566</v>
       </c>
       <c r="C43" t="n">
         <v>23.42000007629395</v>
@@ -1296,7 +1296,7 @@
         <v>40025</v>
       </c>
       <c r="B44" t="n">
-        <v>16.69672584533691</v>
+        <v>16.69672393798828</v>
       </c>
       <c r="C44" t="n">
         <v>24.46500015258789</v>
@@ -1315,7 +1315,7 @@
         <v>40056</v>
       </c>
       <c r="B45" t="n">
-        <v>15.37613010406494</v>
+        <v>15.37613677978516</v>
       </c>
       <c r="C45" t="n">
         <v>22.53000068664551</v>
@@ -1365,7 +1365,7 @@
         <v>40117</v>
       </c>
       <c r="B47" t="n">
-        <v>14.51962375640869</v>
+        <v>14.51962184906006</v>
       </c>
       <c r="C47" t="n">
         <v>21.27499961853027</v>
@@ -1390,7 +1390,7 @@
         <v>40147</v>
       </c>
       <c r="B48" t="n">
-        <v>15.73443222045898</v>
+        <v>15.73443031311035</v>
       </c>
       <c r="C48" t="n">
         <v>23.05500030517578</v>
@@ -1415,7 +1415,7 @@
         <v>40178</v>
       </c>
       <c r="B49" t="n">
-        <v>14.76531219482422</v>
+        <v>14.76531600952148</v>
       </c>
       <c r="C49" t="n">
         <v>21.63500022888184</v>
@@ -1440,7 +1440,7 @@
         <v>40209</v>
       </c>
       <c r="B50" t="n">
-        <v>16.47150421142578</v>
+        <v>16.47150039672852</v>
       </c>
       <c r="C50" t="n">
         <v>24.13500022888184</v>
@@ -1490,7 +1490,7 @@
         <v>40268</v>
       </c>
       <c r="B52" t="n">
-        <v>15.51604080200195</v>
+        <v>15.51604652404785</v>
       </c>
       <c r="C52" t="n">
         <v>22.73500061035156</v>
@@ -1515,7 +1515,7 @@
         <v>40298</v>
       </c>
       <c r="B53" t="n">
-        <v>13.55051326751709</v>
+        <v>13.55051422119141</v>
       </c>
       <c r="C53" t="n">
         <v>19.85499954223633</v>
@@ -1540,7 +1540,7 @@
         <v>40329</v>
       </c>
       <c r="B54" t="n">
-        <v>12.25722599029541</v>
+        <v>12.25722312927246</v>
       </c>
       <c r="C54" t="n">
         <v>17.95999908447266</v>
@@ -1565,7 +1565,7 @@
         <v>40359</v>
       </c>
       <c r="B55" t="n">
-        <v>11.69759941101074</v>
+        <v>11.69759750366211</v>
       </c>
       <c r="C55" t="n">
         <v>17.13999938964844</v>
@@ -1590,7 +1590,7 @@
         <v>40390</v>
       </c>
       <c r="B56" t="n">
-        <v>11.37001037597656</v>
+        <v>11.37001132965088</v>
       </c>
       <c r="C56" t="n">
         <v>16.65999984741211</v>
@@ -1615,7 +1615,7 @@
         <v>40421</v>
       </c>
       <c r="B57" t="n">
-        <v>10.86156845092773</v>
+        <v>10.86157035827637</v>
       </c>
       <c r="C57" t="n">
         <v>15.91499996185303</v>
@@ -1665,7 +1665,7 @@
         <v>40482</v>
       </c>
       <c r="B59" t="n">
-        <v>13.53686428070068</v>
+        <v>13.53687000274658</v>
       </c>
       <c r="C59" t="n">
         <v>19.83499908447266</v>
@@ -1690,7 +1690,7 @@
         <v>40512</v>
       </c>
       <c r="B60" t="n">
-        <v>12.45514392852783</v>
+        <v>12.45514583587646</v>
       </c>
       <c r="C60" t="n">
         <v>18.25</v>
@@ -1715,7 +1715,7 @@
         <v>40543</v>
       </c>
       <c r="B61" t="n">
-        <v>12.36642265319824</v>
+        <v>12.36642456054688</v>
       </c>
       <c r="C61" t="n">
         <v>18.1200008392334</v>
@@ -1740,7 +1740,7 @@
         <v>40574</v>
       </c>
       <c r="B62" t="n">
-        <v>13.09667301177979</v>
+        <v>13.09666728973389</v>
       </c>
       <c r="C62" t="n">
         <v>19.19000053405762</v>
@@ -1765,7 +1765,7 @@
         <v>40602</v>
       </c>
       <c r="B63" t="n">
-        <v>13.30141448974609</v>
+        <v>13.30141067504883</v>
       </c>
       <c r="C63" t="n">
         <v>19.48999977111816</v>
@@ -1794,7 +1794,7 @@
         <v>40633</v>
       </c>
       <c r="B64" t="n">
-        <v>14.49233055114746</v>
+        <v>14.49233245849609</v>
       </c>
       <c r="C64" t="n">
         <v>21.23500061035156</v>
@@ -1823,7 +1823,7 @@
         <v>40663</v>
       </c>
       <c r="B65" t="n">
-        <v>13.25363636016846</v>
+        <v>13.25364017486572</v>
       </c>
       <c r="C65" t="n">
         <v>19.42000007629395</v>
@@ -1852,7 +1852,7 @@
         <v>40694</v>
       </c>
       <c r="B66" t="n">
-        <v>14.24322700500488</v>
+        <v>14.24322414398193</v>
       </c>
       <c r="C66" t="n">
         <v>20.8700008392334</v>
@@ -1881,7 +1881,7 @@
         <v>40724</v>
       </c>
       <c r="B67" t="n">
-        <v>14.13061618804932</v>
+        <v>14.13062191009521</v>
       </c>
       <c r="C67" t="n">
         <v>20.70499992370605</v>
@@ -1910,7 +1910,7 @@
         <v>40755</v>
       </c>
       <c r="B68" t="n">
-        <v>14.45479488372803</v>
+        <v>14.45479393005371</v>
       </c>
       <c r="C68" t="n">
         <v>21.18000030517578</v>
@@ -1939,7 +1939,7 @@
         <v>40786</v>
       </c>
       <c r="B69" t="n">
-        <v>13.6085262298584</v>
+        <v>13.60852336883545</v>
       </c>
       <c r="C69" t="n">
         <v>19.94000053405762</v>
@@ -1968,7 +1968,7 @@
         <v>40816</v>
       </c>
       <c r="B70" t="n">
-        <v>13.23998928070068</v>
+        <v>13.23999118804932</v>
       </c>
       <c r="C70" t="n">
         <v>19.39999961853027</v>
@@ -1997,7 +1997,7 @@
         <v>40847</v>
       </c>
       <c r="B71" t="n">
-        <v>14.21592617034912</v>
+        <v>14.21592903137207</v>
       </c>
       <c r="C71" t="n">
         <v>20.82999992370605</v>
@@ -2026,7 +2026,7 @@
         <v>40877</v>
       </c>
       <c r="B72" t="n">
-        <v>13.59828948974609</v>
+        <v>13.59829139709473</v>
       </c>
       <c r="C72" t="n">
         <v>19.92499923706055</v>
@@ -2055,7 +2055,7 @@
         <v>40908</v>
       </c>
       <c r="B73" t="n">
-        <v>13.96682834625244</v>
+        <v>13.96683025360107</v>
       </c>
       <c r="C73" t="n">
         <v>20.46500015258789</v>
@@ -2084,7 +2084,7 @@
         <v>40939</v>
       </c>
       <c r="B74" t="n">
-        <v>16.67283248901367</v>
+        <v>16.6728343963623</v>
       </c>
       <c r="C74" t="n">
         <v>24.43000030517578</v>
@@ -2113,7 +2113,7 @@
         <v>40968</v>
       </c>
       <c r="B75" t="n">
-        <v>15.53992652893066</v>
+        <v>15.53993034362793</v>
       </c>
       <c r="C75" t="n">
         <v>22.77000045776367</v>
@@ -2142,7 +2142,7 @@
         <v>40999</v>
       </c>
       <c r="B76" t="n">
-        <v>16.67283248901367</v>
+        <v>16.6728343963623</v>
       </c>
       <c r="C76" t="n">
         <v>24.43000030517578</v>
@@ -2171,7 +2171,7 @@
         <v>41029</v>
       </c>
       <c r="B77" t="n">
-        <v>17.75113868713379</v>
+        <v>17.75113487243652</v>
       </c>
       <c r="C77" t="n">
         <v>26.01000022888184</v>
@@ -2200,7 +2200,7 @@
         <v>41060</v>
       </c>
       <c r="B78" t="n">
-        <v>17.04478645324707</v>
+        <v>17.04477691650391</v>
       </c>
       <c r="C78" t="n">
         <v>24.97500038146973</v>
@@ -2229,7 +2229,7 @@
         <v>41090</v>
       </c>
       <c r="B79" t="n">
-        <v>17.49862670898438</v>
+        <v>17.49862289428711</v>
       </c>
       <c r="C79" t="n">
         <v>25.63999938964844</v>
@@ -2258,7 +2258,7 @@
         <v>41121</v>
       </c>
       <c r="B80" t="n">
-        <v>18.53939819335938</v>
+        <v>18.53940200805664</v>
       </c>
       <c r="C80" t="n">
         <v>27.16500091552734</v>
@@ -2316,7 +2316,7 @@
         <v>41182</v>
       </c>
       <c r="B82" t="n">
-        <v>22.63423728942871</v>
+        <v>22.63424110412598</v>
       </c>
       <c r="C82" t="n">
         <v>33.16500091552734</v>
@@ -2345,7 +2345,7 @@
         <v>41213</v>
       </c>
       <c r="B83" t="n">
-        <v>22.92429733276367</v>
+        <v>22.92429542541504</v>
       </c>
       <c r="C83" t="n">
         <v>33.59000015258789</v>
@@ -2374,7 +2374,7 @@
         <v>41243</v>
       </c>
       <c r="B84" t="n">
-        <v>25.5927619934082</v>
+        <v>25.5927677154541</v>
       </c>
       <c r="C84" t="n">
         <v>37.5</v>
@@ -2403,7 +2403,7 @@
         <v>41274</v>
       </c>
       <c r="B85" t="n">
-        <v>25.06384658813477</v>
+        <v>25.0638484954834</v>
       </c>
       <c r="C85" t="n">
         <v>36.72499847412109</v>
@@ -2432,7 +2432,7 @@
         <v>41305</v>
       </c>
       <c r="B86" t="n">
-        <v>26.92359352111816</v>
+        <v>26.923583984375</v>
       </c>
       <c r="C86" t="n">
         <v>39.45000076293945</v>
@@ -2461,7 +2461,7 @@
         <v>41333</v>
       </c>
       <c r="B87" t="n">
-        <v>29.1552791595459</v>
+        <v>29.1552734375</v>
       </c>
       <c r="C87" t="n">
         <v>42.72000122070312</v>
@@ -2490,7 +2490,7 @@
         <v>41364</v>
       </c>
       <c r="B88" t="n">
-        <v>33.40026092529297</v>
+        <v>33.40026473999023</v>
       </c>
       <c r="C88" t="n">
         <v>48.93999862670898</v>
@@ -2519,7 +2519,7 @@
         <v>41394</v>
       </c>
       <c r="B89" t="n">
-        <v>34.56045913696289</v>
+        <v>34.56047058105469</v>
       </c>
       <c r="C89" t="n">
         <v>50.63999938964844</v>
@@ -2548,7 +2548,7 @@
         <v>41425</v>
       </c>
       <c r="B90" t="n">
-        <v>37.18117523193359</v>
+        <v>37.18116760253906</v>
       </c>
       <c r="C90" t="n">
         <v>54.47999954223633</v>
@@ -2577,7 +2577,7 @@
         <v>41455</v>
       </c>
       <c r="B91" t="n">
-        <v>34.99043655395508</v>
+        <v>34.99042510986328</v>
       </c>
       <c r="C91" t="n">
         <v>51.27000045776367</v>
@@ -2606,7 +2606,7 @@
         <v>41486</v>
       </c>
       <c r="B92" t="n">
-        <v>41.90387725830078</v>
+        <v>41.90388870239258</v>
       </c>
       <c r="C92" t="n">
         <v>61.40000152587891</v>
@@ -2664,7 +2664,7 @@
         <v>41547</v>
       </c>
       <c r="B94" t="n">
-        <v>42.90712356567383</v>
+        <v>42.90711975097656</v>
       </c>
       <c r="C94" t="n">
         <v>62.86999893188477</v>
@@ -2693,7 +2693,7 @@
         <v>41578</v>
       </c>
       <c r="B95" t="n">
-        <v>48.57848739624023</v>
+        <v>48.57847595214844</v>
       </c>
       <c r="C95" t="n">
         <v>71.18000030517578</v>
@@ -2722,7 +2722,7 @@
         <v>41608</v>
       </c>
       <c r="B96" t="n">
-        <v>51.05585098266602</v>
+        <v>51.05585861206055</v>
       </c>
       <c r="C96" t="n">
         <v>74.80999755859375</v>
@@ -2751,7 +2751,7 @@
         <v>41639</v>
       </c>
       <c r="B97" t="n">
-        <v>51.2537727355957</v>
+        <v>51.2537841796875</v>
       </c>
       <c r="C97" t="n">
         <v>75.09999847412109</v>
@@ -2780,7 +2780,7 @@
         <v>41670</v>
       </c>
       <c r="B98" t="n">
-        <v>55.04150009155273</v>
+        <v>55.04150390625</v>
       </c>
       <c r="C98" t="n">
         <v>80.65000152587891</v>
@@ -2809,7 +2809,7 @@
         <v>41698</v>
       </c>
       <c r="B99" t="n">
-        <v>56.50199890136719</v>
+        <v>56.50198745727539</v>
       </c>
       <c r="C99" t="n">
         <v>82.79000091552734</v>
@@ -2838,7 +2838,7 @@
         <v>41729</v>
       </c>
       <c r="B100" t="n">
-        <v>48.36009216308594</v>
+        <v>48.36008071899414</v>
       </c>
       <c r="C100" t="n">
         <v>70.86000061035156</v>
@@ -2867,7 +2867,7 @@
         <v>41759</v>
       </c>
       <c r="B101" t="n">
-        <v>53.56735610961914</v>
+        <v>53.5673713684082</v>
       </c>
       <c r="C101" t="n">
         <v>78.48999786376953</v>
@@ -2896,7 +2896,7 @@
         <v>41790</v>
       </c>
       <c r="B102" t="n">
-        <v>55.4237174987793</v>
+        <v>55.42370223999023</v>
       </c>
       <c r="C102" t="n">
         <v>81.20999908447266</v>
@@ -2954,7 +2954,7 @@
         <v>41851</v>
       </c>
       <c r="B104" t="n">
-        <v>62.48048400878906</v>
+        <v>62.48046875</v>
       </c>
       <c r="C104" t="n">
         <v>91.55000305175781</v>
@@ -2983,7 +2983,7 @@
         <v>41882</v>
       </c>
       <c r="B105" t="n">
-        <v>73.4068603515625</v>
+        <v>73.40689086914062</v>
       </c>
       <c r="C105" t="n">
         <v>107.5599975585938</v>
@@ -3041,7 +3041,7 @@
         <v>41943</v>
       </c>
       <c r="B107" t="n">
-        <v>76.43705749511719</v>
+        <v>76.43704223632812</v>
       </c>
       <c r="C107" t="n">
         <v>112</v>
@@ -3070,7 +3070,7 @@
         <v>41973</v>
       </c>
       <c r="B108" t="n">
-        <v>68.46576690673828</v>
+        <v>68.46577453613281</v>
       </c>
       <c r="C108" t="n">
         <v>100.3199996948242</v>
@@ -3099,7 +3099,7 @@
         <v>42004</v>
       </c>
       <c r="B109" t="n">
-        <v>64.33000183105469</v>
+        <v>64.32996368408203</v>
       </c>
       <c r="C109" t="n">
         <v>94.26000213623047</v>
@@ -3128,7 +3128,7 @@
         <v>42035</v>
       </c>
       <c r="B110" t="n">
-        <v>71.54372406005859</v>
+        <v>71.54370880126953</v>
       </c>
       <c r="C110" t="n">
         <v>104.8300018310547</v>
@@ -3157,7 +3157,7 @@
         <v>42063</v>
       </c>
       <c r="B111" t="n">
-        <v>70.65651702880859</v>
+        <v>70.65650177001953</v>
       </c>
       <c r="C111" t="n">
         <v>103.5299987792969</v>
@@ -3186,7 +3186,7 @@
         <v>42094</v>
       </c>
       <c r="B112" t="n">
-        <v>66.97114562988281</v>
+        <v>66.97113800048828</v>
       </c>
       <c r="C112" t="n">
         <v>98.12999725341797</v>
@@ -3215,7 +3215,7 @@
         <v>42124</v>
       </c>
       <c r="B113" t="n">
-        <v>68.59544372558594</v>
+        <v>68.59542846679688</v>
       </c>
       <c r="C113" t="n">
         <v>100.5100021362305</v>
@@ -3244,7 +3244,7 @@
         <v>42155</v>
       </c>
       <c r="B114" t="n">
-        <v>76.62132263183594</v>
+        <v>76.621337890625</v>
       </c>
       <c r="C114" t="n">
         <v>112.2699966430664</v>
@@ -3273,7 +3273,7 @@
         <v>42185</v>
       </c>
       <c r="B115" t="n">
-        <v>80.19347381591797</v>
+        <v>80.19348907470703</v>
       </c>
       <c r="C115" t="n">
         <v>117.0800018310547</v>
@@ -3302,7 +3302,7 @@
         <v>42216</v>
       </c>
       <c r="B116" t="n">
-        <v>80.72775268554688</v>
+        <v>80.72773742675781</v>
       </c>
       <c r="C116" t="n">
         <v>117.8600006103516</v>
@@ -3331,7 +3331,7 @@
         <v>42247</v>
       </c>
       <c r="B117" t="n">
-        <v>71.96730804443359</v>
+        <v>71.96729278564453</v>
       </c>
       <c r="C117" t="n">
         <v>105.0699996948242</v>
@@ -3360,7 +3360,7 @@
         <v>42277</v>
       </c>
       <c r="B118" t="n">
-        <v>67.51969146728516</v>
+        <v>67.51969909667969</v>
       </c>
       <c r="C118" t="n">
         <v>98.19000244140625</v>
@@ -3389,7 +3389,7 @@
         <v>42308</v>
       </c>
       <c r="B119" t="n">
-        <v>74.35484313964844</v>
+        <v>74.35483551025391</v>
       </c>
       <c r="C119" t="n">
         <v>108.129997253418</v>
@@ -3418,7 +3418,7 @@
         <v>42338</v>
       </c>
       <c r="B120" t="n">
-        <v>72.86264038085938</v>
+        <v>72.8626708984375</v>
       </c>
       <c r="C120" t="n">
         <v>105.9599990844727</v>
@@ -3447,7 +3447,7 @@
         <v>42369</v>
       </c>
       <c r="B121" t="n">
-        <v>69.88301849365234</v>
+        <v>69.88302612304688</v>
       </c>
       <c r="C121" t="n">
         <v>101.1900024414062</v>
@@ -3476,7 +3476,7 @@
         <v>42400</v>
       </c>
       <c r="B122" t="n">
-        <v>57.32080078125</v>
+        <v>57.3207893371582</v>
       </c>
       <c r="C122" t="n">
         <v>83</v>
@@ -3505,7 +3505,7 @@
         <v>42429</v>
       </c>
       <c r="B123" t="n">
-        <v>60.25587844848633</v>
+        <v>60.25590515136719</v>
       </c>
       <c r="C123" t="n">
         <v>87.25</v>
@@ -3534,7 +3534,7 @@
         <v>42460</v>
       </c>
       <c r="B124" t="n">
-        <v>63.74536514282227</v>
+        <v>63.74535369873047</v>
       </c>
       <c r="C124" t="n">
         <v>91.86000061035156</v>
@@ -3563,7 +3563,7 @@
         <v>42490</v>
       </c>
       <c r="B125" t="n">
-        <v>61.21249008178711</v>
+        <v>61.21247863769531</v>
       </c>
       <c r="C125" t="n">
         <v>88.20999908447266</v>
@@ -3592,7 +3592,7 @@
         <v>42521</v>
       </c>
       <c r="B126" t="n">
-        <v>60.41443634033203</v>
+        <v>60.4144401550293</v>
       </c>
       <c r="C126" t="n">
         <v>87.05999755859375</v>
@@ -3621,7 +3621,7 @@
         <v>42551</v>
       </c>
       <c r="B127" t="n">
-        <v>58.21429443359375</v>
+        <v>58.21430969238281</v>
       </c>
       <c r="C127" t="n">
         <v>83.41999816894531</v>
@@ -3650,7 +3650,7 @@
         <v>42582</v>
       </c>
       <c r="B128" t="n">
-        <v>55.45781326293945</v>
+        <v>55.45782852172852</v>
       </c>
       <c r="C128" t="n">
         <v>79.47000122070312</v>
@@ -3679,7 +3679,7 @@
         <v>42613</v>
       </c>
       <c r="B129" t="n">
-        <v>54.6971549987793</v>
+        <v>54.69716644287109</v>
       </c>
       <c r="C129" t="n">
         <v>78.37999725341797</v>
@@ -3708,7 +3708,7 @@
         <v>42643</v>
       </c>
       <c r="B130" t="n">
-        <v>55.54803848266602</v>
+        <v>55.54804229736328</v>
       </c>
       <c r="C130" t="n">
         <v>79.12000274658203</v>
@@ -3737,7 +3737,7 @@
         <v>42674</v>
       </c>
       <c r="B131" t="n">
-        <v>51.69363784790039</v>
+        <v>51.69362640380859</v>
       </c>
       <c r="C131" t="n">
         <v>73.62999725341797</v>
@@ -3766,7 +3766,7 @@
         <v>42704</v>
       </c>
       <c r="B132" t="n">
-        <v>51.74277877807617</v>
+        <v>51.74279022216797</v>
       </c>
       <c r="C132" t="n">
         <v>73.69999694824219</v>
@@ -3795,7 +3795,7 @@
         <v>42735</v>
       </c>
       <c r="B133" t="n">
-        <v>50.59915161132812</v>
+        <v>50.59914398193359</v>
       </c>
       <c r="C133" t="n">
         <v>71.61000061035156</v>
@@ -3824,7 +3824,7 @@
         <v>42766</v>
       </c>
       <c r="B134" t="n">
-        <v>51.19266510009766</v>
+        <v>51.19267272949219</v>
       </c>
       <c r="C134" t="n">
         <v>72.44999694824219</v>
@@ -3853,7 +3853,7 @@
         <v>42794</v>
       </c>
       <c r="B135" t="n">
-        <v>49.80068969726562</v>
+        <v>49.80070114135742</v>
       </c>
       <c r="C135" t="n">
         <v>70.48000335693359</v>
@@ -3911,7 +3911,7 @@
         <v>42855</v>
       </c>
       <c r="B137" t="n">
-        <v>48.80966186523438</v>
+        <v>48.80967712402344</v>
       </c>
       <c r="C137" t="n">
         <v>68.55000305175781</v>
@@ -3940,7 +3940,7 @@
         <v>42886</v>
       </c>
       <c r="B138" t="n">
-        <v>46.20363235473633</v>
+        <v>46.20364761352539</v>
       </c>
       <c r="C138" t="n">
         <v>64.88999938964844</v>
@@ -3969,7 +3969,7 @@
         <v>42916</v>
       </c>
       <c r="B139" t="n">
-        <v>50.80299377441406</v>
+        <v>50.80297470092773</v>
       </c>
       <c r="C139" t="n">
         <v>70.77999877929688</v>
@@ -3998,7 +3998,7 @@
         <v>42947</v>
       </c>
       <c r="B140" t="n">
-        <v>54.61430358886719</v>
+        <v>54.61427688598633</v>
       </c>
       <c r="C140" t="n">
         <v>76.08999633789062</v>
@@ -4027,7 +4027,7 @@
         <v>42978</v>
       </c>
       <c r="B141" t="n">
-        <v>60.08361053466797</v>
+        <v>60.08363342285156</v>
       </c>
       <c r="C141" t="n">
         <v>83.70999908447266</v>
@@ -4056,7 +4056,7 @@
         <v>43008</v>
       </c>
       <c r="B142" t="n">
-        <v>58.5164794921875</v>
+        <v>58.51645278930664</v>
       </c>
       <c r="C142" t="n">
         <v>81.01999664306641</v>
@@ -4085,7 +4085,7 @@
         <v>43039</v>
       </c>
       <c r="B143" t="n">
-        <v>54.1396598815918</v>
+        <v>54.13964462280273</v>
       </c>
       <c r="C143" t="n">
         <v>74.95999908447266</v>
@@ -4114,7 +4114,7 @@
         <v>43069</v>
       </c>
       <c r="B144" t="n">
-        <v>54.0096435546875</v>
+        <v>54.00964736938477</v>
       </c>
       <c r="C144" t="n">
         <v>74.77999877929688</v>
@@ -4143,7 +4143,7 @@
         <v>43100</v>
       </c>
       <c r="B145" t="n">
-        <v>52.09553909301758</v>
+        <v>52.09552001953125</v>
       </c>
       <c r="C145" t="n">
         <v>71.63999938964844</v>
@@ -4172,7 +4172,7 @@
         <v>43131</v>
       </c>
       <c r="B146" t="n">
-        <v>60.93810653686523</v>
+        <v>60.9380989074707</v>
       </c>
       <c r="C146" t="n">
         <v>83.80000305175781</v>
@@ -4230,7 +4230,7 @@
         <v>43190</v>
       </c>
       <c r="B148" t="n">
-        <v>55.21052551269531</v>
+        <v>55.21051406860352</v>
       </c>
       <c r="C148" t="n">
         <v>75.38999938964844</v>
@@ -4259,7 +4259,7 @@
         <v>43220</v>
       </c>
       <c r="B149" t="n">
-        <v>52.89634704589844</v>
+        <v>52.89634323120117</v>
       </c>
       <c r="C149" t="n">
         <v>72.23000335693359</v>
@@ -4346,7 +4346,7 @@
         <v>43312</v>
       </c>
       <c r="B152" t="n">
-        <v>57.45680999755859</v>
+        <v>57.4567985534668</v>
       </c>
       <c r="C152" t="n">
         <v>77.83000183105469</v>
@@ -4404,7 +4404,7 @@
         <v>43373</v>
       </c>
       <c r="B154" t="n">
-        <v>57.44172668457031</v>
+        <v>57.44173049926758</v>
       </c>
       <c r="C154" t="n">
         <v>77.20999908447266</v>
@@ -4462,7 +4462,7 @@
         <v>43434</v>
       </c>
       <c r="B156" t="n">
-        <v>53.52101898193359</v>
+        <v>53.52103805541992</v>
       </c>
       <c r="C156" t="n">
         <v>71.94000244140625</v>
@@ -4491,7 +4491,7 @@
         <v>43465</v>
       </c>
       <c r="B157" t="n">
-        <v>46.92771148681641</v>
+        <v>46.92773056030273</v>
       </c>
       <c r="C157" t="n">
         <v>62.54999923706055</v>
@@ -4520,7 +4520,7 @@
         <v>43496</v>
       </c>
       <c r="B158" t="n">
-        <v>52.52453994750977</v>
+        <v>52.5245475769043</v>
       </c>
       <c r="C158" t="n">
         <v>70.01000213623047</v>
@@ -4549,7 +4549,7 @@
         <v>43524</v>
       </c>
       <c r="B159" t="n">
-        <v>48.78081512451172</v>
+        <v>48.78083801269531</v>
       </c>
       <c r="C159" t="n">
         <v>65.01999664306641</v>
@@ -4578,7 +4578,7 @@
         <v>43555</v>
       </c>
       <c r="B160" t="n">
-        <v>49.24517440795898</v>
+        <v>49.24518203735352</v>
       </c>
       <c r="C160" t="n">
         <v>65.01000213623047</v>
@@ -4636,7 +4636,7 @@
         <v>43616</v>
       </c>
       <c r="B162" t="n">
-        <v>47.15446853637695</v>
+        <v>47.15447616577148</v>
       </c>
       <c r="C162" t="n">
         <v>62.25</v>
@@ -4665,7 +4665,7 @@
         <v>43646</v>
       </c>
       <c r="B163" t="n">
-        <v>51.66420745849609</v>
+        <v>51.66419982910156</v>
       </c>
       <c r="C163" t="n">
         <v>67.55999755859375</v>
@@ -4694,7 +4694,7 @@
         <v>43677</v>
       </c>
       <c r="B164" t="n">
-        <v>50.10417938232422</v>
+        <v>50.10418701171875</v>
       </c>
       <c r="C164" t="n">
         <v>65.51999664306641</v>
@@ -4810,7 +4810,7 @@
         <v>43799</v>
       </c>
       <c r="B168" t="n">
-        <v>51.89977645874023</v>
+        <v>51.89976119995117</v>
       </c>
       <c r="C168" t="n">
         <v>67.23999786376953</v>
@@ -4839,7 +4839,7 @@
         <v>43830</v>
       </c>
       <c r="B169" t="n">
-        <v>50.62593078613281</v>
+        <v>50.62592315673828</v>
       </c>
       <c r="C169" t="n">
         <v>64.98000335693359</v>
@@ -4868,7 +4868,7 @@
         <v>43861</v>
       </c>
       <c r="B170" t="n">
-        <v>49.23913192749023</v>
+        <v>49.2391242980957</v>
       </c>
       <c r="C170" t="n">
         <v>63.20000076293945</v>
@@ -4897,7 +4897,7 @@
         <v>43890</v>
       </c>
       <c r="B171" t="n">
-        <v>54.03838729858398</v>
+        <v>54.03839492797852</v>
       </c>
       <c r="C171" t="n">
         <v>69.36000061035156</v>
@@ -4926,7 +4926,7 @@
         <v>43921</v>
       </c>
       <c r="B172" t="n">
-        <v>58.78792953491211</v>
+        <v>58.78793334960938</v>
       </c>
       <c r="C172" t="n">
         <v>74.76000213623047</v>
@@ -4955,7 +4955,7 @@
         <v>43951</v>
       </c>
       <c r="B173" t="n">
-        <v>66.05385589599609</v>
+        <v>66.05386352539062</v>
       </c>
       <c r="C173" t="n">
         <v>84</v>
@@ -5013,7 +5013,7 @@
         <v>44012</v>
       </c>
       <c r="B175" t="n">
-        <v>61.04076385498047</v>
+        <v>61.0407829284668</v>
       </c>
       <c r="C175" t="n">
         <v>76.94000244140625</v>
@@ -5071,7 +5071,7 @@
         <v>44074</v>
       </c>
       <c r="B177" t="n">
-        <v>52.95645904541016</v>
+        <v>52.95647811889648</v>
       </c>
       <c r="C177" t="n">
         <v>66.75</v>
@@ -5098,7 +5098,7 @@
         <v>44104</v>
       </c>
       <c r="B178" t="n">
-        <v>50.65739440917969</v>
+        <v>50.65738677978516</v>
       </c>
       <c r="C178" t="n">
         <v>63.18999862670898</v>
@@ -5152,7 +5152,7 @@
         <v>44165</v>
       </c>
       <c r="B180" t="n">
-        <v>48.63718032836914</v>
+        <v>48.63719177246094</v>
       </c>
       <c r="C180" t="n">
         <v>60.66999816894531</v>
@@ -5181,7 +5181,7 @@
         <v>44196</v>
       </c>
       <c r="B181" t="n">
-        <v>47.23379135131836</v>
+        <v>47.23378753662109</v>
       </c>
       <c r="C181" t="n">
         <v>58.2599983215332</v>
@@ -5210,7 +5210,7 @@
         <v>44227</v>
       </c>
       <c r="B182" t="n">
-        <v>53.18463516235352</v>
+        <v>53.18462753295898</v>
       </c>
       <c r="C182" t="n">
         <v>65.59999847412109</v>
@@ -5355,7 +5355,7 @@
         <v>44377</v>
       </c>
       <c r="B187" t="n">
-        <v>57.05208969116211</v>
+        <v>57.05207824707031</v>
       </c>
       <c r="C187" t="n">
         <v>68.86000061035156</v>
@@ -5413,7 +5413,7 @@
         <v>44439</v>
       </c>
       <c r="B189" t="n">
-        <v>60.29988098144531</v>
+        <v>60.29989624023438</v>
       </c>
       <c r="C189" t="n">
         <v>72.77999877929688</v>
@@ -5442,7 +5442,7 @@
         <v>44469</v>
       </c>
       <c r="B190" t="n">
-        <v>58.45565032958984</v>
+        <v>58.45565795898438</v>
       </c>
       <c r="C190" t="n">
         <v>69.84999847412109</v>
@@ -5471,7 +5471,7 @@
         <v>44500</v>
       </c>
       <c r="B191" t="n">
-        <v>54.29639053344727</v>
+        <v>54.2963752746582</v>
       </c>
       <c r="C191" t="n">
         <v>64.87999725341797</v>
@@ -5500,7 +5500,7 @@
         <v>44530</v>
       </c>
       <c r="B192" t="n">
-        <v>57.68571853637695</v>
+        <v>57.68571472167969</v>
       </c>
       <c r="C192" t="n">
         <v>68.93000030517578</v>
@@ -5529,7 +5529,7 @@
         <v>44561</v>
       </c>
       <c r="B193" t="n">
-        <v>61.38264465332031</v>
+        <v>61.38263320922852</v>
       </c>
       <c r="C193" t="n">
         <v>72.61000061035156</v>
@@ -5558,7 +5558,7 @@
         <v>44592</v>
       </c>
       <c r="B194" t="n">
-        <v>58.0603141784668</v>
+        <v>58.06032562255859</v>
       </c>
       <c r="C194" t="n">
         <v>68.68000030517578</v>
@@ -5645,7 +5645,7 @@
         <v>44681</v>
       </c>
       <c r="B197" t="n">
-        <v>50.803955078125</v>
+        <v>50.80395126342773</v>
       </c>
       <c r="C197" t="n">
         <v>59.34000015258789</v>
@@ -5674,7 +5674,7 @@
         <v>44712</v>
       </c>
       <c r="B198" t="n">
-        <v>55.52133178710938</v>
+        <v>55.52133941650391</v>
       </c>
       <c r="C198" t="n">
         <v>64.84999847412109</v>
@@ -5703,7 +5703,7 @@
         <v>44742</v>
       </c>
       <c r="B199" t="n">
-        <v>53.57989883422852</v>
+        <v>53.57989501953125</v>
       </c>
       <c r="C199" t="n">
         <v>61.81000137329102</v>
@@ -5761,7 +5761,7 @@
         <v>44804</v>
       </c>
       <c r="B201" t="n">
-        <v>55.01887130737305</v>
+        <v>55.01887512207031</v>
       </c>
       <c r="C201" t="n">
         <v>63.47000122070312</v>
@@ -5790,7 +5790,7 @@
         <v>44834</v>
       </c>
       <c r="B202" t="n">
-        <v>54.08232879638672</v>
+        <v>54.08232498168945</v>
       </c>
       <c r="C202" t="n">
         <v>61.68999862670898</v>
@@ -5819,7 +5819,7 @@
         <v>44865</v>
       </c>
       <c r="B203" t="n">
-        <v>68.78424835205078</v>
+        <v>68.78424072265625</v>
       </c>
       <c r="C203" t="n">
         <v>78.45999908447266</v>
@@ -5848,7 +5848,7 @@
         <v>44895</v>
       </c>
       <c r="B204" t="n">
-        <v>76.99872589111328</v>
+        <v>76.99871826171875</v>
       </c>
       <c r="C204" t="n">
         <v>87.83000183105469</v>
@@ -5964,7 +5964,7 @@
         <v>45016</v>
       </c>
       <c r="B208" t="n">
-        <v>74.03971862792969</v>
+        <v>74.03972625732422</v>
       </c>
       <c r="C208" t="n">
         <v>82.97000122070312</v>
@@ -6022,7 +6022,7 @@
         <v>45077</v>
       </c>
       <c r="B210" t="n">
-        <v>68.65875244140625</v>
+        <v>68.65874481201172</v>
       </c>
       <c r="C210" t="n">
         <v>76.94000244140625</v>
@@ -6051,7 +6051,7 @@
         <v>45107</v>
       </c>
       <c r="B211" t="n">
-        <v>69.43860626220703</v>
+        <v>69.4385986328125</v>
       </c>
       <c r="C211" t="n">
         <v>77.06999969482422</v>
@@ -6080,7 +6080,7 @@
         <v>45138</v>
       </c>
       <c r="B212" t="n">
-        <v>68.60070037841797</v>
+        <v>68.60068511962891</v>
       </c>
       <c r="C212" t="n">
         <v>76.13999938964844</v>
@@ -6109,7 +6109,7 @@
         <v>45169</v>
       </c>
       <c r="B213" t="n">
-        <v>68.90702819824219</v>
+        <v>68.90703582763672</v>
       </c>
       <c r="C213" t="n">
         <v>76.48000335693359</v>
@@ -6138,7 +6138,7 @@
         <v>45199</v>
       </c>
       <c r="B214" t="n">
-        <v>68.18095397949219</v>
+        <v>68.18094635009766</v>
       </c>
       <c r="C214" t="n">
         <v>74.94000244140625</v>
@@ -6167,7 +6167,7 @@
         <v>45230</v>
       </c>
       <c r="B215" t="n">
-        <v>71.45626068115234</v>
+        <v>71.45625305175781</v>
       </c>
       <c r="C215" t="n">
         <v>78.54000091552734</v>
@@ -6196,7 +6196,7 @@
         <v>45260</v>
       </c>
       <c r="B216" t="n">
-        <v>69.69123077392578</v>
+        <v>69.69121551513672</v>
       </c>
       <c r="C216" t="n">
         <v>76.59999847412109</v>
@@ -6225,7 +6225,7 @@
         <v>45291</v>
       </c>
       <c r="B217" t="n">
-        <v>74.37482452392578</v>
+        <v>74.37480926513672</v>
       </c>
       <c r="C217" t="n">
         <v>81.01000213623047</v>
@@ -6254,7 +6254,7 @@
         <v>45322</v>
       </c>
       <c r="B218" t="n">
-        <v>71.85005950927734</v>
+        <v>71.85005187988281</v>
       </c>
       <c r="C218" t="n">
         <v>78.26000213623047</v>
@@ -6283,7 +6283,7 @@
         <v>45351</v>
       </c>
       <c r="B219" t="n">
-        <v>66.19458770751953</v>
+        <v>66.19459533691406</v>
       </c>
       <c r="C219" t="n">
         <v>72.09999847412109</v>
@@ -6312,7 +6312,7 @@
         <v>45382</v>
       </c>
       <c r="B220" t="n">
-        <v>67.93927764892578</v>
+        <v>67.93928527832031</v>
       </c>
       <c r="C220" t="n">
         <v>73.25</v>
@@ -6370,7 +6370,7 @@
         <v>45443</v>
       </c>
       <c r="B222" t="n">
-        <v>59.61034774780273</v>
+        <v>59.61032867431641</v>
       </c>
       <c r="C222" t="n">
         <v>64.26999664306641</v>
@@ -6399,7 +6399,7 @@
         <v>45473</v>
       </c>
       <c r="B223" t="n">
-        <v>64.41606140136719</v>
+        <v>64.41605377197266</v>
       </c>
       <c r="C223" t="n">
         <v>68.61000061035156</v>
@@ -6428,7 +6428,7 @@
         <v>45504</v>
       </c>
       <c r="B224" t="n">
-        <v>71.41065216064453</v>
+        <v>71.41064453125</v>
       </c>
       <c r="C224" t="n">
         <v>76.05999755859375</v>
@@ -6457,7 +6457,7 @@
         <v>45535</v>
       </c>
       <c r="B225" t="n">
-        <v>74.17094421386719</v>
+        <v>74.17093658447266</v>
       </c>
       <c r="C225" t="n">
         <v>79</v>
@@ -6486,7 +6486,7 @@
         <v>45565</v>
       </c>
       <c r="B226" t="n">
-        <v>79.45074462890625</v>
+        <v>79.45073699951172</v>
       </c>
       <c r="C226" t="n">
         <v>83.83999633789062</v>
@@ -6515,7 +6515,7 @@
         <v>45596</v>
       </c>
       <c r="B227" t="n">
-        <v>84.17002105712891</v>
+        <v>84.17003631591797</v>
       </c>
       <c r="C227" t="n">
         <v>88.81999969482422</v>
@@ -6544,7 +6544,7 @@
         <v>45626</v>
       </c>
       <c r="B228" t="n">
-        <v>87.73317718505859</v>
+        <v>87.73318481445312</v>
       </c>
       <c r="C228" t="n">
         <v>92.58000183105469</v>
@@ -6573,7 +6573,7 @@
         <v>45657</v>
       </c>
       <c r="B229" t="n">
-        <v>88.26992797851562</v>
+        <v>88.26990509033203</v>
       </c>
       <c r="C229" t="n">
         <v>92.37000274658203</v>
@@ -6602,7 +6602,7 @@
         <v>45688</v>
       </c>
       <c r="B230" t="n">
-        <v>92.88551330566406</v>
+        <v>92.88552093505859</v>
       </c>
       <c r="C230" t="n">
         <v>97.19999694824219</v>
@@ -6747,7 +6747,7 @@
         <v>45838</v>
       </c>
       <c r="B235" t="n">
-        <v>107.4498977661133</v>
+        <v>107.4499053955078</v>
       </c>
       <c r="C235" t="n">
         <v>110.870002746582</v>
@@ -6776,7 +6776,7 @@
         <v>45869</v>
       </c>
       <c r="B236" t="n">
-        <v>108.8260955810547</v>
+        <v>108.8261108398438</v>
       </c>
       <c r="C236" t="n">
         <v>112.2900009155273</v>
@@ -6863,7 +6863,7 @@
         <v>45961</v>
       </c>
       <c r="B239" t="n">
-        <v>116.9009628295898</v>
+        <v>116.9009552001953</v>
       </c>
       <c r="C239" t="n">
         <v>119.7900009155273</v>
@@ -6921,7 +6921,7 @@
         <v>46022</v>
       </c>
       <c r="B241" t="n">
-        <v>120.5709228515625</v>
+        <v>120.570930480957</v>
       </c>
       <c r="C241" t="n">
         <v>122.7399978637695</v>
